--- a/2026/SALTA 1167/Agosto/SALTA1167-Agosto.xlsx
+++ b/2026/SALTA 1167/Agosto/SALTA1167-Agosto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\SALTA 1167\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BC6BCB-73A8-4FBA-BE50-E7F8612137C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9B951C-E2CA-4EDC-ACD3-0CC4DA347267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$97</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$95</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="158">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -408,60 +413,9 @@
     <t>FCI FIMA</t>
   </si>
   <si>
-    <t>SALDO A FIN DE MES</t>
-  </si>
-  <si>
-    <t>VTO 17/08</t>
-  </si>
-  <si>
-    <t>PERÍODO: JULIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honorario administracion - Mes de JULIO </t>
-  </si>
-  <si>
-    <t>Transf 10/07</t>
-  </si>
-  <si>
-    <t>Transf 07/07</t>
-  </si>
-  <si>
-    <t>Transf 06/07</t>
-  </si>
-  <si>
-    <t>Transf 13/07</t>
-  </si>
-  <si>
-    <t>Transf 23/07</t>
-  </si>
-  <si>
-    <t>Easy Barracas - Compra de termotanque - Cuota 5  - Resta 1 cuotas de $157.988,29</t>
-  </si>
-  <si>
-    <t>Efectivo</t>
-  </si>
-  <si>
-    <t>Compra de pilas - Puerta SUM</t>
-  </si>
-  <si>
-    <t>Transf 30/07</t>
-  </si>
-  <si>
-    <t>Mantenimiento de cuenta - Bonificacion bancaria</t>
-  </si>
-  <si>
     <t>Saldo al 01/07</t>
   </si>
   <si>
-    <t>Megasec - Compra de matafuegos - Cuota 1/2</t>
-  </si>
-  <si>
-    <t>GrupoProtect - Compra de matafuego</t>
-  </si>
-  <si>
-    <t>Transf 27/07</t>
-  </si>
-  <si>
     <t>26/052026</t>
   </si>
   <si>
@@ -517,6 +471,45 @@
   </si>
   <si>
     <t>A gaston le doble cobramos un sum erroneamente el mes pasado, corregir en agosto - Debe abonar 132.216,09 , pago 182.216,09</t>
+  </si>
+  <si>
+    <t>VTO 17/09</t>
+  </si>
+  <si>
+    <t>PERÍODO: AGOSTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honorario administracion - Mes de AGOSTO </t>
+  </si>
+  <si>
+    <t>Transf 05/08</t>
+  </si>
+  <si>
+    <t>Transf 13/08</t>
+  </si>
+  <si>
+    <t>Transf 04/08</t>
+  </si>
+  <si>
+    <t>Transf 06/08</t>
+  </si>
+  <si>
+    <t>Megasec - Compra de matafuegos - Cuota 2/2</t>
+  </si>
+  <si>
+    <t>Transf 31/08</t>
+  </si>
+  <si>
+    <t>Easy Barracas - Compra de termotanque - Cuota 6  - Resta 0 cuotas de $157.988,29</t>
+  </si>
+  <si>
+    <t>SUM Mal cobrado</t>
+  </si>
+  <si>
+    <t>Mantenimiento de cuenta</t>
+  </si>
+  <si>
+    <t>SALDO A 30/08</t>
   </si>
 </sst>
 </file>
@@ -536,7 +529,7 @@
     <numFmt numFmtId="170" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
     <numFmt numFmtId="171" formatCode="0.0"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -756,6 +749,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -1471,21 +1471,14 @@
     </xf>
     <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="0" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="8" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="2" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1565,23 +1558,28 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1594,36 +1592,30 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1678,9 +1670,6 @@
     <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1699,6 +1688,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="29" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="29" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1778,9 +1778,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1818,9 +1818,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1853,9 +1853,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1888,9 +1905,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2064,22 +2098,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M101"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M99"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5546875" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.44140625" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
       <c r="B1" s="44" t="s">
         <v>73</v>
@@ -2088,7 +2122,7 @@
       <c r="D1" s="44"/>
       <c r="E1" s="45"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
       <c r="B2" s="46" t="s">
         <v>14</v>
@@ -2097,16 +2131,16 @@
       <c r="D2" s="46"/>
       <c r="E2" s="47"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13"/>
-      <c r="B3" s="220" t="s">
+      <c r="B3" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="220"/>
-      <c r="D3" s="220"/>
-      <c r="E3" s="221"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="216"/>
+      <c r="D3" s="216"/>
+      <c r="E3" s="217"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>0</v>
       </c>
@@ -2117,12 +2151,12 @@
       <c r="D4" s="17"/>
       <c r="E4" s="18"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>74</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="46" t="s">
@@ -2130,7 +2164,7 @@
       </c>
       <c r="E5" s="15"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>122</v>
       </c>
@@ -2141,57 +2175,57 @@
       </c>
       <c r="E6" s="18"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="223" t="s">
-        <v>126</v>
-      </c>
-      <c r="C8" s="223"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="223"/>
-      <c r="C9" s="223"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="223"/>
-      <c r="C10" s="223"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="222" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="219" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" s="219"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="219"/>
+      <c r="C9" s="219"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="219"/>
+      <c r="C10" s="219"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="218" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="222"/>
-      <c r="C13" s="222"/>
-      <c r="D13" s="222"/>
-      <c r="E13" s="222"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="222"/>
-      <c r="B14" s="222"/>
-      <c r="C14" s="222"/>
-      <c r="D14" s="222"/>
-      <c r="E14" s="222"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="222"/>
-      <c r="B15" s="222"/>
-      <c r="C15" s="222"/>
-      <c r="D15" s="222"/>
-      <c r="E15" s="222"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="222"/>
-      <c r="B16" s="222"/>
-      <c r="C16" s="222"/>
-      <c r="D16" s="222"/>
-      <c r="E16" s="222"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="218"/>
+      <c r="C13" s="218"/>
+      <c r="D13" s="218"/>
+      <c r="E13" s="218"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="218"/>
+      <c r="B14" s="218"/>
+      <c r="C14" s="218"/>
+      <c r="D14" s="218"/>
+      <c r="E14" s="218"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="218"/>
+      <c r="B15" s="218"/>
+      <c r="C15" s="218"/>
+      <c r="D15" s="218"/>
+      <c r="E15" s="218"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="218"/>
+      <c r="B16" s="218"/>
+      <c r="C16" s="218"/>
+      <c r="D16" s="218"/>
+      <c r="E16" s="218"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>101</v>
       </c>
@@ -2200,7 +2234,7 @@
       <c r="D20" s="6"/>
       <c r="E20" s="11"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
         <v>76</v>
       </c>
@@ -2209,29 +2243,29 @@
       <c r="D21" s="98"/>
       <c r="E21" s="93"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="218" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="212" t="s">
         <v>112</v>
       </c>
-      <c r="B22" s="219"/>
+      <c r="B22" s="213"/>
       <c r="C22" s="152"/>
-      <c r="D22" s="172">
+      <c r="D22" s="253">
         <v>510846.85</v>
       </c>
       <c r="E22" s="146" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="H22" s="82"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="218"/>
-      <c r="B23" s="219"/>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="212"/>
+      <c r="B23" s="213"/>
       <c r="C23" s="152"/>
       <c r="D23" s="172"/>
       <c r="E23" s="94"/>
       <c r="H23" s="82"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="153" t="s">
         <v>9</v>
       </c>
@@ -2243,7 +2277,7 @@
         <v>510846.85</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="154" t="s">
         <v>17</v>
       </c>
@@ -2252,20 +2286,20 @@
       <c r="D25" s="174"/>
       <c r="E25" s="138"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="218" t="s">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="212" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="219"/>
+      <c r="B26" s="213"/>
       <c r="C26" s="155"/>
-      <c r="D26" s="175">
-        <v>79864</v>
+      <c r="D26" s="254">
+        <v>79873.05</v>
       </c>
       <c r="E26" s="96" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="153" t="s">
         <v>1</v>
       </c>
@@ -2274,652 +2308,618 @@
       <c r="D27" s="173"/>
       <c r="E27" s="104">
         <f>SUM(D26:D26)</f>
-        <v>79864</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+        <v>79873.05</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="154" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="156"/>
       <c r="C28" s="156"/>
-      <c r="D28" s="176"/>
+      <c r="D28" s="175"/>
       <c r="E28" s="139"/>
     </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="65" t="s">
         <v>66</v>
       </c>
       <c r="B29" s="65"/>
       <c r="C29" s="65"/>
-      <c r="D29" s="177">
-        <v>162387.66</v>
+      <c r="D29" s="252">
+        <v>14396.25</v>
       </c>
       <c r="E29" s="96" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="65" t="s">
         <v>65</v>
       </c>
       <c r="B30" s="65"/>
       <c r="C30" s="65"/>
-      <c r="D30" s="177">
-        <v>7090.36</v>
+      <c r="D30" s="252">
+        <v>6644.39</v>
       </c>
       <c r="E30" s="146" t="str">
         <f>E31</f>
-        <v>Transf 06/07</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+        <v>Transf 04/08</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="65" t="s">
         <v>65</v>
       </c>
       <c r="B31" s="157"/>
       <c r="C31" s="65"/>
-      <c r="D31" s="177">
-        <v>482288.43</v>
+      <c r="D31" s="252">
+        <v>482119.34</v>
       </c>
       <c r="E31" s="96" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="216" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="217"/>
+      <c r="B32" s="215"/>
       <c r="C32" s="65"/>
-      <c r="D32" s="177">
-        <v>632390</v>
+      <c r="D32" s="252">
+        <v>872785.72</v>
       </c>
       <c r="E32" s="96" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="158" t="s">
         <v>77</v>
       </c>
       <c r="B33" s="159"/>
       <c r="C33" s="65"/>
-      <c r="D33" s="177">
-        <v>27338.01</v>
+      <c r="D33" s="252">
+        <v>28704.880000000001</v>
       </c>
       <c r="E33" s="96" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="153" t="s">
         <v>2</v>
       </c>
       <c r="B34" s="153"/>
       <c r="C34" s="153"/>
-      <c r="D34" s="178"/>
+      <c r="D34" s="177"/>
       <c r="E34" s="140">
         <f>SUM(D29:D33)</f>
-        <v>1311494.46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1404650.5799999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="154"/>
       <c r="B35" s="153"/>
       <c r="C35" s="153"/>
       <c r="D35" s="173"/>
       <c r="E35" s="141"/>
     </row>
-    <row r="36" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="218" t="s">
+    <row r="36" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="212" t="s">
         <v>114</v>
       </c>
-      <c r="B36" s="219"/>
+      <c r="B36" s="213"/>
       <c r="C36" s="65"/>
-      <c r="D36" s="177">
+      <c r="D36" s="252">
         <v>82000</v>
       </c>
       <c r="E36" s="96" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="160" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="B37" s="161"/>
       <c r="C37" s="65"/>
-      <c r="D37" s="177">
+      <c r="D37" s="252">
         <f>199530</f>
         <v>199530</v>
       </c>
       <c r="E37" s="96" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="218" t="s">
-        <v>141</v>
-      </c>
-      <c r="B38" s="219"/>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="212" t="s">
+        <v>154</v>
+      </c>
+      <c r="B38" s="213"/>
       <c r="C38" s="65"/>
-      <c r="D38" s="179">
-        <v>72635</v>
-      </c>
-      <c r="E38" s="96" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="218" t="s">
-        <v>134</v>
-      </c>
-      <c r="B39" s="219"/>
-      <c r="C39" s="65"/>
-      <c r="D39" s="179">
+      <c r="D38" s="256">
         <v>157988.29</v>
       </c>
-      <c r="E39" s="96"/>
-    </row>
-    <row r="40" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="218" t="s">
-        <v>136</v>
-      </c>
-      <c r="B40" s="219"/>
-      <c r="C40" s="65"/>
-      <c r="D40" s="179">
-        <v>8000</v>
-      </c>
-      <c r="E40" s="96" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="153" t="s">
+      <c r="E38" s="96"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="153" t="s">
         <v>6</v>
       </c>
-      <c r="B41" s="154"/>
-      <c r="C41" s="154"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="104">
-        <f>SUM(D36:D40)</f>
-        <v>520153.29000000004</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="154" t="s">
+      <c r="B39" s="154"/>
+      <c r="C39" s="154"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="104">
+        <f>SUM(D36:D38)</f>
+        <v>439518.29000000004</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="154" t="s">
         <v>11</v>
       </c>
-      <c r="B42" s="154"/>
-      <c r="C42" s="154"/>
-      <c r="D42" s="180"/>
-      <c r="E42" s="142"/>
-    </row>
-    <row r="43" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="218" t="s">
-        <v>128</v>
-      </c>
-      <c r="B43" s="219"/>
-      <c r="C43" s="152"/>
-      <c r="D43" s="181">
+      <c r="B40" s="154"/>
+      <c r="C40" s="154"/>
+      <c r="D40" s="178"/>
+      <c r="E40" s="142"/>
+    </row>
+    <row r="41" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="212" t="s">
+        <v>147</v>
+      </c>
+      <c r="B41" s="213"/>
+      <c r="C41" s="152"/>
+      <c r="D41" s="255">
         <v>190000</v>
       </c>
-      <c r="E43" s="143" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="153" t="s">
+      <c r="E41" s="143" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="153" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="153"/>
-      <c r="C44" s="153"/>
-      <c r="D44" s="173"/>
-      <c r="E44" s="137">
-        <f>SUM(D43:D43)</f>
+      <c r="B42" s="153"/>
+      <c r="C42" s="153"/>
+      <c r="D42" s="173"/>
+      <c r="E42" s="137">
+        <f>SUM(D41:D41)</f>
         <v>190000</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="154" t="s">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="154" t="s">
         <v>8</v>
       </c>
-      <c r="B45" s="162"/>
-      <c r="C45" s="153"/>
-      <c r="D45" s="182"/>
-      <c r="E45" s="104"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="65" t="s">
-        <v>138</v>
-      </c>
-      <c r="B46" s="65"/>
-      <c r="C46" s="65"/>
-      <c r="D46" s="177">
-        <v>0</v>
-      </c>
-      <c r="E46" s="144"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="65" t="s">
+      <c r="B43" s="162"/>
+      <c r="C43" s="153"/>
+      <c r="D43" s="179"/>
+      <c r="E43" s="104"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="B44" s="65"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="252"/>
+      <c r="E44" s="144"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="65" t="s">
         <v>113</v>
       </c>
+      <c r="B45" s="65"/>
+      <c r="C45" s="65"/>
+      <c r="D45" s="176">
+        <v>44926.11</v>
+      </c>
+      <c r="E45" s="145"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="163" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="163"/>
+      <c r="C46" s="163"/>
+      <c r="D46" s="180"/>
+      <c r="E46" s="104">
+        <f>SUM(D44:D45)</f>
+        <v>44926.11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="65"/>
       <c r="B47" s="65"/>
       <c r="C47" s="65"/>
-      <c r="D47" s="177">
-        <v>44926.11</v>
-      </c>
-      <c r="E47" s="145"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="163" t="s">
-        <v>9</v>
-      </c>
-      <c r="B48" s="163"/>
-      <c r="C48" s="163"/>
-      <c r="D48" s="183"/>
-      <c r="E48" s="104">
-        <f>SUM(D46:D47)</f>
-        <v>44926.11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="65"/>
-      <c r="B49" s="65"/>
-      <c r="C49" s="65"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="70"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="164" t="s">
+      <c r="D47" s="4"/>
+      <c r="E47" s="70"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="164" t="s">
         <v>97</v>
       </c>
-      <c r="B50" s="164"/>
-      <c r="C50" s="164"/>
-      <c r="D50" s="71"/>
-      <c r="E50" s="105"/>
-    </row>
-    <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="165"/>
+      <c r="B48" s="164"/>
+      <c r="C48" s="164"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="105"/>
+    </row>
+    <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="165"/>
+      <c r="B49" s="72"/>
+      <c r="C49" s="72"/>
+      <c r="D49" s="72"/>
+      <c r="E49" s="73"/>
+      <c r="F49" s="27"/>
+    </row>
+    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="166" t="s">
+        <v>93</v>
+      </c>
+      <c r="B50" s="167"/>
+      <c r="C50" s="74"/>
+      <c r="D50" s="74"/>
+      <c r="E50" s="75">
+        <f>(SUM(E21:E48))</f>
+        <v>2669814.88</v>
+      </c>
+      <c r="F50" s="92"/>
+      <c r="G50" s="27"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="72"/>
       <c r="B51" s="72"/>
       <c r="C51" s="72"/>
       <c r="D51" s="72"/>
-      <c r="E51" s="73"/>
-      <c r="F51" s="27"/>
-    </row>
-    <row r="52" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="166" t="s">
-        <v>93</v>
-      </c>
-      <c r="B52" s="167"/>
-      <c r="C52" s="74"/>
-      <c r="D52" s="74"/>
-      <c r="E52" s="75">
-        <f>(SUM(E21:E50))</f>
-        <v>2657284.71</v>
-      </c>
-      <c r="F52" s="92"/>
-      <c r="G52" s="27"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="72"/>
-      <c r="B53" s="72"/>
-      <c r="C53" s="72"/>
-      <c r="D53" s="72"/>
-      <c r="E53" s="72"/>
-    </row>
-    <row r="54" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="72"/>
-      <c r="B54" s="72"/>
-      <c r="C54" s="72"/>
-      <c r="D54" s="72"/>
-      <c r="E54" s="72"/>
-      <c r="H54" s="99"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="168" t="s">
+      <c r="E51" s="72"/>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="72"/>
+      <c r="B52" s="72"/>
+      <c r="C52" s="72"/>
+      <c r="D52" s="72"/>
+      <c r="E52" s="72"/>
+      <c r="H52" s="99"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="168" t="s">
         <v>94</v>
       </c>
-      <c r="B55" s="169"/>
-      <c r="C55" s="170"/>
-      <c r="D55" s="76"/>
-      <c r="E55" s="77"/>
-    </row>
-    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="171"/>
-      <c r="B56" s="159"/>
-      <c r="C56" s="65"/>
-      <c r="D56" s="68"/>
-      <c r="E56" s="66"/>
-    </row>
-    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="226"/>
-      <c r="B57" s="226"/>
-      <c r="C57" s="65"/>
-      <c r="D57" s="95"/>
+      <c r="B53" s="169"/>
+      <c r="C53" s="170"/>
+      <c r="D53" s="76"/>
+      <c r="E53" s="77"/>
+    </row>
+    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="171"/>
+      <c r="B54" s="159"/>
+      <c r="C54" s="65"/>
+      <c r="D54" s="68"/>
+      <c r="E54" s="66"/>
+    </row>
+    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="211"/>
+      <c r="B55" s="211"/>
+      <c r="C55" s="65"/>
+      <c r="D55" s="95"/>
+      <c r="E55" s="66"/>
+    </row>
+    <row r="56" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="67"/>
+      <c r="B57" s="69"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="68"/>
       <c r="E57" s="66"/>
     </row>
-    <row r="58" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="4"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="67"/>
-      <c r="B59" s="69"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="68"/>
-      <c r="E59" s="66"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="32"/>
-      <c r="B60" s="31"/>
-      <c r="C60" s="31"/>
-      <c r="D60" s="36"/>
-      <c r="E60" s="36">
-        <f>SUM(D56:D59)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="20" t="s">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="32"/>
+      <c r="B58" s="31"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="36"/>
+      <c r="E58" s="36">
+        <f>SUM(D54:D57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="B63" s="20"/>
-      <c r="C63" s="20"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="135"/>
-    </row>
-    <row r="64" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="2" t="s">
+      <c r="B61" s="20"/>
+      <c r="C61" s="20"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="135"/>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B65" s="7"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="43">
-        <f>E60+E63</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B63" s="7"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="43">
+        <f>E58+E61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="63" t="s">
+        <v>102</v>
+      </c>
+      <c r="B65" s="64">
+        <f>E50</f>
+        <v>2669814.88</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="B66" s="64">
+        <f>E50-E48</f>
+        <v>2669814.88</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="63" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B67" s="64">
-        <f>E52</f>
-        <v>2657284.71</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f>E63-E61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="63" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B68" s="64">
-        <f>E52-E50</f>
-        <v>2657284.71</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="B69" s="64">
-        <f>E65-E63</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="63" t="s">
-        <v>105</v>
-      </c>
-      <c r="B70" s="64">
-        <f>E65</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A72"/>
-      <c r="B72" s="26"/>
-      <c r="C72" s="24"/>
-    </row>
-    <row r="73" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="84" t="s">
+        <f>E63</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70"/>
+      <c r="B70" s="26"/>
+      <c r="C70" s="24"/>
+    </row>
+    <row r="71" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="84" t="s">
         <v>106</v>
       </c>
-      <c r="B73" s="111">
-        <v>-149034.37999999756</v>
-      </c>
-      <c r="C73" s="24"/>
-      <c r="D73" s="30"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B71" s="111">
+        <v>231226.35000000335</v>
+      </c>
+      <c r="C71" s="24"/>
+      <c r="D71" s="30"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="B72" s="89">
+        <f>-B66</f>
+        <v>-2669814.88</v>
+      </c>
+      <c r="E72" s="27"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" s="89">
+        <f>B94</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="B74" s="89">
-        <f>-B68</f>
-        <v>-2657284.71</v>
-      </c>
-      <c r="E74" s="27"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="B74" s="90">
+        <f>PRORRATEO!G36-B81</f>
+        <v>3248082.4500000007</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="91" t="s">
+        <v>155</v>
+      </c>
+      <c r="B75" s="100">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="87" t="s">
+        <v>110</v>
+      </c>
+      <c r="B76" s="88">
+        <f>SUM(B71:C75)</f>
+        <v>759493.92000000412</v>
+      </c>
+      <c r="D76" s="27"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="85"/>
+      <c r="B77" s="85"/>
+      <c r="D77" s="27"/>
+      <c r="E77" s="26"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="84" t="s">
+        <v>107</v>
+      </c>
+      <c r="B78" s="111">
+        <v>1000000</v>
+      </c>
+      <c r="D78" s="26"/>
+      <c r="E78" s="27"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B79" s="89">
+        <f>-B67</f>
+        <v>0</v>
+      </c>
+      <c r="D79" s="27"/>
+      <c r="E79" s="27"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B75" s="89">
-        <f>B96</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="B76" s="90">
-        <f>PRORRATEO!G36-B83</f>
-        <v>3037545.4400000009</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="91" t="s">
+      <c r="B80" s="89">
+        <f>B102</f>
+        <v>0</v>
+      </c>
+      <c r="D80" s="27"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="B81" s="90">
+        <v>0</v>
+      </c>
+      <c r="D81" s="136"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="B77" s="100"/>
-    </row>
-    <row r="78" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="87" t="s">
-        <v>110</v>
-      </c>
-      <c r="B78" s="88">
-        <f>SUM(B73:C77)</f>
-        <v>231226.35000000335</v>
-      </c>
-      <c r="D78" s="27"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="85"/>
-      <c r="B79" s="85"/>
-      <c r="D79" s="27"/>
-      <c r="E79" s="26"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="84" t="s">
-        <v>107</v>
-      </c>
-      <c r="B80" s="111">
+      <c r="B82" s="100"/>
+      <c r="D82" s="27"/>
+      <c r="E82" s="27"/>
+      <c r="F82" s="26"/>
+    </row>
+    <row r="83" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="87" t="s">
+        <v>111</v>
+      </c>
+      <c r="B83" s="88">
+        <f>SUM(B78:C82)</f>
         <v>1000000</v>
       </c>
-      <c r="D80" s="26"/>
-      <c r="E80" s="27"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="B81" s="89">
-        <f>-B69</f>
-        <v>0</v>
-      </c>
-      <c r="D81" s="27"/>
-      <c r="E81" s="27"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="B82" s="89">
-        <f>B104</f>
-        <v>0</v>
-      </c>
-      <c r="D82" s="27"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="B83" s="90">
-        <v>0</v>
-      </c>
-      <c r="D83" s="136"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="91" t="s">
-        <v>24</v>
-      </c>
-      <c r="B84" s="100"/>
-      <c r="D84" s="27"/>
-      <c r="E84" s="27"/>
-      <c r="F84" s="26"/>
-    </row>
-    <row r="85" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="87" t="s">
-        <v>111</v>
-      </c>
-      <c r="B85" s="88">
-        <f>SUM(B80:C84)</f>
-        <v>1000000</v>
-      </c>
-      <c r="D85" s="27"/>
-      <c r="F85" s="27"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="85"/>
-      <c r="B86" s="85"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="85"/>
-      <c r="B87" s="85"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="84" t="s">
+      <c r="D83" s="27"/>
+      <c r="F83" s="27"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" s="85"/>
+      <c r="B84" s="85"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" s="85"/>
+      <c r="B85" s="85"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" s="84" t="s">
         <v>124</v>
       </c>
-      <c r="B88" s="111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="B89" s="89">
+      <c r="B86" s="111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="B87" s="89">
         <v>1025063.51</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="87" t="s">
-        <v>125</v>
-      </c>
-      <c r="B90" s="88">
-        <v>1040813.49</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="225" t="s">
+    <row r="88" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="87" t="s">
+        <v>157</v>
+      </c>
+      <c r="B88" s="88">
+        <v>1054849.6000000001</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" s="210" t="s">
         <v>18</v>
       </c>
-      <c r="B92" s="225"/>
-      <c r="C92" s="225"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="225"/>
-      <c r="B93" s="225"/>
-      <c r="C93" s="225"/>
-    </row>
-    <row r="94" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="79"/>
-      <c r="B94" s="23"/>
-      <c r="C94" s="23">
+      <c r="B90" s="210"/>
+      <c r="C90" s="210"/>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" s="210"/>
+      <c r="B91" s="210"/>
+      <c r="C91" s="210"/>
+    </row>
+    <row r="92" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="79"/>
+      <c r="B92" s="23"/>
+      <c r="C92" s="23">
         <v>40000</v>
       </c>
-      <c r="E94" s="92"/>
-    </row>
-    <row r="95" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="79"/>
-      <c r="B95" s="81"/>
-      <c r="C95" s="78"/>
-      <c r="D95" s="92"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="28" t="s">
+      <c r="E92" s="92"/>
+    </row>
+    <row r="93" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="79"/>
+      <c r="B93" s="81"/>
+      <c r="C93" s="78"/>
+      <c r="D93" s="92"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B96" s="80">
-        <f>SUM(B94:B95)</f>
-        <v>0</v>
-      </c>
-      <c r="C96" s="29"/>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M97" s="5"/>
-    </row>
-    <row r="98" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="224"/>
-      <c r="B98" s="224"/>
-      <c r="C98" s="224"/>
-      <c r="D98" s="224"/>
-      <c r="E98" s="224"/>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A99" s="224"/>
-      <c r="B99" s="224"/>
-      <c r="C99" s="224"/>
-      <c r="D99" s="224"/>
-      <c r="E99" s="224"/>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A100" s="224"/>
-      <c r="B100" s="224"/>
-      <c r="C100" s="224"/>
-      <c r="D100" s="224"/>
-      <c r="E100" s="224"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A101" s="224"/>
-      <c r="B101" s="224"/>
-      <c r="C101" s="224"/>
-      <c r="D101" s="224"/>
-      <c r="E101" s="224"/>
+      <c r="B94" s="80">
+        <f>SUM(B92:B93)</f>
+        <v>0</v>
+      </c>
+      <c r="C94" s="29"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M95" s="5"/>
+    </row>
+    <row r="96" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="209"/>
+      <c r="B96" s="209"/>
+      <c r="C96" s="209"/>
+      <c r="D96" s="209"/>
+      <c r="E96" s="209"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="209"/>
+      <c r="B97" s="209"/>
+      <c r="C97" s="209"/>
+      <c r="D97" s="209"/>
+      <c r="E97" s="209"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="209"/>
+      <c r="B98" s="209"/>
+      <c r="C98" s="209"/>
+      <c r="D98" s="209"/>
+      <c r="E98" s="209"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="209"/>
+      <c r="B99" s="209"/>
+      <c r="C99" s="209"/>
+      <c r="D99" s="209"/>
+      <c r="E99" s="209"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A98:E101"/>
-    <mergeCell ref="A92:C93"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A43:B43"/>
+  <mergeCells count="13">
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
@@ -2927,6 +2927,12 @@
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A96:E99"/>
+    <mergeCell ref="A90:C91"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A41:B41"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2937,47 +2943,47 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4.44140625" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="1" max="2" width="4.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" customWidth="1"/>
     <col min="15" max="15" width="12" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="14.44140625" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="112"/>
       <c r="B1" s="113"/>
       <c r="C1" s="114"/>
       <c r="D1" s="114"/>
-      <c r="E1" s="227"/>
-      <c r="F1" s="227"/>
-      <c r="G1" s="227"/>
-      <c r="H1" s="227"/>
-      <c r="I1" s="227"/>
-      <c r="J1" s="227"/>
-      <c r="K1" s="227"/>
-      <c r="L1" s="227"/>
-      <c r="M1" s="227"/>
-      <c r="N1" s="227"/>
+      <c r="E1" s="225"/>
+      <c r="F1" s="225"/>
+      <c r="G1" s="225"/>
+      <c r="H1" s="225"/>
+      <c r="I1" s="225"/>
+      <c r="J1" s="225"/>
+      <c r="K1" s="225"/>
+      <c r="L1" s="225"/>
+      <c r="M1" s="225"/>
+      <c r="N1" s="225"/>
       <c r="O1" s="113"/>
       <c r="P1" s="115"/>
     </row>
-    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="116"/>
       <c r="B2" s="117"/>
       <c r="C2" s="118"/>
@@ -3004,7 +3010,7 @@
       <c r="P2" s="124"/>
       <c r="Q2" s="19"/>
     </row>
-    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="116"/>
       <c r="B3" s="117"/>
       <c r="C3" s="118"/>
@@ -3023,212 +3029,212 @@
       <c r="P3" s="124"/>
       <c r="Q3" s="19"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="238" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="232" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="239"/>
-      <c r="C4" s="239"/>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
-      <c r="M4" s="239"/>
-      <c r="N4" s="239"/>
-      <c r="O4" s="239"/>
-      <c r="P4" s="240"/>
+      <c r="B4" s="233"/>
+      <c r="C4" s="233"/>
+      <c r="D4" s="233"/>
+      <c r="E4" s="233"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="233"/>
+      <c r="J4" s="233"/>
+      <c r="K4" s="233"/>
+      <c r="L4" s="233"/>
+      <c r="M4" s="233"/>
+      <c r="N4" s="233"/>
+      <c r="O4" s="233"/>
+      <c r="P4" s="234"/>
       <c r="Q4" s="19"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="241"/>
-      <c r="B5" s="242"/>
-      <c r="C5" s="242"/>
-      <c r="D5" s="242"/>
-      <c r="E5" s="242"/>
-      <c r="F5" s="242"/>
-      <c r="G5" s="242"/>
-      <c r="H5" s="242"/>
-      <c r="I5" s="242"/>
-      <c r="J5" s="242"/>
-      <c r="K5" s="242"/>
-      <c r="L5" s="242"/>
-      <c r="M5" s="242"/>
-      <c r="N5" s="242"/>
-      <c r="O5" s="242"/>
-      <c r="P5" s="243"/>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="235"/>
+      <c r="B5" s="236"/>
+      <c r="C5" s="236"/>
+      <c r="D5" s="236"/>
+      <c r="E5" s="236"/>
+      <c r="F5" s="236"/>
+      <c r="G5" s="236"/>
+      <c r="H5" s="236"/>
+      <c r="I5" s="236"/>
+      <c r="J5" s="236"/>
+      <c r="K5" s="236"/>
+      <c r="L5" s="236"/>
+      <c r="M5" s="236"/>
+      <c r="N5" s="236"/>
+      <c r="O5" s="236"/>
+      <c r="P5" s="237"/>
       <c r="Q5" s="19"/>
     </row>
-    <row r="6" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="241"/>
-      <c r="B6" s="242"/>
-      <c r="C6" s="242"/>
-      <c r="D6" s="242"/>
-      <c r="E6" s="242"/>
-      <c r="F6" s="242"/>
-      <c r="G6" s="242"/>
-      <c r="H6" s="242"/>
-      <c r="I6" s="242"/>
-      <c r="J6" s="242"/>
-      <c r="K6" s="242"/>
-      <c r="L6" s="242"/>
-      <c r="M6" s="242"/>
-      <c r="N6" s="242"/>
-      <c r="O6" s="242"/>
-      <c r="P6" s="243"/>
+    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="235"/>
+      <c r="B6" s="236"/>
+      <c r="C6" s="236"/>
+      <c r="D6" s="236"/>
+      <c r="E6" s="236"/>
+      <c r="F6" s="236"/>
+      <c r="G6" s="236"/>
+      <c r="H6" s="236"/>
+      <c r="I6" s="236"/>
+      <c r="J6" s="236"/>
+      <c r="K6" s="236"/>
+      <c r="L6" s="236"/>
+      <c r="M6" s="236"/>
+      <c r="N6" s="236"/>
+      <c r="O6" s="236"/>
+      <c r="P6" s="237"/>
       <c r="Q6" s="19"/>
     </row>
-    <row r="7" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="241"/>
-      <c r="B7" s="242"/>
-      <c r="C7" s="242"/>
-      <c r="D7" s="242"/>
-      <c r="E7" s="242"/>
-      <c r="F7" s="242"/>
-      <c r="G7" s="242"/>
-      <c r="H7" s="242"/>
-      <c r="I7" s="242"/>
-      <c r="J7" s="242"/>
-      <c r="K7" s="242"/>
-      <c r="L7" s="242"/>
-      <c r="M7" s="242"/>
-      <c r="N7" s="242"/>
-      <c r="O7" s="242"/>
-      <c r="P7" s="243"/>
+    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="235"/>
+      <c r="B7" s="236"/>
+      <c r="C7" s="236"/>
+      <c r="D7" s="236"/>
+      <c r="E7" s="236"/>
+      <c r="F7" s="236"/>
+      <c r="G7" s="236"/>
+      <c r="H7" s="236"/>
+      <c r="I7" s="236"/>
+      <c r="J7" s="236"/>
+      <c r="K7" s="236"/>
+      <c r="L7" s="236"/>
+      <c r="M7" s="236"/>
+      <c r="N7" s="236"/>
+      <c r="O7" s="236"/>
+      <c r="P7" s="237"/>
       <c r="Q7" s="19"/>
     </row>
-    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="244"/>
-      <c r="B8" s="245"/>
-      <c r="C8" s="245"/>
-      <c r="D8" s="245"/>
-      <c r="E8" s="245"/>
-      <c r="F8" s="245"/>
-      <c r="G8" s="245"/>
-      <c r="H8" s="245"/>
-      <c r="I8" s="245"/>
-      <c r="J8" s="245"/>
-      <c r="K8" s="245"/>
-      <c r="L8" s="245"/>
-      <c r="M8" s="245"/>
-      <c r="N8" s="245"/>
-      <c r="O8" s="245"/>
-      <c r="P8" s="246"/>
-    </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="249" t="s">
+    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="238"/>
+      <c r="B8" s="239"/>
+      <c r="C8" s="239"/>
+      <c r="D8" s="239"/>
+      <c r="E8" s="239"/>
+      <c r="F8" s="239"/>
+      <c r="G8" s="239"/>
+      <c r="H8" s="239"/>
+      <c r="I8" s="239"/>
+      <c r="J8" s="239"/>
+      <c r="K8" s="239"/>
+      <c r="L8" s="239"/>
+      <c r="M8" s="239"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="240"/>
+    </row>
+    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="243" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="250"/>
-      <c r="C9" s="250"/>
-      <c r="D9" s="250"/>
-      <c r="E9" s="250"/>
-      <c r="F9" s="250"/>
-      <c r="G9" s="250"/>
-      <c r="H9" s="250"/>
-      <c r="I9" s="250"/>
-      <c r="J9" s="250"/>
-      <c r="K9" s="250"/>
-      <c r="L9" s="250"/>
-      <c r="M9" s="250"/>
-      <c r="N9" s="250"/>
-      <c r="O9" s="250"/>
-      <c r="P9" s="250"/>
-    </row>
-    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="251" t="s">
+      <c r="B9" s="244"/>
+      <c r="C9" s="244"/>
+      <c r="D9" s="244"/>
+      <c r="E9" s="244"/>
+      <c r="F9" s="244"/>
+      <c r="G9" s="244"/>
+      <c r="H9" s="244"/>
+      <c r="I9" s="244"/>
+      <c r="J9" s="244"/>
+      <c r="K9" s="244"/>
+      <c r="L9" s="244"/>
+      <c r="M9" s="244"/>
+      <c r="N9" s="244"/>
+      <c r="O9" s="244"/>
+      <c r="P9" s="244"/>
+    </row>
+    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="245" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="251"/>
-      <c r="C10" s="251"/>
-      <c r="D10" s="251"/>
-      <c r="E10" s="251"/>
-      <c r="F10" s="251"/>
-      <c r="G10" s="251"/>
-      <c r="H10" s="251"/>
-      <c r="I10" s="251"/>
-      <c r="J10" s="251"/>
-      <c r="K10" s="251"/>
-      <c r="L10" s="251"/>
-      <c r="M10" s="251"/>
-      <c r="N10" s="251"/>
-      <c r="O10" s="251"/>
-      <c r="P10" s="251"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="232" t="s">
+      <c r="B10" s="245"/>
+      <c r="C10" s="245"/>
+      <c r="D10" s="245"/>
+      <c r="E10" s="245"/>
+      <c r="F10" s="245"/>
+      <c r="G10" s="245"/>
+      <c r="H10" s="245"/>
+      <c r="I10" s="245"/>
+      <c r="J10" s="245"/>
+      <c r="K10" s="245"/>
+      <c r="L10" s="245"/>
+      <c r="M10" s="245"/>
+      <c r="N10" s="245"/>
+      <c r="O10" s="245"/>
+      <c r="P10" s="245"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="220" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="101"/>
-      <c r="C11" s="232" t="s">
+      <c r="C11" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="232" t="s">
+      <c r="D11" s="220" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="232" t="s">
+      <c r="E11" s="220" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="228" t="s">
+      <c r="F11" s="223" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="232" t="s">
+      <c r="G11" s="220" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="234" t="s">
+      <c r="H11" s="228" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="228" t="s">
+      <c r="I11" s="223" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="228" t="s">
+      <c r="J11" s="223" t="s">
         <v>91</v>
       </c>
-      <c r="K11" s="236" t="s">
+      <c r="K11" s="230" t="s">
         <v>92</v>
       </c>
-      <c r="L11" s="228" t="s">
+      <c r="L11" s="223" t="s">
         <v>78</v>
       </c>
-      <c r="M11" s="228" t="s">
+      <c r="M11" s="223" t="s">
         <v>123</v>
       </c>
       <c r="N11" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="230" t="s">
+      <c r="O11" s="226" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="247" t="s">
+      <c r="P11" s="241" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="233"/>
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="222"/>
       <c r="B12" s="102"/>
-      <c r="C12" s="233"/>
-      <c r="D12" s="252"/>
-      <c r="E12" s="233"/>
-      <c r="F12" s="229"/>
-      <c r="G12" s="233"/>
-      <c r="H12" s="235"/>
-      <c r="I12" s="229"/>
-      <c r="J12" s="229"/>
-      <c r="K12" s="237"/>
-      <c r="L12" s="229"/>
-      <c r="M12" s="229"/>
+      <c r="C12" s="222"/>
+      <c r="D12" s="221"/>
+      <c r="E12" s="222"/>
+      <c r="F12" s="224"/>
+      <c r="G12" s="222"/>
+      <c r="H12" s="229"/>
+      <c r="I12" s="224"/>
+      <c r="J12" s="224"/>
+      <c r="K12" s="231"/>
+      <c r="L12" s="224"/>
+      <c r="M12" s="224"/>
       <c r="N12" s="37" t="str">
         <f>RESUMEN!B8</f>
-        <v>VTO 17/08</v>
-      </c>
-      <c r="O12" s="231"/>
-      <c r="P12" s="248"/>
-    </row>
-    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>VTO 17/09</v>
+      </c>
+      <c r="O12" s="227"/>
+      <c r="P12" s="242"/>
+    </row>
+    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="40">
         <v>1</v>
       </c>
@@ -3243,19 +3249,19 @@
         <v>12</v>
       </c>
       <c r="F13" s="49">
-        <v>324000.01</v>
-      </c>
-      <c r="G13" s="184">
-        <f>356868.01-G29-G30</f>
-        <v>324009.66000000003</v>
+        <v>364055.01</v>
+      </c>
+      <c r="G13" s="257">
+        <f>400461-G29-G30</f>
+        <v>364054.65</v>
       </c>
       <c r="H13" s="51">
         <f t="shared" ref="H13:H35" si="0">F13-G13</f>
-        <v>-9.6500000000232831</v>
+        <v>0.35999999998603016</v>
       </c>
       <c r="I13" s="51">
         <f>IF(H13&gt;0,H13*3%,0)</f>
-        <v>0</v>
+        <v>1.0799999999580905E-2</v>
       </c>
       <c r="J13" s="97">
         <f t="shared" ref="J13:J35" si="1">K$2*E13/100</f>
@@ -3272,21 +3278,21 @@
       <c r="M13" s="148"/>
       <c r="N13" s="133">
         <f>ROUND(SUM(H13:M13),0) + Q13</f>
-        <v>353451.01</v>
+        <v>353461.01</v>
       </c>
       <c r="O13" s="52">
         <f>ROUND(N13*6% + N13,0) + Q13</f>
-        <v>374658.01</v>
+        <v>374669.01</v>
       </c>
       <c r="P13" s="53">
         <f>ROUND(N13*3%,0) + N13</f>
-        <v>364055.01</v>
+        <v>364065.01</v>
       </c>
       <c r="Q13" s="27">
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="126">
         <v>2</v>
       </c>
@@ -3301,14 +3307,15 @@
         <v>6.6</v>
       </c>
       <c r="F14" s="50">
-        <v>280517.02</v>
-      </c>
-      <c r="G14" s="184">
-        <v>281000</v>
+        <v>326822.02</v>
+      </c>
+      <c r="G14" s="257">
+        <f>F14</f>
+        <v>326822.02</v>
       </c>
       <c r="H14" s="129">
         <f t="shared" si="0"/>
-        <v>-482.97999999998137</v>
+        <v>0</v>
       </c>
       <c r="I14" s="129">
         <f t="shared" ref="I14:I35" si="3">IF(H14&gt;0,H14*3%,0)</f>
@@ -3329,22 +3336,22 @@
       <c r="M14" s="149"/>
       <c r="N14" s="133">
         <f t="shared" ref="N14:N35" si="4">ROUND(SUM(H14:M14),0) + Q14</f>
-        <v>326822.02</v>
+        <v>327305.02</v>
       </c>
       <c r="O14" s="131">
         <f t="shared" ref="O14:O30" si="5">ROUND(N14*6% + N14,0) + Q14</f>
-        <v>346431.02</v>
+        <v>346943.02</v>
       </c>
       <c r="P14" s="132">
         <f t="shared" ref="P14:P35" si="6">ROUND(N14*3%,0) + N14</f>
-        <v>336627.02</v>
+        <v>337124.02</v>
       </c>
       <c r="Q14" s="27">
         <f>Q13+0.01</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="40">
         <v>3</v>
       </c>
@@ -3361,11 +3368,11 @@
         <v>5.4</v>
       </c>
       <c r="F15" s="49">
-        <v>149456.03</v>
-      </c>
-      <c r="G15" s="184">
+        <v>159057.03</v>
+      </c>
+      <c r="G15" s="257">
         <f>F15</f>
-        <v>149456.03</v>
+        <v>159057.03</v>
       </c>
       <c r="H15" s="51">
         <f t="shared" si="0"/>
@@ -3405,7 +3412,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="40">
         <v>4</v>
       </c>
@@ -3422,15 +3429,15 @@
         <v>6.6</v>
       </c>
       <c r="F16" s="49">
-        <v>172600.04</v>
-      </c>
-      <c r="G16" s="184">
-        <f>189033-G32</f>
-        <v>172603.8</v>
+        <v>194400.04</v>
+      </c>
+      <c r="G16" s="257">
+        <f>218435-G32</f>
+        <v>200761.8</v>
       </c>
       <c r="H16" s="51">
         <f t="shared" si="0"/>
-        <v>-3.7599999999802094</v>
+        <v>-6361.7599999999802</v>
       </c>
       <c r="I16" s="51">
         <f t="shared" si="3"/>
@@ -3451,22 +3458,22 @@
       <c r="M16" s="148"/>
       <c r="N16" s="133">
         <f t="shared" si="4"/>
-        <v>194400.04</v>
+        <v>188042.04</v>
       </c>
       <c r="O16" s="52">
         <f t="shared" si="5"/>
-        <v>206064.04</v>
+        <v>199325.04</v>
       </c>
       <c r="P16" s="53">
         <f t="shared" si="6"/>
-        <v>200232.04</v>
+        <v>193683.04</v>
       </c>
       <c r="Q16" s="27">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="126">
         <v>5</v>
       </c>
@@ -3483,11 +3490,11 @@
         <v>6.6</v>
       </c>
       <c r="F17" s="50">
-        <v>178200.05</v>
-      </c>
-      <c r="G17" s="184">
+        <v>194403.05</v>
+      </c>
+      <c r="G17" s="257">
         <f>F17</f>
-        <v>178200.05</v>
+        <v>194403.05</v>
       </c>
       <c r="H17" s="129">
         <f t="shared" si="0"/>
@@ -3532,7 +3539,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <v>6</v>
       </c>
@@ -3549,18 +3556,19 @@
         <v>5.4</v>
       </c>
       <c r="F18" s="49">
-        <v>156924.06</v>
-      </c>
-      <c r="G18" s="184">
-        <v>129600.06</v>
+        <v>187201.06</v>
+      </c>
+      <c r="G18" s="257">
+        <f>F18</f>
+        <v>187201.06</v>
       </c>
       <c r="H18" s="51">
         <f t="shared" si="0"/>
-        <v>27324</v>
+        <v>0</v>
       </c>
       <c r="I18" s="51">
         <f t="shared" si="3"/>
-        <v>819.71999999999991</v>
+        <v>0</v>
       </c>
       <c r="J18" s="97">
         <f t="shared" si="1"/>
@@ -3577,22 +3585,22 @@
       <c r="M18" s="148"/>
       <c r="N18" s="133">
         <f t="shared" si="4"/>
-        <v>187201.06</v>
+        <v>159057.06</v>
       </c>
       <c r="O18" s="52">
         <f t="shared" si="5"/>
-        <v>198433.06</v>
+        <v>168600.06</v>
       </c>
       <c r="P18" s="53">
         <f t="shared" si="6"/>
-        <v>192817.06</v>
+        <v>163829.06</v>
       </c>
       <c r="Q18" s="27">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="126">
         <v>7</v>
       </c>
@@ -3609,11 +3617,11 @@
         <v>5.4</v>
       </c>
       <c r="F19" s="50">
-        <v>279288.07</v>
-      </c>
-      <c r="G19" s="184">
+        <v>159057.07</v>
+      </c>
+      <c r="G19" s="257">
         <f>F19</f>
-        <v>279288.07</v>
+        <v>159057.07</v>
       </c>
       <c r="H19" s="129">
         <f t="shared" si="0"/>
@@ -3653,7 +3661,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="126">
         <v>8</v>
       </c>
@@ -3670,11 +3678,11 @@
         <v>6.6</v>
       </c>
       <c r="F20" s="50">
-        <v>248675.08</v>
-      </c>
-      <c r="G20" s="184">
+        <v>258648.08</v>
+      </c>
+      <c r="G20" s="257">
         <f>F20</f>
-        <v>248675.08</v>
+        <v>258648.08</v>
       </c>
       <c r="H20" s="129">
         <f t="shared" si="0"/>
@@ -3714,32 +3722,33 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="213">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="126">
         <v>9</v>
       </c>
-      <c r="B21" s="213" t="s">
+      <c r="B21" s="126" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="213" t="s">
+      <c r="C21" s="126" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="214" t="s">
+      <c r="D21" s="127" t="s">
         <v>72</v>
       </c>
       <c r="E21" s="48">
         <v>6.6</v>
       </c>
       <c r="F21" s="49">
-        <v>199813.09</v>
-      </c>
-      <c r="G21" s="184">
-        <f>F21+12187.9</f>
-        <v>212000.99</v>
+        <f>50000+182216.09</f>
+        <v>232216.09</v>
+      </c>
+      <c r="G21" s="257">
+        <f>F21</f>
+        <v>232216.09</v>
       </c>
       <c r="H21" s="51">
         <f t="shared" si="0"/>
-        <v>-12187.899999999994</v>
+        <v>0</v>
       </c>
       <c r="I21" s="51">
         <f t="shared" si="3"/>
@@ -3762,47 +3771,47 @@
       </c>
       <c r="N21" s="133">
         <f t="shared" si="4"/>
-        <v>182216.09</v>
+        <v>194403.09</v>
       </c>
       <c r="O21" s="52">
         <f t="shared" si="5"/>
-        <v>193149.09</v>
+        <v>206067.09</v>
       </c>
       <c r="P21" s="53">
         <f t="shared" si="6"/>
-        <v>187682.09</v>
+        <v>200235.09</v>
       </c>
       <c r="Q21" s="27">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="40">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="126">
         <v>10</v>
       </c>
-      <c r="B22" s="40" t="s">
+      <c r="B22" s="126" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="126" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="41" t="s">
+      <c r="D22" s="127" t="s">
         <v>70</v>
       </c>
       <c r="E22" s="48">
         <v>5.4</v>
       </c>
       <c r="F22" s="49">
-        <v>16198.1</v>
-      </c>
-      <c r="G22" s="184">
-        <f>RESUMEN!D39+16198.1-12187.9</f>
-        <v>161998.49000000002</v>
+        <v>13257.1</v>
+      </c>
+      <c r="G22" s="257">
+        <f>F22+RESUMEN!D38</f>
+        <v>171245.39</v>
       </c>
       <c r="H22" s="51">
         <f>F22-G22</f>
-        <v>-145800.39000000001</v>
+        <v>-157988.29</v>
       </c>
       <c r="I22" s="51">
         <f t="shared" si="3"/>
@@ -3823,22 +3832,22 @@
       <c r="M22" s="148"/>
       <c r="N22" s="133">
         <f t="shared" si="4"/>
-        <v>13257.1</v>
+        <v>1069.0999999999999</v>
       </c>
       <c r="O22" s="52">
         <f t="shared" si="5"/>
-        <v>14053.1</v>
+        <v>1133.0999999999999</v>
       </c>
       <c r="P22" s="53">
         <f t="shared" si="6"/>
-        <v>13655.1</v>
+        <v>1101.0999999999999</v>
       </c>
       <c r="Q22" s="27">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="40">
         <v>11</v>
       </c>
@@ -3853,11 +3862,11 @@
         <v>5.4</v>
       </c>
       <c r="F23" s="49">
-        <v>145800.10999999999</v>
-      </c>
-      <c r="G23" s="184">
-        <f>154014.33-G34</f>
-        <v>145800.10999999999</v>
+        <v>159057.10999999999</v>
+      </c>
+      <c r="G23" s="257">
+        <f>167894.33-G34</f>
+        <v>159057.10999999999</v>
       </c>
       <c r="H23" s="51">
         <f t="shared" si="0"/>
@@ -3900,7 +3909,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>12</v>
       </c>
@@ -3917,11 +3926,11 @@
         <v>6.6</v>
       </c>
       <c r="F24" s="49">
-        <v>178200.12</v>
-      </c>
-      <c r="G24" s="184">
+        <v>194403.12</v>
+      </c>
+      <c r="G24" s="257">
         <f>F24</f>
-        <v>178200.12</v>
+        <v>194403.12</v>
       </c>
       <c r="H24" s="51">
         <f t="shared" si="0"/>
@@ -3961,7 +3970,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="40">
         <v>13</v>
       </c>
@@ -3978,15 +3987,14 @@
         <v>6.6</v>
       </c>
       <c r="F25" s="49">
-        <v>173579.13</v>
-      </c>
-      <c r="G25" s="184">
-        <f>F25</f>
-        <v>173579.13</v>
+        <v>194403.13</v>
+      </c>
+      <c r="G25" s="257">
+        <v>200235.13</v>
       </c>
       <c r="H25" s="51">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-5832</v>
       </c>
       <c r="I25" s="51">
         <f t="shared" si="3"/>
@@ -4007,22 +4015,22 @@
       <c r="M25" s="148"/>
       <c r="N25" s="133">
         <f t="shared" si="4"/>
-        <v>194403.13</v>
+        <v>188571.13</v>
       </c>
       <c r="O25" s="52">
         <f t="shared" si="5"/>
-        <v>206067.13</v>
+        <v>199885.13</v>
       </c>
       <c r="P25" s="53">
         <f t="shared" si="6"/>
-        <v>200235.13</v>
+        <v>194228.13</v>
       </c>
       <c r="Q25" s="27">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="126">
         <v>14</v>
       </c>
@@ -4037,10 +4045,11 @@
         <v>5.4</v>
       </c>
       <c r="F26" s="50">
-        <v>150174.14000000001</v>
-      </c>
-      <c r="G26" s="184">
-        <v>150174.14000000001</v>
+        <v>159057.14000000001</v>
+      </c>
+      <c r="G26" s="257">
+        <f>F26</f>
+        <v>159057.14000000001</v>
       </c>
       <c r="H26" s="129">
         <f t="shared" si="0"/>
@@ -4080,7 +4089,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="40">
         <v>15</v>
       </c>
@@ -4095,11 +4104,11 @@
         <v>5.4</v>
       </c>
       <c r="F27" s="49">
-        <v>145800.15</v>
-      </c>
-      <c r="G27" s="184">
+        <v>159057.15</v>
+      </c>
+      <c r="G27" s="257">
         <f>F27</f>
-        <v>145800.15</v>
+        <v>159057.15</v>
       </c>
       <c r="H27" s="51">
         <f t="shared" si="0"/>
@@ -4139,7 +4148,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="126">
         <v>16</v>
       </c>
@@ -4156,18 +4165,19 @@
         <v>0.7</v>
       </c>
       <c r="F28" s="49">
-        <v>20609.16</v>
-      </c>
-      <c r="G28" s="184">
-        <v>16800.16</v>
+        <v>24542.16</v>
+      </c>
+      <c r="G28" s="257">
+        <f>F28</f>
+        <v>24542.16</v>
       </c>
       <c r="H28" s="51">
         <f t="shared" si="0"/>
-        <v>3809</v>
+        <v>0</v>
       </c>
       <c r="I28" s="51">
         <f t="shared" si="3"/>
-        <v>114.27</v>
+        <v>0</v>
       </c>
       <c r="J28" s="97">
         <f t="shared" si="1"/>
@@ -4184,22 +4194,22 @@
       <c r="M28" s="148"/>
       <c r="N28" s="133">
         <f t="shared" si="4"/>
-        <v>24542.16</v>
+        <v>20619.16</v>
       </c>
       <c r="O28" s="52">
         <f t="shared" si="5"/>
-        <v>26015.16</v>
+        <v>21856.16</v>
       </c>
       <c r="P28" s="53">
         <f t="shared" si="6"/>
-        <v>25278.16</v>
+        <v>21238.16</v>
       </c>
       <c r="Q28" s="27">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="126">
         <v>17</v>
       </c>
@@ -4214,11 +4224,11 @@
         <v>0.6</v>
       </c>
       <c r="F29" s="50">
-        <v>16429.169999999998</v>
-      </c>
-      <c r="G29" s="184">
+        <v>18203.169999999998</v>
+      </c>
+      <c r="G29" s="257">
         <f>F29</f>
-        <v>16429.169999999998</v>
+        <v>18203.169999999998</v>
       </c>
       <c r="H29" s="51">
         <f t="shared" si="0"/>
@@ -4258,7 +4268,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>18</v>
       </c>
@@ -4273,11 +4283,11 @@
         <v>0.6</v>
       </c>
       <c r="F30" s="49">
-        <v>16429.18</v>
-      </c>
-      <c r="G30" s="184">
+        <v>18203.18</v>
+      </c>
+      <c r="G30" s="257">
         <f>F30</f>
-        <v>16429.18</v>
+        <v>18203.18</v>
       </c>
       <c r="H30" s="51">
         <f t="shared" si="0"/>
@@ -4317,7 +4327,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="126">
         <v>19</v>
       </c>
@@ -4332,11 +4342,11 @@
         <v>0.6</v>
       </c>
       <c r="F31" s="50">
-        <v>16429.189999999999</v>
-      </c>
-      <c r="G31" s="184">
+        <v>17673.189999999999</v>
+      </c>
+      <c r="G31" s="257">
         <f>F31</f>
-        <v>16429.189999999999</v>
+        <v>17673.189999999999</v>
       </c>
       <c r="H31" s="129">
         <f t="shared" si="0"/>
@@ -4373,7 +4383,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="21.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A32" s="54">
         <v>20</v>
       </c>
@@ -4390,11 +4400,11 @@
         <v>0.6</v>
       </c>
       <c r="F32" s="56">
-        <v>16429.2</v>
-      </c>
-      <c r="G32" s="184">
+        <v>17673.2</v>
+      </c>
+      <c r="G32" s="257">
         <f>F32</f>
-        <v>16429.2</v>
+        <v>17673.2</v>
       </c>
       <c r="H32" s="51">
         <f t="shared" si="0"/>
@@ -4431,7 +4441,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="54">
         <v>21</v>
       </c>
@@ -4448,11 +4458,11 @@
         <v>0.3</v>
       </c>
       <c r="F33" s="56">
-        <v>8214.2099999999991</v>
-      </c>
-      <c r="G33" s="184">
+        <v>8837.2099999999991</v>
+      </c>
+      <c r="G33" s="257">
         <f>F33</f>
-        <v>8214.2099999999991</v>
+        <v>8837.2099999999991</v>
       </c>
       <c r="H33" s="51">
         <f t="shared" si="0"/>
@@ -4489,7 +4499,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="55">
         <v>22</v>
       </c>
@@ -4504,11 +4514,11 @@
         <v>0.3</v>
       </c>
       <c r="F34" s="56">
-        <v>8214.2199999999993</v>
-      </c>
-      <c r="G34" s="185">
+        <v>8837.2199999999993</v>
+      </c>
+      <c r="G34" s="258">
         <f t="shared" ref="G34" si="9">F34</f>
-        <v>8214.2199999999993</v>
+        <v>8837.2199999999993</v>
       </c>
       <c r="H34" s="51">
         <f t="shared" si="0"/>
@@ -4545,7 +4555,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="40">
         <v>23</v>
       </c>
@@ -4562,11 +4572,11 @@
         <v>0.3</v>
       </c>
       <c r="F35" s="56">
-        <v>8214.23</v>
-      </c>
-      <c r="G35" s="184">
+        <v>8837.23</v>
+      </c>
+      <c r="G35" s="257">
         <f>F35</f>
-        <v>8214.23</v>
+        <v>8837.23</v>
       </c>
       <c r="H35" s="51">
         <f t="shared" si="0"/>
@@ -4603,7 +4613,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="59"/>
       <c r="B36" s="59"/>
       <c r="C36" s="60"/>
@@ -4614,19 +4624,19 @@
       </c>
       <c r="F36" s="34">
         <f>SUM(F13:F35)</f>
-        <v>2910193.7600000012</v>
+        <v>3077900.7600000012</v>
       </c>
       <c r="G36" s="38">
         <f>SUM(G13:G35)</f>
-        <v>3037545.4400000009</v>
+        <v>3248082.4500000007</v>
       </c>
       <c r="H36" s="38">
         <f>SUM(H13:H35)</f>
-        <v>-127351.67999999999</v>
+        <v>-170181.69</v>
       </c>
       <c r="I36" s="38">
         <f t="shared" ref="I36:O36" si="10">SUM(I13:I35)</f>
-        <v>933.9899999999999</v>
+        <v>1.0799999999580905E-2</v>
       </c>
       <c r="J36" s="86">
         <f t="shared" si="10"/>
@@ -4643,117 +4653,111 @@
       <c r="M36" s="61"/>
       <c r="N36" s="61">
         <f>SUM(N13:N35)</f>
-        <v>3016236.7600000012</v>
+        <v>2972471.7600000012</v>
       </c>
       <c r="O36" s="61">
         <f t="shared" si="10"/>
-        <v>3131643.7100000004</v>
+        <v>3085251.7100000004</v>
       </c>
       <c r="P36" s="61">
         <f>SUM(P13:P35)</f>
-        <v>3106723.7600000012</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>3061645.7600000012</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="33"/>
       <c r="D37" s="33"/>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="224" t="str">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="209" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="224"/>
-      <c r="E39" s="224"/>
-      <c r="F39" s="224"/>
-      <c r="G39" s="224"/>
-      <c r="H39" s="224"/>
-      <c r="I39" s="224"/>
-      <c r="J39" s="224"/>
-      <c r="K39" s="224"/>
-      <c r="L39" s="224"/>
-      <c r="M39" s="224"/>
-      <c r="N39" s="224"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="224"/>
-      <c r="D40" s="224"/>
-      <c r="E40" s="224"/>
-      <c r="F40" s="224"/>
-      <c r="G40" s="224"/>
-      <c r="H40" s="224"/>
-      <c r="I40" s="224"/>
-      <c r="J40" s="224"/>
-      <c r="K40" s="224"/>
-      <c r="L40" s="224"/>
-      <c r="M40" s="224"/>
-      <c r="N40" s="224"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="224"/>
-      <c r="D41" s="224"/>
-      <c r="E41" s="224"/>
-      <c r="F41" s="224"/>
-      <c r="G41" s="224"/>
-      <c r="H41" s="224"/>
-      <c r="I41" s="224"/>
-      <c r="J41" s="224"/>
-      <c r="K41" s="224"/>
-      <c r="L41" s="224"/>
-      <c r="M41" s="224"/>
-      <c r="N41" s="224"/>
-    </row>
-    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="224"/>
-      <c r="D42" s="224"/>
-      <c r="E42" s="224"/>
-      <c r="F42" s="224"/>
-      <c r="G42" s="224"/>
-      <c r="H42" s="224"/>
-      <c r="I42" s="224"/>
-      <c r="J42" s="224"/>
-      <c r="K42" s="224"/>
-      <c r="L42" s="224"/>
-      <c r="M42" s="224"/>
-      <c r="N42" s="224"/>
-    </row>
-    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="224"/>
-      <c r="D43" s="224"/>
-      <c r="E43" s="224"/>
-      <c r="F43" s="224"/>
-      <c r="G43" s="224"/>
-      <c r="H43" s="224"/>
-      <c r="I43" s="224"/>
-      <c r="J43" s="224"/>
-      <c r="K43" s="224"/>
-      <c r="L43" s="224"/>
-      <c r="M43" s="224"/>
-      <c r="N43" s="224"/>
-    </row>
-    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="224"/>
-      <c r="D44" s="224"/>
-      <c r="E44" s="224"/>
-      <c r="F44" s="224"/>
-      <c r="G44" s="224"/>
-      <c r="H44" s="224"/>
-      <c r="I44" s="224"/>
-      <c r="J44" s="224"/>
-      <c r="K44" s="224"/>
-      <c r="L44" s="224"/>
-      <c r="M44" s="224"/>
-      <c r="N44" s="224"/>
+      <c r="D39" s="209"/>
+      <c r="E39" s="209"/>
+      <c r="F39" s="209"/>
+      <c r="G39" s="209"/>
+      <c r="H39" s="209"/>
+      <c r="I39" s="209"/>
+      <c r="J39" s="209"/>
+      <c r="K39" s="209"/>
+      <c r="L39" s="209"/>
+      <c r="M39" s="209"/>
+      <c r="N39" s="209"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="209"/>
+      <c r="D40" s="209"/>
+      <c r="E40" s="209"/>
+      <c r="F40" s="209"/>
+      <c r="G40" s="209"/>
+      <c r="H40" s="209"/>
+      <c r="I40" s="209"/>
+      <c r="J40" s="209"/>
+      <c r="K40" s="209"/>
+      <c r="L40" s="209"/>
+      <c r="M40" s="209"/>
+      <c r="N40" s="209"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="209"/>
+      <c r="D41" s="209"/>
+      <c r="E41" s="209"/>
+      <c r="F41" s="209"/>
+      <c r="G41" s="209"/>
+      <c r="H41" s="209"/>
+      <c r="I41" s="209"/>
+      <c r="J41" s="209"/>
+      <c r="K41" s="209"/>
+      <c r="L41" s="209"/>
+      <c r="M41" s="209"/>
+      <c r="N41" s="209"/>
+    </row>
+    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="209"/>
+      <c r="D42" s="209"/>
+      <c r="E42" s="209"/>
+      <c r="F42" s="209"/>
+      <c r="G42" s="209"/>
+      <c r="H42" s="209"/>
+      <c r="I42" s="209"/>
+      <c r="J42" s="209"/>
+      <c r="K42" s="209"/>
+      <c r="L42" s="209"/>
+      <c r="M42" s="209"/>
+      <c r="N42" s="209"/>
+    </row>
+    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="209"/>
+      <c r="D43" s="209"/>
+      <c r="E43" s="209"/>
+      <c r="F43" s="209"/>
+      <c r="G43" s="209"/>
+      <c r="H43" s="209"/>
+      <c r="I43" s="209"/>
+      <c r="J43" s="209"/>
+      <c r="K43" s="209"/>
+      <c r="L43" s="209"/>
+      <c r="M43" s="209"/>
+      <c r="N43" s="209"/>
+    </row>
+    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="209"/>
+      <c r="D44" s="209"/>
+      <c r="E44" s="209"/>
+      <c r="F44" s="209"/>
+      <c r="G44" s="209"/>
+      <c r="H44" s="209"/>
+      <c r="I44" s="209"/>
+      <c r="J44" s="209"/>
+      <c r="K44" s="209"/>
+      <c r="L44" s="209"/>
+      <c r="M44" s="209"/>
+      <c r="N44" s="209"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C39:N44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="M11:M12"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4767,6 +4771,12 @@
     <mergeCell ref="A9:P9"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="L11:L12"/>
+    <mergeCell ref="C39:N44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="M11:M12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4776,11 +4786,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B474AF3-BA14-4AC3-BE41-D99CD4C43EE8}">
   <dimension ref="C3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C3" s="215" t="s">
-        <v>161</v>
+    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="208" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -4791,79 +4801,79 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A2E191-9409-46F3-B653-02D2C9674BEA}">
   <dimension ref="B2:K39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" style="204" customWidth="1"/>
-    <col min="6" max="6" width="13" style="204" customWidth="1"/>
-    <col min="7" max="7" width="18.109375" style="204" customWidth="1"/>
-    <col min="8" max="8" width="18.44140625" style="204" customWidth="1"/>
-    <col min="9" max="9" width="11.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="199" customWidth="1"/>
+    <col min="6" max="6" width="13" style="199" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" style="199" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" style="199" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" style="1" customWidth="1"/>
     <col min="10" max="10" width="15" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.6640625" style="204" customWidth="1"/>
-    <col min="12" max="12" width="2.6640625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.109375" style="1"/>
+    <col min="11" max="11" width="15.7109375" style="199" customWidth="1"/>
+    <col min="12" max="12" width="2.7109375" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="106" t="s">
         <v>79</v>
       </c>
       <c r="C2" s="106" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="186" t="s">
-        <v>143</v>
-      </c>
-      <c r="E2" s="186" t="s">
-        <v>144</v>
+      <c r="D2" s="181" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" s="181" t="s">
+        <v>127</v>
       </c>
       <c r="F2" s="106" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="G2" s="106" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="H2" s="107" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="I2" s="106"/>
-      <c r="J2" s="187" t="s">
-        <v>148</v>
+      <c r="J2" s="182" t="s">
+        <v>131</v>
       </c>
       <c r="K2" s="107" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B3" s="188">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B3" s="183">
         <v>1</v>
       </c>
-      <c r="C3" s="188" t="s">
+      <c r="C3" s="183" t="s">
         <v>81</v>
       </c>
-      <c r="D3" s="189">
+      <c r="D3" s="184">
         <v>8687.5</v>
       </c>
-      <c r="E3" s="189">
+      <c r="E3" s="184">
         <v>8687.5</v>
       </c>
-      <c r="F3" s="190">
+      <c r="F3" s="185">
         <f>(E3-D3)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="191">
+      <c r="G3" s="186">
         <f>F3/F32</f>
         <v>0</v>
       </c>
-      <c r="H3" s="192">
+      <c r="H3" s="187">
         <f>(F3/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I3" s="193">
+      <c r="I3" s="188">
         <v>0.12</v>
       </c>
       <c r="J3" s="151">
@@ -4875,32 +4885,32 @@
         <v>29460.826927751194</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="194">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B4" s="189">
         <v>1</v>
       </c>
-      <c r="C4" s="194" t="s">
+      <c r="C4" s="189" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="195">
+      <c r="D4" s="190">
         <v>4488.6000000000004</v>
       </c>
-      <c r="E4" s="195">
+      <c r="E4" s="190">
         <v>4865.1000000000004</v>
       </c>
-      <c r="F4" s="196">
+      <c r="F4" s="191">
         <f>(E4-D4)</f>
         <v>376.5</v>
       </c>
-      <c r="G4" s="197">
+      <c r="G4" s="192">
         <f>F4/F32</f>
         <v>0.67412712623097581</v>
       </c>
-      <c r="H4" s="192">
+      <c r="H4" s="187">
         <f>(F4/F32)*H32</f>
         <v>132902.00501196174</v>
       </c>
-      <c r="I4" s="198">
+      <c r="I4" s="193">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J4" s="151">
@@ -4912,32 +4922,32 @@
         <v>149105.45982222489</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="194">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B5" s="189">
         <v>1</v>
       </c>
-      <c r="C5" s="194" t="s">
+      <c r="C5" s="189" t="s">
         <v>83</v>
       </c>
-      <c r="D5" s="189">
+      <c r="D5" s="184">
         <v>2366.38</v>
       </c>
-      <c r="E5" s="189">
+      <c r="E5" s="184">
         <v>2366.38</v>
       </c>
-      <c r="F5" s="190">
+      <c r="F5" s="185">
         <f t="shared" ref="F5:F17" si="1">(E5-D5)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="191">
+      <c r="G5" s="186">
         <f>F5/F32</f>
         <v>0</v>
       </c>
-      <c r="H5" s="192">
+      <c r="H5" s="187">
         <f>(F5/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I5" s="198">
+      <c r="I5" s="193">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J5" s="151">
@@ -4949,32 +4959,32 @@
         <v>13257.372117488037</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="188">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B6" s="183">
         <v>2</v>
       </c>
-      <c r="C6" s="188" t="s">
+      <c r="C6" s="183" t="s">
         <v>81</v>
       </c>
-      <c r="D6" s="189">
+      <c r="D6" s="184">
         <v>3731.1</v>
       </c>
-      <c r="E6" s="189">
+      <c r="E6" s="184">
         <v>3731.1</v>
       </c>
-      <c r="F6" s="190">
+      <c r="F6" s="185">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G6" s="191">
+      <c r="G6" s="186">
         <f>F6/F32</f>
         <v>0</v>
       </c>
-      <c r="H6" s="192">
+      <c r="H6" s="187">
         <f>(F6/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I6" s="198">
+      <c r="I6" s="193">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J6" s="151">
@@ -4986,32 +4996,32 @@
         <v>13257.372117488037</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="188">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B7" s="183">
         <v>2</v>
       </c>
-      <c r="C7" s="188" t="s">
+      <c r="C7" s="183" t="s">
         <v>84</v>
       </c>
-      <c r="D7" s="189">
+      <c r="D7" s="184">
         <v>3897.7</v>
       </c>
-      <c r="E7" s="189">
+      <c r="E7" s="184">
         <v>3897.7</v>
       </c>
-      <c r="F7" s="190">
+      <c r="F7" s="185">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G7" s="191">
+      <c r="G7" s="186">
         <f>F7/F32</f>
         <v>0</v>
       </c>
-      <c r="H7" s="192">
+      <c r="H7" s="187">
         <f>(F7/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I7" s="198">
+      <c r="I7" s="193">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J7" s="151">
@@ -5023,32 +5033,32 @@
         <v>16203.454810263158</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="188">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B8" s="183">
         <v>2</v>
       </c>
-      <c r="C8" s="188" t="s">
+      <c r="C8" s="183" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="189">
+      <c r="D8" s="184">
         <v>2956.2</v>
       </c>
-      <c r="E8" s="189">
+      <c r="E8" s="184">
         <v>2956.2</v>
       </c>
-      <c r="F8" s="190">
+      <c r="F8" s="185">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G8" s="191">
+      <c r="G8" s="186">
         <f>F8/F32</f>
         <v>0</v>
       </c>
-      <c r="H8" s="192">
+      <c r="H8" s="187">
         <f>(F8/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I8" s="198">
+      <c r="I8" s="193">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J8" s="151">
@@ -5060,32 +5070,32 @@
         <v>16203.454810263158</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="188">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B9" s="183">
         <v>2</v>
       </c>
-      <c r="C9" s="188" t="s">
+      <c r="C9" s="183" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="189">
+      <c r="D9" s="184">
         <v>3923.7</v>
       </c>
-      <c r="E9" s="189">
+      <c r="E9" s="184">
         <v>3923.7</v>
       </c>
-      <c r="F9" s="190">
+      <c r="F9" s="185">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G9" s="191">
+      <c r="G9" s="186">
         <f>F9/F32</f>
         <v>0</v>
       </c>
-      <c r="H9" s="199">
+      <c r="H9" s="194">
         <f>(F9/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I9" s="198">
+      <c r="I9" s="193">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J9" s="151">
@@ -5097,32 +5107,32 @@
         <v>13257.372117488037</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="188">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B10" s="183">
         <v>3</v>
       </c>
-      <c r="C10" s="188" t="s">
+      <c r="C10" s="183" t="s">
         <v>81</v>
       </c>
-      <c r="D10" s="189">
+      <c r="D10" s="184">
         <v>2881.8</v>
       </c>
-      <c r="E10" s="189">
+      <c r="E10" s="184">
         <v>2881.8</v>
       </c>
-      <c r="F10" s="190">
+      <c r="F10" s="185">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G10" s="191">
+      <c r="G10" s="186">
         <f>F10/F32</f>
         <v>0</v>
       </c>
-      <c r="H10" s="192">
+      <c r="H10" s="187">
         <f>(F10/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I10" s="198">
+      <c r="I10" s="193">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J10" s="151">
@@ -5134,32 +5144,32 @@
         <v>13257.372117488037</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="194">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B11" s="189">
         <v>3</v>
       </c>
-      <c r="C11" s="194" t="s">
+      <c r="C11" s="189" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="195">
+      <c r="D11" s="190">
         <v>4646</v>
       </c>
-      <c r="E11" s="195">
+      <c r="E11" s="190">
         <v>4828</v>
       </c>
-      <c r="F11" s="196">
+      <c r="F11" s="191">
         <f t="shared" si="1"/>
         <v>182</v>
       </c>
-      <c r="G11" s="197">
+      <c r="G11" s="192">
         <f>F11/F32</f>
         <v>0.32587287376902419</v>
       </c>
-      <c r="H11" s="192">
+      <c r="H11" s="187">
         <f>(F11/F32)*H32</f>
         <v>64244.793923444988</v>
       </c>
-      <c r="I11" s="198">
+      <c r="I11" s="193">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J11" s="151">
@@ -5171,32 +5181,32 @@
         <v>80448.24873370814</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="188">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B12" s="183">
         <v>3</v>
       </c>
-      <c r="C12" s="188" t="s">
+      <c r="C12" s="183" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="189">
+      <c r="D12" s="184">
         <v>4554.6000000000004</v>
       </c>
-      <c r="E12" s="189">
+      <c r="E12" s="184">
         <v>4554.6000000000004</v>
       </c>
-      <c r="F12" s="190">
+      <c r="F12" s="185">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G12" s="191">
+      <c r="G12" s="186">
         <f>F12/F32</f>
         <v>0</v>
       </c>
-      <c r="H12" s="192">
+      <c r="H12" s="187">
         <f>(F12/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I12" s="198">
+      <c r="I12" s="193">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J12" s="151">
@@ -5208,32 +5218,32 @@
         <v>16203.454810263158</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="188">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B13" s="183">
         <v>3</v>
       </c>
-      <c r="C13" s="188" t="s">
+      <c r="C13" s="183" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="189">
+      <c r="D13" s="184">
         <v>4138.6000000000004</v>
       </c>
-      <c r="E13" s="189">
+      <c r="E13" s="184">
         <v>4138.6000000000004</v>
       </c>
-      <c r="F13" s="190">
+      <c r="F13" s="185">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G13" s="191">
+      <c r="G13" s="186">
         <f>F13/F32</f>
         <v>0</v>
       </c>
-      <c r="H13" s="192">
+      <c r="H13" s="187">
         <f>(F13/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I13" s="198">
+      <c r="I13" s="193">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J13" s="151">
@@ -5245,32 +5255,32 @@
         <v>13257.372117488037</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="188">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B14" s="183">
         <v>4</v>
       </c>
-      <c r="C14" s="188" t="s">
+      <c r="C14" s="183" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="189">
+      <c r="D14" s="184">
         <v>8190.4</v>
       </c>
-      <c r="E14" s="189">
+      <c r="E14" s="184">
         <v>8190.4</v>
       </c>
-      <c r="F14" s="190">
+      <c r="F14" s="185">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G14" s="191">
+      <c r="G14" s="186">
         <f>F14/F32</f>
         <v>0</v>
       </c>
-      <c r="H14" s="192">
+      <c r="H14" s="187">
         <f>(F14/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I14" s="198">
+      <c r="I14" s="193">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J14" s="151">
@@ -5282,32 +5292,32 @@
         <v>13257.372117488037</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="188">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B15" s="183">
         <v>4</v>
       </c>
-      <c r="C15" s="188" t="s">
+      <c r="C15" s="183" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="189">
+      <c r="D15" s="184">
         <v>3475.3</v>
       </c>
-      <c r="E15" s="189">
+      <c r="E15" s="184">
         <v>3475.3</v>
       </c>
-      <c r="F15" s="190">
+      <c r="F15" s="185">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G15" s="191">
+      <c r="G15" s="186">
         <f>F15/F32</f>
         <v>0</v>
       </c>
-      <c r="H15" s="192">
+      <c r="H15" s="187">
         <f>(F15/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I15" s="198">
+      <c r="I15" s="193">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J15" s="151">
@@ -5319,32 +5329,32 @@
         <v>16203.454810263158</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="188">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B16" s="183">
         <v>4</v>
       </c>
-      <c r="C16" s="188" t="s">
+      <c r="C16" s="183" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="189">
+      <c r="D16" s="184">
         <v>4363.3</v>
       </c>
-      <c r="E16" s="189">
+      <c r="E16" s="184">
         <v>4363.3</v>
       </c>
-      <c r="F16" s="190">
+      <c r="F16" s="185">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G16" s="191">
+      <c r="G16" s="186">
         <f>F16/F32</f>
         <v>0</v>
       </c>
-      <c r="H16" s="192">
+      <c r="H16" s="187">
         <f>(F16/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I16" s="198">
+      <c r="I16" s="193">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J16" s="151">
@@ -5356,32 +5366,32 @@
         <v>16203.454810263158</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B17" s="188">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17" s="183">
         <v>4</v>
       </c>
-      <c r="C17" s="188" t="s">
+      <c r="C17" s="183" t="s">
         <v>83</v>
       </c>
-      <c r="D17" s="189">
+      <c r="D17" s="184">
         <v>6036.6</v>
       </c>
-      <c r="E17" s="189">
+      <c r="E17" s="184">
         <v>6036.6</v>
       </c>
-      <c r="F17" s="190">
+      <c r="F17" s="185">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G17" s="191">
+      <c r="G17" s="186">
         <f>F17/F32</f>
         <v>0</v>
       </c>
-      <c r="H17" s="192">
+      <c r="H17" s="187">
         <f>(F17/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I17" s="198">
+      <c r="I17" s="193">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J17" s="151">
@@ -5393,24 +5403,24 @@
         <v>13257.372117488037</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="106"/>
       <c r="C18" s="106"/>
-      <c r="D18" s="200"/>
-      <c r="E18" s="200"/>
-      <c r="F18" s="201">
+      <c r="D18" s="195"/>
+      <c r="E18" s="195"/>
+      <c r="F18" s="196">
         <f>SUM(F3:F17)</f>
         <v>558.5</v>
       </c>
       <c r="G18" s="107" t="s">
-        <v>150</v>
-      </c>
-      <c r="H18" s="192">
+        <v>133</v>
+      </c>
+      <c r="H18" s="187">
         <f>SUM(H3:H17)</f>
         <v>197146.79893540672</v>
       </c>
       <c r="I18" s="106"/>
-      <c r="J18" s="202">
+      <c r="J18" s="197">
         <f>SUM(J3:J17)</f>
         <v>235686.61542200952</v>
       </c>
@@ -5419,20 +5429,20 @@
         <v>432833.41435741622</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="106"/>
       <c r="C19" s="106"/>
       <c r="D19" s="106"/>
       <c r="E19" s="106"/>
       <c r="F19" s="106"/>
       <c r="G19" s="106"/>
-      <c r="H19" s="203"/>
+      <c r="H19" s="198"/>
       <c r="K19" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="106" t="s">
         <v>85</v>
       </c>
@@ -5444,7 +5454,7 @@
       <c r="F20" s="106"/>
       <c r="G20" s="106"/>
       <c r="H20" s="106"/>
-      <c r="I20" s="198">
+      <c r="I20" s="193">
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="J20" s="151">
@@ -5456,7 +5466,7 @@
         <v>1718.548237452153</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="106" t="s">
         <v>85</v>
       </c>
@@ -5468,7 +5478,7 @@
       <c r="F21" s="106"/>
       <c r="G21" s="106"/>
       <c r="H21" s="106"/>
-      <c r="I21" s="198">
+      <c r="I21" s="193">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J21" s="151">
@@ -5480,7 +5490,7 @@
         <v>1473.0413463875598</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="106" t="s">
         <v>85</v>
       </c>
@@ -5492,7 +5502,7 @@
       <c r="F22" s="106"/>
       <c r="G22" s="106"/>
       <c r="H22" s="106"/>
-      <c r="I22" s="198">
+      <c r="I22" s="193">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J22" s="151">
@@ -5504,7 +5514,7 @@
         <v>1473.0413463875598</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="106" t="s">
         <v>85</v>
       </c>
@@ -5516,7 +5526,7 @@
       <c r="F23" s="106"/>
       <c r="G23" s="106"/>
       <c r="H23" s="106"/>
-      <c r="I23" s="198">
+      <c r="I23" s="193">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J23" s="151">
@@ -5528,7 +5538,7 @@
         <v>1473.0413463875598</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="106" t="s">
         <v>85</v>
       </c>
@@ -5540,7 +5550,7 @@
       <c r="F24" s="106"/>
       <c r="G24" s="106"/>
       <c r="H24" s="106"/>
-      <c r="I24" s="198">
+      <c r="I24" s="193">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J24" s="151">
@@ -5552,7 +5562,7 @@
         <v>1473.0413463875598</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="106" t="s">
         <v>85</v>
       </c>
@@ -5564,7 +5574,7 @@
       <c r="F25" s="106"/>
       <c r="G25" s="106"/>
       <c r="H25" s="106"/>
-      <c r="I25" s="198">
+      <c r="I25" s="193">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="J25" s="151">
@@ -5576,7 +5586,7 @@
         <v>736.52067319377988</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="106" t="s">
         <v>85</v>
       </c>
@@ -5588,7 +5598,7 @@
       <c r="F26" s="106"/>
       <c r="G26" s="106"/>
       <c r="H26" s="106"/>
-      <c r="I26" s="198">
+      <c r="I26" s="193">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="J26" s="151">
@@ -5600,7 +5610,7 @@
         <v>736.52067319377988</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="106" t="s">
         <v>85</v>
       </c>
@@ -5612,7 +5622,7 @@
       <c r="F27" s="106"/>
       <c r="G27" s="106"/>
       <c r="H27" s="106"/>
-      <c r="I27" s="198">
+      <c r="I27" s="193">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="J27" s="151">
@@ -5624,7 +5634,7 @@
         <v>736.52067319377988</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="109"/>
       <c r="C28" s="109"/>
       <c r="D28" s="109"/>
@@ -5633,7 +5643,7 @@
       <c r="G28" s="109"/>
       <c r="H28" s="109"/>
       <c r="I28" s="107" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="J28" s="151">
         <f>SUM(J20:J27)</f>
@@ -5644,21 +5654,21 @@
         <v>9820.2756425837306</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F29" s="109"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="D30" s="257" t="s">
-        <v>152</v>
-      </c>
-      <c r="E30" s="258"/>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D30" s="250" t="s">
+        <v>135</v>
+      </c>
+      <c r="E30" s="251"/>
       <c r="F30" s="108">
         <v>1254</v>
       </c>
       <c r="G30" s="107" t="s">
-        <v>153</v>
-      </c>
-      <c r="H30" s="205">
+        <v>136</v>
+      </c>
+      <c r="H30" s="200">
         <v>442653.69</v>
       </c>
       <c r="K30" s="150">
@@ -5666,94 +5676,94 @@
         <v>442653.68999999994</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D31" s="109"/>
       <c r="E31" s="109"/>
       <c r="F31" s="110"/>
-      <c r="H31" s="206"/>
-      <c r="K31" s="207"/>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="D32" s="257" t="s">
-        <v>154</v>
-      </c>
-      <c r="E32" s="258"/>
-      <c r="F32" s="201">
+      <c r="H31" s="201"/>
+      <c r="K31" s="202"/>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D32" s="250" t="s">
+        <v>137</v>
+      </c>
+      <c r="E32" s="251"/>
+      <c r="F32" s="196">
         <f>SUM(F3:F17)</f>
         <v>558.5</v>
       </c>
       <c r="G32" s="107" t="s">
-        <v>150</v>
-      </c>
-      <c r="H32" s="208">
+        <v>133</v>
+      </c>
+      <c r="H32" s="203">
         <f>H30-H34</f>
         <v>197146.79893540672</v>
       </c>
-      <c r="K32" s="207"/>
-    </row>
-    <row r="33" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D33" s="257"/>
-      <c r="E33" s="258"/>
+      <c r="K32" s="202"/>
+    </row>
+    <row r="33" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D33" s="250"/>
+      <c r="E33" s="251"/>
       <c r="F33" s="108"/>
       <c r="G33" s="107"/>
-      <c r="H33" s="209"/>
-      <c r="K33" s="207"/>
-    </row>
-    <row r="34" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D34" s="257" t="s">
-        <v>155</v>
-      </c>
-      <c r="E34" s="258"/>
-      <c r="F34" s="201">
+      <c r="H33" s="204"/>
+      <c r="K33" s="202"/>
+    </row>
+    <row r="34" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D34" s="250" t="s">
+        <v>138</v>
+      </c>
+      <c r="E34" s="251"/>
+      <c r="F34" s="196">
         <f>F30-F32</f>
         <v>695.5</v>
       </c>
       <c r="G34" s="107" t="s">
-        <v>156</v>
-      </c>
-      <c r="H34" s="208">
+        <v>139</v>
+      </c>
+      <c r="H34" s="203">
         <f>(H30*F34)/F30</f>
         <v>245506.89106459328</v>
       </c>
       <c r="K34" s="1"/>
     </row>
-    <row r="36" spans="4:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="F36" s="253" t="s">
-        <v>157</v>
-      </c>
-      <c r="G36" s="254"/>
-      <c r="H36" s="210">
+    <row r="36" spans="4:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F36" s="246" t="s">
+        <v>140</v>
+      </c>
+      <c r="G36" s="247"/>
+      <c r="H36" s="205">
         <f>H32+H33+H34</f>
         <v>442653.69</v>
       </c>
     </row>
-    <row r="38" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D38" s="255" t="s">
-        <v>158</v>
-      </c>
-      <c r="E38" s="256"/>
-      <c r="F38" s="211">
+    <row r="38" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D38" s="248" t="s">
+        <v>141</v>
+      </c>
+      <c r="E38" s="249"/>
+      <c r="F38" s="206">
         <v>46164</v>
       </c>
-      <c r="G38" s="211">
+      <c r="G38" s="206">
         <v>46197</v>
       </c>
-      <c r="H38" s="212" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="39" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D39" s="255" t="s">
-        <v>160</v>
-      </c>
-      <c r="E39" s="256"/>
-      <c r="F39" s="212">
+      <c r="H38" s="207" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="39" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D39" s="248" t="s">
+        <v>143</v>
+      </c>
+      <c r="E39" s="249"/>
+      <c r="F39" s="207">
         <v>274268</v>
       </c>
-      <c r="G39" s="212">
+      <c r="G39" s="207">
         <v>275522</v>
       </c>
-      <c r="H39" s="212">
+      <c r="H39" s="207">
         <f>G39-F39</f>
         <v>1254</v>
       </c>

--- a/2026/SALTA 1167/Agosto/SALTA1167-Agosto.xlsx
+++ b/2026/SALTA 1167/Agosto/SALTA1167-Agosto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9B951C-E2CA-4EDC-ACD3-0CC4DA347267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29C2953-C4A2-4A21-9AEE-551C82D36185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$95</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$96</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="159">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -510,6 +510,9 @@
   </si>
   <si>
     <t>SALDO A 30/08</t>
+  </si>
+  <si>
+    <t>Bonificado</t>
   </si>
 </sst>
 </file>
@@ -529,7 +532,7 @@
     <numFmt numFmtId="170" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
     <numFmt numFmtId="171" formatCode="0.0"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -749,13 +752,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -1193,7 +1189,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="259">
+  <cellXfs count="253">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1466,19 +1462,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1559,6 +1542,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1568,108 +1575,84 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1688,17 +1671,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="17" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="29" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="29" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2098,7 +2086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M99"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -2133,12 +2121,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13"/>
-      <c r="B3" s="216" t="s">
+      <c r="B3" s="204" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="216"/>
-      <c r="D3" s="216"/>
-      <c r="E3" s="217"/>
+      <c r="C3" s="204"/>
+      <c r="D3" s="204"/>
+      <c r="E3" s="205"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
@@ -2176,49 +2164,49 @@
       <c r="E6" s="18"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="219" t="s">
+      <c r="B8" s="207" t="s">
         <v>145</v>
       </c>
-      <c r="C8" s="219"/>
+      <c r="C8" s="207"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="219"/>
-      <c r="C9" s="219"/>
+      <c r="B9" s="207"/>
+      <c r="C9" s="207"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="219"/>
-      <c r="C10" s="219"/>
+      <c r="B10" s="207"/>
+      <c r="C10" s="207"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="218" t="s">
+      <c r="A13" s="206" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="218"/>
-      <c r="C13" s="218"/>
-      <c r="D13" s="218"/>
-      <c r="E13" s="218"/>
+      <c r="B13" s="206"/>
+      <c r="C13" s="206"/>
+      <c r="D13" s="206"/>
+      <c r="E13" s="206"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="218"/>
-      <c r="B14" s="218"/>
-      <c r="C14" s="218"/>
-      <c r="D14" s="218"/>
-      <c r="E14" s="218"/>
+      <c r="A14" s="206"/>
+      <c r="B14" s="206"/>
+      <c r="C14" s="206"/>
+      <c r="D14" s="206"/>
+      <c r="E14" s="206"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="218"/>
-      <c r="B15" s="218"/>
-      <c r="C15" s="218"/>
-      <c r="D15" s="218"/>
-      <c r="E15" s="218"/>
+      <c r="A15" s="206"/>
+      <c r="B15" s="206"/>
+      <c r="C15" s="206"/>
+      <c r="D15" s="206"/>
+      <c r="E15" s="206"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="218"/>
-      <c r="B16" s="218"/>
-      <c r="C16" s="218"/>
-      <c r="D16" s="218"/>
-      <c r="E16" s="218"/>
+      <c r="A16" s="206"/>
+      <c r="B16" s="206"/>
+      <c r="C16" s="206"/>
+      <c r="D16" s="206"/>
+      <c r="E16" s="206"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2244,12 +2232,12 @@
       <c r="E21" s="93"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="212" t="s">
+      <c r="A22" s="202" t="s">
         <v>112</v>
       </c>
-      <c r="B22" s="213"/>
+      <c r="B22" s="203"/>
       <c r="C22" s="152"/>
-      <c r="D22" s="253">
+      <c r="D22" s="244">
         <v>510846.85</v>
       </c>
       <c r="E22" s="146" t="s">
@@ -2258,10 +2246,10 @@
       <c r="H22" s="82"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="212"/>
-      <c r="B23" s="213"/>
+      <c r="A23" s="202"/>
+      <c r="B23" s="203"/>
       <c r="C23" s="152"/>
-      <c r="D23" s="172"/>
+      <c r="D23" s="244"/>
       <c r="E23" s="94"/>
       <c r="H23" s="82"/>
     </row>
@@ -2271,7 +2259,7 @@
       </c>
       <c r="B24" s="153"/>
       <c r="C24" s="153"/>
-      <c r="D24" s="173"/>
+      <c r="D24" s="245"/>
       <c r="E24" s="137">
         <f>SUM(D22:D23)</f>
         <v>510846.85</v>
@@ -2283,16 +2271,16 @@
       </c>
       <c r="B25" s="153"/>
       <c r="C25" s="153"/>
-      <c r="D25" s="174"/>
+      <c r="D25" s="246"/>
       <c r="E25" s="138"/>
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="212" t="s">
+      <c r="A26" s="202" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="213"/>
+      <c r="B26" s="203"/>
       <c r="C26" s="155"/>
-      <c r="D26" s="254">
+      <c r="D26" s="247">
         <v>79873.05</v>
       </c>
       <c r="E26" s="96" t="s">
@@ -2305,7 +2293,7 @@
       </c>
       <c r="B27" s="153"/>
       <c r="C27" s="153"/>
-      <c r="D27" s="173"/>
+      <c r="D27" s="245"/>
       <c r="E27" s="104">
         <f>SUM(D26:D26)</f>
         <v>79873.05</v>
@@ -2317,7 +2305,7 @@
       </c>
       <c r="B28" s="156"/>
       <c r="C28" s="156"/>
-      <c r="D28" s="175"/>
+      <c r="D28" s="248"/>
       <c r="E28" s="139"/>
     </row>
     <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2326,613 +2314,629 @@
       </c>
       <c r="B29" s="65"/>
       <c r="C29" s="65"/>
-      <c r="D29" s="252">
+      <c r="D29" s="95">
         <v>14396.25</v>
       </c>
       <c r="E29" s="96" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="65" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B30" s="65"/>
       <c r="C30" s="65"/>
-      <c r="D30" s="252">
-        <v>6644.39</v>
-      </c>
-      <c r="E30" s="146" t="str">
-        <f>E31</f>
-        <v>Transf 04/08</v>
+      <c r="D30" s="95">
+        <v>265234.65000000002</v>
+      </c>
+      <c r="E30" s="96" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="157"/>
+      <c r="B31" s="65"/>
       <c r="C31" s="65"/>
-      <c r="D31" s="252">
+      <c r="D31" s="95">
+        <v>6644.39</v>
+      </c>
+      <c r="E31" s="146" t="str">
+        <f>E32</f>
+        <v>Transf 04/08</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" s="157"/>
+      <c r="C32" s="65"/>
+      <c r="D32" s="95">
         <v>482119.34</v>
       </c>
-      <c r="E31" s="96" t="s">
+      <c r="E32" s="96" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="214" t="s">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="200" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="215"/>
-      <c r="C32" s="65"/>
-      <c r="D32" s="252">
+      <c r="B33" s="201"/>
+      <c r="C33" s="65"/>
+      <c r="D33" s="95">
         <v>872785.72</v>
       </c>
-      <c r="E32" s="96" t="s">
+      <c r="E33" s="96" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="158" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="158" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="159"/>
-      <c r="C33" s="65"/>
-      <c r="D33" s="252">
+      <c r="B34" s="159"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="95">
         <v>28704.880000000001</v>
       </c>
-      <c r="E33" s="96" t="s">
+      <c r="E34" s="96" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="153" t="s">
+    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="153" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="153"/>
-      <c r="C34" s="153"/>
-      <c r="D34" s="177"/>
-      <c r="E34" s="140">
-        <f>SUM(D29:D33)</f>
-        <v>1404650.5799999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="154"/>
       <c r="B35" s="153"/>
       <c r="C35" s="153"/>
-      <c r="D35" s="173"/>
-      <c r="E35" s="141"/>
-    </row>
-    <row r="36" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="212" t="s">
+      <c r="D35" s="249"/>
+      <c r="E35" s="140">
+        <f>SUM(D29:D34)</f>
+        <v>1669885.23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="154"/>
+      <c r="B36" s="153"/>
+      <c r="C36" s="153"/>
+      <c r="D36" s="245"/>
+      <c r="E36" s="141"/>
+    </row>
+    <row r="37" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="202" t="s">
         <v>114</v>
       </c>
-      <c r="B36" s="213"/>
-      <c r="C36" s="65"/>
-      <c r="D36" s="252">
+      <c r="B37" s="203"/>
+      <c r="C37" s="65"/>
+      <c r="D37" s="95">
         <v>82000</v>
       </c>
-      <c r="E36" s="96" t="s">
+      <c r="E37" s="96" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="160" t="s">
+    <row r="38" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="160" t="s">
         <v>152</v>
       </c>
-      <c r="B37" s="161"/>
-      <c r="C37" s="65"/>
-      <c r="D37" s="252">
+      <c r="B38" s="161"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="95">
         <f>199530</f>
         <v>199530</v>
       </c>
-      <c r="E37" s="96" t="s">
+      <c r="E38" s="96" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="212" t="s">
+    <row r="39" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="202" t="s">
         <v>154</v>
       </c>
-      <c r="B38" s="213"/>
-      <c r="C38" s="65"/>
-      <c r="D38" s="256">
+      <c r="B39" s="203"/>
+      <c r="C39" s="65"/>
+      <c r="D39" s="68">
         <v>157988.29</v>
       </c>
-      <c r="E38" s="96"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="153" t="s">
+      <c r="E39" s="96"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="153" t="s">
         <v>6</v>
-      </c>
-      <c r="B39" s="154"/>
-      <c r="C39" s="154"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="104">
-        <f>SUM(D36:D38)</f>
-        <v>439518.29000000004</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="154" t="s">
-        <v>11</v>
       </c>
       <c r="B40" s="154"/>
       <c r="C40" s="154"/>
-      <c r="D40" s="178"/>
-      <c r="E40" s="142"/>
-    </row>
-    <row r="41" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="212" t="s">
+      <c r="D40" s="154"/>
+      <c r="E40" s="104">
+        <f>SUM(D37:D39)</f>
+        <v>439518.29000000004</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="154" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" s="154"/>
+      <c r="C41" s="154"/>
+      <c r="D41" s="98"/>
+      <c r="E41" s="142"/>
+    </row>
+    <row r="42" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="202" t="s">
         <v>147</v>
       </c>
-      <c r="B41" s="213"/>
-      <c r="C41" s="152"/>
-      <c r="D41" s="255">
+      <c r="B42" s="203"/>
+      <c r="C42" s="152"/>
+      <c r="D42" s="250">
         <v>190000</v>
       </c>
-      <c r="E41" s="143" t="s">
+      <c r="E42" s="143" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="153" t="s">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="153" t="s">
         <v>9</v>
       </c>
-      <c r="B42" s="153"/>
-      <c r="C42" s="153"/>
-      <c r="D42" s="173"/>
-      <c r="E42" s="137">
-        <f>SUM(D41:D41)</f>
+      <c r="B43" s="153"/>
+      <c r="C43" s="153"/>
+      <c r="D43" s="245"/>
+      <c r="E43" s="137">
+        <f>SUM(D42:D42)</f>
         <v>190000</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="154" t="s">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="154" t="s">
         <v>8</v>
       </c>
-      <c r="B43" s="162"/>
-      <c r="C43" s="153"/>
-      <c r="D43" s="179"/>
-      <c r="E43" s="104"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="65" t="s">
-        <v>156</v>
-      </c>
-      <c r="B44" s="65"/>
-      <c r="C44" s="65"/>
-      <c r="D44" s="252"/>
-      <c r="E44" s="144"/>
+      <c r="B44" s="162"/>
+      <c r="C44" s="153"/>
+      <c r="D44" s="251"/>
+      <c r="E44" s="104"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="B45" s="65" t="s">
+        <v>158</v>
+      </c>
+      <c r="C45" s="65"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="144"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="65" t="s">
         <v>113</v>
       </c>
-      <c r="B45" s="65"/>
-      <c r="C45" s="65"/>
-      <c r="D45" s="176">
-        <v>44926.11</v>
-      </c>
-      <c r="E45" s="145"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="163" t="s">
+      <c r="B46" s="65"/>
+      <c r="C46" s="65"/>
+      <c r="D46" s="95">
+        <f>374.4+864+181.44+1597.68+33590.8</f>
+        <v>36608.320000000007</v>
+      </c>
+      <c r="E46" s="145"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="163" t="s">
         <v>9</v>
       </c>
-      <c r="B46" s="163"/>
-      <c r="C46" s="163"/>
-      <c r="D46" s="180"/>
-      <c r="E46" s="104">
-        <f>SUM(D44:D45)</f>
-        <v>44926.11</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="65"/>
-      <c r="B47" s="65"/>
-      <c r="C47" s="65"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="70"/>
+      <c r="B47" s="163"/>
+      <c r="C47" s="163"/>
+      <c r="D47" s="252"/>
+      <c r="E47" s="104">
+        <f>SUM(D45:D46)</f>
+        <v>36608.320000000007</v>
+      </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="164" t="s">
+      <c r="A48" s="65"/>
+      <c r="B48" s="65"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="70"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="164" t="s">
         <v>97</v>
       </c>
-      <c r="B48" s="164"/>
-      <c r="C48" s="164"/>
-      <c r="D48" s="71"/>
-      <c r="E48" s="105"/>
-    </row>
-    <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="165"/>
-      <c r="B49" s="72"/>
-      <c r="C49" s="72"/>
-      <c r="D49" s="72"/>
-      <c r="E49" s="73"/>
-      <c r="F49" s="27"/>
+      <c r="B49" s="164"/>
+      <c r="C49" s="164"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="105"/>
     </row>
     <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="166" t="s">
+      <c r="A50" s="165"/>
+      <c r="B50" s="72"/>
+      <c r="C50" s="72"/>
+      <c r="D50" s="72"/>
+      <c r="E50" s="73"/>
+      <c r="F50" s="27"/>
+    </row>
+    <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="166" t="s">
         <v>93</v>
       </c>
-      <c r="B50" s="167"/>
-      <c r="C50" s="74"/>
-      <c r="D50" s="74"/>
-      <c r="E50" s="75">
-        <f>(SUM(E21:E48))</f>
-        <v>2669814.88</v>
-      </c>
-      <c r="F50" s="92"/>
-      <c r="G50" s="27"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="72"/>
-      <c r="B51" s="72"/>
-      <c r="C51" s="72"/>
-      <c r="D51" s="72"/>
-      <c r="E51" s="72"/>
-    </row>
-    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="167"/>
+      <c r="C51" s="74"/>
+      <c r="D51" s="74"/>
+      <c r="E51" s="75">
+        <f>(SUM(E21:E49))</f>
+        <v>2926731.7399999998</v>
+      </c>
+      <c r="F51" s="92"/>
+      <c r="G51" s="27"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="72"/>
       <c r="B52" s="72"/>
       <c r="C52" s="72"/>
       <c r="D52" s="72"/>
       <c r="E52" s="72"/>
-      <c r="H52" s="99"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="168" t="s">
+    </row>
+    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="72"/>
+      <c r="B53" s="72"/>
+      <c r="C53" s="72"/>
+      <c r="D53" s="72"/>
+      <c r="E53" s="72"/>
+      <c r="H53" s="99"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="168" t="s">
         <v>94</v>
       </c>
-      <c r="B53" s="169"/>
-      <c r="C53" s="170"/>
-      <c r="D53" s="76"/>
-      <c r="E53" s="77"/>
-    </row>
-    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="171"/>
-      <c r="B54" s="159"/>
-      <c r="C54" s="65"/>
-      <c r="D54" s="68"/>
-      <c r="E54" s="66"/>
+      <c r="B54" s="169"/>
+      <c r="C54" s="170"/>
+      <c r="D54" s="76"/>
+      <c r="E54" s="77"/>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="211"/>
-      <c r="B55" s="211"/>
+      <c r="A55" s="171"/>
+      <c r="B55" s="159"/>
       <c r="C55" s="65"/>
-      <c r="D55" s="95"/>
+      <c r="D55" s="68"/>
       <c r="E55" s="66"/>
     </row>
-    <row r="56" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="4"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="67"/>
-      <c r="B57" s="69"/>
+    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="210"/>
+      <c r="B56" s="210"/>
+      <c r="C56" s="65"/>
+      <c r="D56" s="95"/>
+      <c r="E56" s="66"/>
+    </row>
+    <row r="57" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
       <c r="C57" s="4"/>
-      <c r="D57" s="68"/>
-      <c r="E57" s="66"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="32"/>
-      <c r="B58" s="31"/>
-      <c r="C58" s="31"/>
-      <c r="D58" s="36"/>
-      <c r="E58" s="36">
-        <f>SUM(D54:D57)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="20" t="s">
+      <c r="A58" s="67"/>
+      <c r="B58" s="69"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="68"/>
+      <c r="E58" s="66"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="32"/>
+      <c r="B59" s="31"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="36">
+        <f>SUM(D55:D58)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="B61" s="20"/>
-      <c r="C61" s="20"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="135"/>
-    </row>
-    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
+      <c r="B62" s="20"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="135"/>
+    </row>
+    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B63" s="7"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="43">
-        <f>E58+E61</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="63" t="s">
-        <v>102</v>
-      </c>
-      <c r="B65" s="64">
-        <f>E50</f>
-        <v>2669814.88</v>
-      </c>
-    </row>
+      <c r="B64" s="7"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="43">
+        <f>E59+E62</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="63" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B66" s="64">
-        <f>E50-E48</f>
-        <v>2669814.88</v>
+        <f>E51</f>
+        <v>2926731.7399999998</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="63" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B67" s="64">
-        <f>E63-E61</f>
-        <v>0</v>
+        <f>E51-E49</f>
+        <v>2926731.7399999998</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="63" t="s">
+        <v>104</v>
+      </c>
+      <c r="B68" s="64">
+        <f>E64-E62</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="B68" s="64">
-        <f>E63</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70"/>
-      <c r="B70" s="26"/>
-      <c r="C70" s="24"/>
+      <c r="B69" s="64">
+        <f>E64</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="71" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="84" t="s">
+      <c r="A71"/>
+      <c r="B71" s="26"/>
+      <c r="C71" s="24"/>
+    </row>
+    <row r="72" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="84" t="s">
         <v>106</v>
       </c>
-      <c r="B71" s="111">
+      <c r="B72" s="111">
         <v>231226.35000000335</v>
       </c>
-      <c r="C71" s="24"/>
-      <c r="D71" s="30"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="B72" s="89">
-        <f>-B66</f>
-        <v>-2669814.88</v>
-      </c>
-      <c r="E72" s="27"/>
+      <c r="C72" s="24"/>
+      <c r="D72" s="30"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="35" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="B73" s="89">
-        <f>B94</f>
-        <v>0</v>
-      </c>
+        <f>-B67</f>
+        <v>-2926731.7399999998</v>
+      </c>
+      <c r="E73" s="27"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B74" s="89">
+        <f>B95</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="B74" s="90">
-        <f>PRORRATEO!G36-B81</f>
+      <c r="B75" s="90">
+        <f>PRORRATEO!G36-B82</f>
         <v>3248082.4500000007</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="91" t="s">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="91" t="s">
         <v>155</v>
       </c>
-      <c r="B75" s="100">
+      <c r="B76" s="100">
         <v>-50000</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="87" t="s">
+    <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="87" t="s">
         <v>110</v>
       </c>
-      <c r="B76" s="88">
-        <f>SUM(B71:C75)</f>
-        <v>759493.92000000412</v>
-      </c>
-      <c r="D76" s="27"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="85"/>
-      <c r="B77" s="85"/>
+      <c r="B77" s="88">
+        <f>SUM(B72:C76)</f>
+        <v>502577.06000000425</v>
+      </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="26"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="84" t="s">
+      <c r="A78" s="85"/>
+      <c r="B78" s="85"/>
+      <c r="D78" s="27"/>
+      <c r="E78" s="26"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="84" t="s">
         <v>107</v>
       </c>
-      <c r="B78" s="111">
+      <c r="B79" s="111">
         <v>1000000</v>
       </c>
-      <c r="D78" s="26"/>
-      <c r="E78" s="27"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="B79" s="89">
-        <f>-B67</f>
-        <v>0</v>
-      </c>
-      <c r="D79" s="27"/>
+      <c r="D79" s="26"/>
       <c r="E79" s="27"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="35" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="B80" s="89">
-        <f>B102</f>
+        <f>-B68</f>
         <v>0</v>
       </c>
       <c r="D80" s="27"/>
+      <c r="E80" s="27"/>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B81" s="89">
+        <f>B103</f>
+        <v>0</v>
+      </c>
+      <c r="D81" s="27"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="B81" s="90">
-        <v>0</v>
-      </c>
-      <c r="D81" s="136"/>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A82" s="91" t="s">
+      <c r="B82" s="90">
+        <v>0</v>
+      </c>
+      <c r="D82" s="136"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="B82" s="100"/>
-      <c r="D82" s="27"/>
-      <c r="E82" s="27"/>
-      <c r="F82" s="26"/>
-    </row>
-    <row r="83" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="87" t="s">
+      <c r="B83" s="100"/>
+      <c r="D83" s="27"/>
+      <c r="E83" s="27"/>
+      <c r="F83" s="26"/>
+    </row>
+    <row r="84" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="87" t="s">
         <v>111</v>
       </c>
-      <c r="B83" s="88">
-        <f>SUM(B78:C82)</f>
+      <c r="B84" s="88">
+        <f>SUM(B79:C83)</f>
         <v>1000000</v>
       </c>
-      <c r="D83" s="27"/>
-      <c r="F83" s="27"/>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A84" s="85"/>
-      <c r="B84" s="85"/>
+      <c r="D84" s="27"/>
+      <c r="F84" s="27"/>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="85"/>
       <c r="B85" s="85"/>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A86" s="84" t="s">
+      <c r="A86" s="85"/>
+      <c r="B86" s="85"/>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" s="84" t="s">
         <v>124</v>
       </c>
-      <c r="B86" s="111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A87" s="35" t="s">
+      <c r="B87" s="111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="B87" s="89">
+      <c r="B88" s="89">
         <v>1025063.51</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="87" t="s">
+    <row r="89" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="87" t="s">
         <v>157</v>
       </c>
-      <c r="B88" s="88">
+      <c r="B89" s="88">
         <v>1054849.6000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" s="210" t="s">
+    <row r="90" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" s="209" t="s">
         <v>18</v>
       </c>
-      <c r="B90" s="210"/>
-      <c r="C90" s="210"/>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A91" s="210"/>
-      <c r="B91" s="210"/>
-      <c r="C91" s="210"/>
-    </row>
-    <row r="92" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="79"/>
-      <c r="B92" s="23"/>
-      <c r="C92" s="23">
+      <c r="B91" s="209"/>
+      <c r="C91" s="209"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" s="209"/>
+      <c r="B92" s="209"/>
+      <c r="C92" s="209"/>
+    </row>
+    <row r="93" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="79"/>
+      <c r="B93" s="23"/>
+      <c r="C93" s="23">
         <v>40000</v>
       </c>
-      <c r="E92" s="92"/>
-    </row>
-    <row r="93" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="79"/>
-      <c r="B93" s="81"/>
-      <c r="C93" s="78"/>
-      <c r="D93" s="92"/>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A94" s="28" t="s">
+      <c r="E93" s="92"/>
+    </row>
+    <row r="94" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="79"/>
+      <c r="B94" s="81"/>
+      <c r="C94" s="78"/>
+      <c r="D94" s="92"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B94" s="80">
-        <f>SUM(B92:B93)</f>
-        <v>0</v>
-      </c>
-      <c r="C94" s="29"/>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M95" s="5"/>
-    </row>
-    <row r="96" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="209"/>
-      <c r="B96" s="209"/>
-      <c r="C96" s="209"/>
-      <c r="D96" s="209"/>
-      <c r="E96" s="209"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="209"/>
-      <c r="B97" s="209"/>
-      <c r="C97" s="209"/>
-      <c r="D97" s="209"/>
-      <c r="E97" s="209"/>
+      <c r="B95" s="80">
+        <f>SUM(B93:B94)</f>
+        <v>0</v>
+      </c>
+      <c r="C95" s="29"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M96" s="5"/>
+    </row>
+    <row r="97" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="208"/>
+      <c r="B97" s="208"/>
+      <c r="C97" s="208"/>
+      <c r="D97" s="208"/>
+      <c r="E97" s="208"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="209"/>
-      <c r="B98" s="209"/>
-      <c r="C98" s="209"/>
-      <c r="D98" s="209"/>
-      <c r="E98" s="209"/>
+      <c r="A98" s="208"/>
+      <c r="B98" s="208"/>
+      <c r="C98" s="208"/>
+      <c r="D98" s="208"/>
+      <c r="E98" s="208"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="209"/>
-      <c r="B99" s="209"/>
-      <c r="C99" s="209"/>
-      <c r="D99" s="209"/>
-      <c r="E99" s="209"/>
+      <c r="A99" s="208"/>
+      <c r="B99" s="208"/>
+      <c r="C99" s="208"/>
+      <c r="D99" s="208"/>
+      <c r="E99" s="208"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="208"/>
+      <c r="B100" s="208"/>
+      <c r="C100" s="208"/>
+      <c r="D100" s="208"/>
+      <c r="E100" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A97:E100"/>
+    <mergeCell ref="A91:C92"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A33:B33"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A96:E99"/>
-    <mergeCell ref="A90:C91"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A41:B41"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2970,16 +2974,16 @@
       <c r="B1" s="113"/>
       <c r="C1" s="114"/>
       <c r="D1" s="114"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="225"/>
-      <c r="G1" s="225"/>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
-      <c r="J1" s="225"/>
-      <c r="K1" s="225"/>
-      <c r="L1" s="225"/>
-      <c r="M1" s="225"/>
-      <c r="N1" s="225"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="211"/>
+      <c r="M1" s="211"/>
+      <c r="N1" s="211"/>
       <c r="O1" s="113"/>
       <c r="P1" s="115"/>
     </row>
@@ -3030,209 +3034,209 @@
       <c r="Q3" s="19"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="232" t="s">
+      <c r="A4" s="222" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="233"/>
-      <c r="C4" s="233"/>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
-      <c r="H4" s="233"/>
-      <c r="I4" s="233"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="233"/>
-      <c r="L4" s="233"/>
-      <c r="M4" s="233"/>
-      <c r="N4" s="233"/>
-      <c r="O4" s="233"/>
-      <c r="P4" s="234"/>
+      <c r="B4" s="223"/>
+      <c r="C4" s="223"/>
+      <c r="D4" s="223"/>
+      <c r="E4" s="223"/>
+      <c r="F4" s="223"/>
+      <c r="G4" s="223"/>
+      <c r="H4" s="223"/>
+      <c r="I4" s="223"/>
+      <c r="J4" s="223"/>
+      <c r="K4" s="223"/>
+      <c r="L4" s="223"/>
+      <c r="M4" s="223"/>
+      <c r="N4" s="223"/>
+      <c r="O4" s="223"/>
+      <c r="P4" s="224"/>
       <c r="Q4" s="19"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="235"/>
-      <c r="B5" s="236"/>
-      <c r="C5" s="236"/>
-      <c r="D5" s="236"/>
-      <c r="E5" s="236"/>
-      <c r="F5" s="236"/>
-      <c r="G5" s="236"/>
-      <c r="H5" s="236"/>
-      <c r="I5" s="236"/>
-      <c r="J5" s="236"/>
-      <c r="K5" s="236"/>
-      <c r="L5" s="236"/>
-      <c r="M5" s="236"/>
-      <c r="N5" s="236"/>
-      <c r="O5" s="236"/>
-      <c r="P5" s="237"/>
+      <c r="A5" s="225"/>
+      <c r="B5" s="226"/>
+      <c r="C5" s="226"/>
+      <c r="D5" s="226"/>
+      <c r="E5" s="226"/>
+      <c r="F5" s="226"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="226"/>
+      <c r="J5" s="226"/>
+      <c r="K5" s="226"/>
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="226"/>
+      <c r="O5" s="226"/>
+      <c r="P5" s="227"/>
       <c r="Q5" s="19"/>
     </row>
     <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="235"/>
-      <c r="B6" s="236"/>
-      <c r="C6" s="236"/>
-      <c r="D6" s="236"/>
-      <c r="E6" s="236"/>
-      <c r="F6" s="236"/>
-      <c r="G6" s="236"/>
-      <c r="H6" s="236"/>
-      <c r="I6" s="236"/>
-      <c r="J6" s="236"/>
-      <c r="K6" s="236"/>
-      <c r="L6" s="236"/>
-      <c r="M6" s="236"/>
-      <c r="N6" s="236"/>
-      <c r="O6" s="236"/>
-      <c r="P6" s="237"/>
+      <c r="A6" s="225"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
+      <c r="D6" s="226"/>
+      <c r="E6" s="226"/>
+      <c r="F6" s="226"/>
+      <c r="G6" s="226"/>
+      <c r="H6" s="226"/>
+      <c r="I6" s="226"/>
+      <c r="J6" s="226"/>
+      <c r="K6" s="226"/>
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="226"/>
+      <c r="O6" s="226"/>
+      <c r="P6" s="227"/>
       <c r="Q6" s="19"/>
     </row>
     <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="235"/>
-      <c r="B7" s="236"/>
-      <c r="C7" s="236"/>
-      <c r="D7" s="236"/>
-      <c r="E7" s="236"/>
-      <c r="F7" s="236"/>
-      <c r="G7" s="236"/>
-      <c r="H7" s="236"/>
-      <c r="I7" s="236"/>
-      <c r="J7" s="236"/>
-      <c r="K7" s="236"/>
-      <c r="L7" s="236"/>
-      <c r="M7" s="236"/>
-      <c r="N7" s="236"/>
-      <c r="O7" s="236"/>
-      <c r="P7" s="237"/>
+      <c r="A7" s="225"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
+      <c r="D7" s="226"/>
+      <c r="E7" s="226"/>
+      <c r="F7" s="226"/>
+      <c r="G7" s="226"/>
+      <c r="H7" s="226"/>
+      <c r="I7" s="226"/>
+      <c r="J7" s="226"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="226"/>
+      <c r="O7" s="226"/>
+      <c r="P7" s="227"/>
       <c r="Q7" s="19"/>
     </row>
     <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="238"/>
-      <c r="B8" s="239"/>
-      <c r="C8" s="239"/>
-      <c r="D8" s="239"/>
-      <c r="E8" s="239"/>
-      <c r="F8" s="239"/>
-      <c r="G8" s="239"/>
-      <c r="H8" s="239"/>
-      <c r="I8" s="239"/>
-      <c r="J8" s="239"/>
-      <c r="K8" s="239"/>
-      <c r="L8" s="239"/>
-      <c r="M8" s="239"/>
-      <c r="N8" s="239"/>
-      <c r="O8" s="239"/>
-      <c r="P8" s="240"/>
+      <c r="A8" s="228"/>
+      <c r="B8" s="229"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="229"/>
+      <c r="E8" s="229"/>
+      <c r="F8" s="229"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="229"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="229"/>
+      <c r="L8" s="229"/>
+      <c r="M8" s="229"/>
+      <c r="N8" s="229"/>
+      <c r="O8" s="229"/>
+      <c r="P8" s="230"/>
     </row>
     <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="243" t="s">
+      <c r="A9" s="233" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="244"/>
-      <c r="C9" s="244"/>
-      <c r="D9" s="244"/>
-      <c r="E9" s="244"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
-      <c r="H9" s="244"/>
-      <c r="I9" s="244"/>
-      <c r="J9" s="244"/>
-      <c r="K9" s="244"/>
-      <c r="L9" s="244"/>
-      <c r="M9" s="244"/>
-      <c r="N9" s="244"/>
-      <c r="O9" s="244"/>
-      <c r="P9" s="244"/>
+      <c r="B9" s="234"/>
+      <c r="C9" s="234"/>
+      <c r="D9" s="234"/>
+      <c r="E9" s="234"/>
+      <c r="F9" s="234"/>
+      <c r="G9" s="234"/>
+      <c r="H9" s="234"/>
+      <c r="I9" s="234"/>
+      <c r="J9" s="234"/>
+      <c r="K9" s="234"/>
+      <c r="L9" s="234"/>
+      <c r="M9" s="234"/>
+      <c r="N9" s="234"/>
+      <c r="O9" s="234"/>
+      <c r="P9" s="234"/>
     </row>
     <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="245" t="s">
+      <c r="A10" s="235" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="245"/>
-      <c r="C10" s="245"/>
-      <c r="D10" s="245"/>
-      <c r="E10" s="245"/>
-      <c r="F10" s="245"/>
-      <c r="G10" s="245"/>
-      <c r="H10" s="245"/>
-      <c r="I10" s="245"/>
-      <c r="J10" s="245"/>
-      <c r="K10" s="245"/>
-      <c r="L10" s="245"/>
-      <c r="M10" s="245"/>
-      <c r="N10" s="245"/>
-      <c r="O10" s="245"/>
-      <c r="P10" s="245"/>
+      <c r="B10" s="235"/>
+      <c r="C10" s="235"/>
+      <c r="D10" s="235"/>
+      <c r="E10" s="235"/>
+      <c r="F10" s="235"/>
+      <c r="G10" s="235"/>
+      <c r="H10" s="235"/>
+      <c r="I10" s="235"/>
+      <c r="J10" s="235"/>
+      <c r="K10" s="235"/>
+      <c r="L10" s="235"/>
+      <c r="M10" s="235"/>
+      <c r="N10" s="235"/>
+      <c r="O10" s="235"/>
+      <c r="P10" s="235"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="220" t="s">
+      <c r="A11" s="216" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="101"/>
-      <c r="C11" s="220" t="s">
+      <c r="C11" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="220" t="s">
+      <c r="D11" s="216" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="220" t="s">
+      <c r="E11" s="216" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="223" t="s">
+      <c r="F11" s="212" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="220" t="s">
+      <c r="G11" s="216" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="228" t="s">
+      <c r="H11" s="218" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="223" t="s">
+      <c r="I11" s="212" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="223" t="s">
+      <c r="J11" s="212" t="s">
         <v>91</v>
       </c>
-      <c r="K11" s="230" t="s">
+      <c r="K11" s="220" t="s">
         <v>92</v>
       </c>
-      <c r="L11" s="223" t="s">
+      <c r="L11" s="212" t="s">
         <v>78</v>
       </c>
-      <c r="M11" s="223" t="s">
+      <c r="M11" s="212" t="s">
         <v>123</v>
       </c>
       <c r="N11" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="226" t="s">
+      <c r="O11" s="214" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="241" t="s">
+      <c r="P11" s="231" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="222"/>
+      <c r="A12" s="217"/>
       <c r="B12" s="102"/>
-      <c r="C12" s="222"/>
-      <c r="D12" s="221"/>
-      <c r="E12" s="222"/>
-      <c r="F12" s="224"/>
-      <c r="G12" s="222"/>
-      <c r="H12" s="229"/>
-      <c r="I12" s="224"/>
-      <c r="J12" s="224"/>
-      <c r="K12" s="231"/>
-      <c r="L12" s="224"/>
-      <c r="M12" s="224"/>
+      <c r="C12" s="217"/>
+      <c r="D12" s="236"/>
+      <c r="E12" s="217"/>
+      <c r="F12" s="213"/>
+      <c r="G12" s="217"/>
+      <c r="H12" s="219"/>
+      <c r="I12" s="213"/>
+      <c r="J12" s="213"/>
+      <c r="K12" s="221"/>
+      <c r="L12" s="213"/>
+      <c r="M12" s="213"/>
       <c r="N12" s="37" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="O12" s="227"/>
-      <c r="P12" s="242"/>
+      <c r="O12" s="215"/>
+      <c r="P12" s="232"/>
     </row>
     <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="40">
@@ -3251,7 +3255,7 @@
       <c r="F13" s="49">
         <v>364055.01</v>
       </c>
-      <c r="G13" s="257">
+      <c r="G13" s="50">
         <f>400461-G29-G30</f>
         <v>364054.65</v>
       </c>
@@ -3309,7 +3313,7 @@
       <c r="F14" s="50">
         <v>326822.02</v>
       </c>
-      <c r="G14" s="257">
+      <c r="G14" s="50">
         <f>F14</f>
         <v>326822.02</v>
       </c>
@@ -3333,18 +3337,20 @@
         <f>EDESUR!K4</f>
         <v>149105.45982222489</v>
       </c>
-      <c r="M14" s="149"/>
+      <c r="M14" s="149">
+        <v>10000</v>
+      </c>
       <c r="N14" s="133">
         <f t="shared" ref="N14:N35" si="4">ROUND(SUM(H14:M14),0) + Q14</f>
-        <v>327305.02</v>
+        <v>337305.02</v>
       </c>
       <c r="O14" s="131">
         <f t="shared" ref="O14:O30" si="5">ROUND(N14*6% + N14,0) + Q14</f>
-        <v>346943.02</v>
+        <v>357543.02</v>
       </c>
       <c r="P14" s="132">
         <f t="shared" ref="P14:P35" si="6">ROUND(N14*3%,0) + N14</f>
-        <v>337124.02</v>
+        <v>347424.02</v>
       </c>
       <c r="Q14" s="27">
         <f>Q13+0.01</f>
@@ -3370,7 +3376,7 @@
       <c r="F15" s="49">
         <v>159057.03</v>
       </c>
-      <c r="G15" s="257">
+      <c r="G15" s="50">
         <f>F15</f>
         <v>159057.03</v>
       </c>
@@ -3431,7 +3437,7 @@
       <c r="F16" s="49">
         <v>194400.04</v>
       </c>
-      <c r="G16" s="257">
+      <c r="G16" s="50">
         <f>218435-G32</f>
         <v>200761.8</v>
       </c>
@@ -3492,7 +3498,7 @@
       <c r="F17" s="50">
         <v>194403.05</v>
       </c>
-      <c r="G17" s="257">
+      <c r="G17" s="50">
         <f>F17</f>
         <v>194403.05</v>
       </c>
@@ -3558,7 +3564,7 @@
       <c r="F18" s="49">
         <v>187201.06</v>
       </c>
-      <c r="G18" s="257">
+      <c r="G18" s="50">
         <f>F18</f>
         <v>187201.06</v>
       </c>
@@ -3619,7 +3625,7 @@
       <c r="F19" s="50">
         <v>159057.07</v>
       </c>
-      <c r="G19" s="257">
+      <c r="G19" s="50">
         <f>F19</f>
         <v>159057.07</v>
       </c>
@@ -3680,7 +3686,7 @@
       <c r="F20" s="50">
         <v>258648.08</v>
       </c>
-      <c r="G20" s="257">
+      <c r="G20" s="50">
         <f>F20</f>
         <v>258648.08</v>
       </c>
@@ -3742,7 +3748,7 @@
         <f>50000+182216.09</f>
         <v>232216.09</v>
       </c>
-      <c r="G21" s="257">
+      <c r="G21" s="50">
         <f>F21</f>
         <v>232216.09</v>
       </c>
@@ -3805,8 +3811,8 @@
       <c r="F22" s="49">
         <v>13257.1</v>
       </c>
-      <c r="G22" s="257">
-        <f>F22+RESUMEN!D38</f>
+      <c r="G22" s="50">
+        <f>F22+RESUMEN!D39</f>
         <v>171245.39</v>
       </c>
       <c r="H22" s="51">
@@ -3864,7 +3870,7 @@
       <c r="F23" s="49">
         <v>159057.10999999999</v>
       </c>
-      <c r="G23" s="257">
+      <c r="G23" s="50">
         <f>167894.33-G34</f>
         <v>159057.10999999999</v>
       </c>
@@ -3928,7 +3934,7 @@
       <c r="F24" s="49">
         <v>194403.12</v>
       </c>
-      <c r="G24" s="257">
+      <c r="G24" s="50">
         <f>F24</f>
         <v>194403.12</v>
       </c>
@@ -3989,7 +3995,7 @@
       <c r="F25" s="49">
         <v>194403.13</v>
       </c>
-      <c r="G25" s="257">
+      <c r="G25" s="50">
         <v>200235.13</v>
       </c>
       <c r="H25" s="51">
@@ -4047,8 +4053,8 @@
       <c r="F26" s="50">
         <v>159057.14000000001</v>
       </c>
-      <c r="G26" s="257">
-        <f>F26</f>
+      <c r="G26" s="50">
+        <f t="shared" ref="G26:G33" si="8">F26</f>
         <v>159057.14000000001</v>
       </c>
       <c r="H26" s="129">
@@ -4106,8 +4112,8 @@
       <c r="F27" s="49">
         <v>159057.15</v>
       </c>
-      <c r="G27" s="257">
-        <f>F27</f>
+      <c r="G27" s="50">
+        <f t="shared" si="8"/>
         <v>159057.15</v>
       </c>
       <c r="H27" s="51">
@@ -4167,8 +4173,8 @@
       <c r="F28" s="49">
         <v>24542.16</v>
       </c>
-      <c r="G28" s="257">
-        <f>F28</f>
+      <c r="G28" s="50">
+        <f t="shared" si="8"/>
         <v>24542.16</v>
       </c>
       <c r="H28" s="51">
@@ -4226,8 +4232,8 @@
       <c r="F29" s="50">
         <v>18203.169999999998</v>
       </c>
-      <c r="G29" s="257">
-        <f>F29</f>
+      <c r="G29" s="50">
+        <f t="shared" si="8"/>
         <v>18203.169999999998</v>
       </c>
       <c r="H29" s="51">
@@ -4285,8 +4291,8 @@
       <c r="F30" s="49">
         <v>18203.18</v>
       </c>
-      <c r="G30" s="257">
-        <f>F30</f>
+      <c r="G30" s="50">
+        <f t="shared" si="8"/>
         <v>18203.18</v>
       </c>
       <c r="H30" s="51">
@@ -4344,8 +4350,8 @@
       <c r="F31" s="50">
         <v>17673.189999999999</v>
       </c>
-      <c r="G31" s="257">
-        <f>F31</f>
+      <c r="G31" s="50">
+        <f t="shared" si="8"/>
         <v>17673.189999999999</v>
       </c>
       <c r="H31" s="129">
@@ -4402,8 +4408,8 @@
       <c r="F32" s="56">
         <v>17673.2</v>
       </c>
-      <c r="G32" s="257">
-        <f>F32</f>
+      <c r="G32" s="50">
+        <f t="shared" si="8"/>
         <v>17673.2</v>
       </c>
       <c r="H32" s="51">
@@ -4437,7 +4443,7 @@
         <v>18203.2</v>
       </c>
       <c r="Q32" s="27">
-        <f t="shared" ref="Q32:Q35" si="8">Q31+0.01</f>
+        <f t="shared" ref="Q32:Q35" si="9">Q31+0.01</f>
         <v>0.20000000000000004</v>
       </c>
     </row>
@@ -4460,8 +4466,8 @@
       <c r="F33" s="56">
         <v>8837.2099999999991</v>
       </c>
-      <c r="G33" s="257">
-        <f>F33</f>
+      <c r="G33" s="50">
+        <f t="shared" si="8"/>
         <v>8837.2099999999991</v>
       </c>
       <c r="H33" s="51">
@@ -4495,7 +4501,7 @@
         <v>9102.2099999999991</v>
       </c>
       <c r="Q33" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
@@ -4516,8 +4522,8 @@
       <c r="F34" s="56">
         <v>8837.2199999999993</v>
       </c>
-      <c r="G34" s="258">
-        <f t="shared" ref="G34" si="9">F34</f>
+      <c r="G34" s="243">
+        <f t="shared" ref="G34" si="10">F34</f>
         <v>8837.2199999999993</v>
       </c>
       <c r="H34" s="51">
@@ -4551,7 +4557,7 @@
         <v>9102.2199999999993</v>
       </c>
       <c r="Q34" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
@@ -4574,7 +4580,7 @@
       <c r="F35" s="56">
         <v>8837.23</v>
       </c>
-      <c r="G35" s="257">
+      <c r="G35" s="50">
         <f>F35</f>
         <v>8837.23</v>
       </c>
@@ -4609,7 +4615,7 @@
         <v>9102.23</v>
       </c>
       <c r="Q35" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
@@ -4635,15 +4641,15 @@
         <v>-170181.69</v>
       </c>
       <c r="I36" s="38">
-        <f t="shared" ref="I36:O36" si="10">SUM(I13:I35)</f>
+        <f t="shared" ref="I36:O36" si="11">SUM(I13:I35)</f>
         <v>1.0799999999580905E-2</v>
       </c>
       <c r="J36" s="86">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2700000</v>
       </c>
       <c r="K36" s="38">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L36" s="61">
@@ -4653,15 +4659,15 @@
       <c r="M36" s="61"/>
       <c r="N36" s="61">
         <f>SUM(N13:N35)</f>
-        <v>2972471.7600000012</v>
+        <v>2982471.7600000012</v>
       </c>
       <c r="O36" s="61">
-        <f t="shared" si="10"/>
-        <v>3085251.7100000004</v>
+        <f t="shared" si="11"/>
+        <v>3095851.7100000004</v>
       </c>
       <c r="P36" s="61">
         <f>SUM(P13:P35)</f>
-        <v>3061645.7600000012</v>
+        <v>3071945.7600000012</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4670,94 +4676,100 @@
     </row>
     <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="209" t="str">
+      <c r="C39" s="208" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="209"/>
-      <c r="E39" s="209"/>
-      <c r="F39" s="209"/>
-      <c r="G39" s="209"/>
-      <c r="H39" s="209"/>
-      <c r="I39" s="209"/>
-      <c r="J39" s="209"/>
-      <c r="K39" s="209"/>
-      <c r="L39" s="209"/>
-      <c r="M39" s="209"/>
-      <c r="N39" s="209"/>
+      <c r="D39" s="208"/>
+      <c r="E39" s="208"/>
+      <c r="F39" s="208"/>
+      <c r="G39" s="208"/>
+      <c r="H39" s="208"/>
+      <c r="I39" s="208"/>
+      <c r="J39" s="208"/>
+      <c r="K39" s="208"/>
+      <c r="L39" s="208"/>
+      <c r="M39" s="208"/>
+      <c r="N39" s="208"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="209"/>
-      <c r="D40" s="209"/>
-      <c r="E40" s="209"/>
-      <c r="F40" s="209"/>
-      <c r="G40" s="209"/>
-      <c r="H40" s="209"/>
-      <c r="I40" s="209"/>
-      <c r="J40" s="209"/>
-      <c r="K40" s="209"/>
-      <c r="L40" s="209"/>
-      <c r="M40" s="209"/>
-      <c r="N40" s="209"/>
+      <c r="C40" s="208"/>
+      <c r="D40" s="208"/>
+      <c r="E40" s="208"/>
+      <c r="F40" s="208"/>
+      <c r="G40" s="208"/>
+      <c r="H40" s="208"/>
+      <c r="I40" s="208"/>
+      <c r="J40" s="208"/>
+      <c r="K40" s="208"/>
+      <c r="L40" s="208"/>
+      <c r="M40" s="208"/>
+      <c r="N40" s="208"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="209"/>
-      <c r="D41" s="209"/>
-      <c r="E41" s="209"/>
-      <c r="F41" s="209"/>
-      <c r="G41" s="209"/>
-      <c r="H41" s="209"/>
-      <c r="I41" s="209"/>
-      <c r="J41" s="209"/>
-      <c r="K41" s="209"/>
-      <c r="L41" s="209"/>
-      <c r="M41" s="209"/>
-      <c r="N41" s="209"/>
+      <c r="C41" s="208"/>
+      <c r="D41" s="208"/>
+      <c r="E41" s="208"/>
+      <c r="F41" s="208"/>
+      <c r="G41" s="208"/>
+      <c r="H41" s="208"/>
+      <c r="I41" s="208"/>
+      <c r="J41" s="208"/>
+      <c r="K41" s="208"/>
+      <c r="L41" s="208"/>
+      <c r="M41" s="208"/>
+      <c r="N41" s="208"/>
     </row>
     <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="209"/>
-      <c r="D42" s="209"/>
-      <c r="E42" s="209"/>
-      <c r="F42" s="209"/>
-      <c r="G42" s="209"/>
-      <c r="H42" s="209"/>
-      <c r="I42" s="209"/>
-      <c r="J42" s="209"/>
-      <c r="K42" s="209"/>
-      <c r="L42" s="209"/>
-      <c r="M42" s="209"/>
-      <c r="N42" s="209"/>
+      <c r="C42" s="208"/>
+      <c r="D42" s="208"/>
+      <c r="E42" s="208"/>
+      <c r="F42" s="208"/>
+      <c r="G42" s="208"/>
+      <c r="H42" s="208"/>
+      <c r="I42" s="208"/>
+      <c r="J42" s="208"/>
+      <c r="K42" s="208"/>
+      <c r="L42" s="208"/>
+      <c r="M42" s="208"/>
+      <c r="N42" s="208"/>
     </row>
     <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="209"/>
-      <c r="D43" s="209"/>
-      <c r="E43" s="209"/>
-      <c r="F43" s="209"/>
-      <c r="G43" s="209"/>
-      <c r="H43" s="209"/>
-      <c r="I43" s="209"/>
-      <c r="J43" s="209"/>
-      <c r="K43" s="209"/>
-      <c r="L43" s="209"/>
-      <c r="M43" s="209"/>
-      <c r="N43" s="209"/>
+      <c r="C43" s="208"/>
+      <c r="D43" s="208"/>
+      <c r="E43" s="208"/>
+      <c r="F43" s="208"/>
+      <c r="G43" s="208"/>
+      <c r="H43" s="208"/>
+      <c r="I43" s="208"/>
+      <c r="J43" s="208"/>
+      <c r="K43" s="208"/>
+      <c r="L43" s="208"/>
+      <c r="M43" s="208"/>
+      <c r="N43" s="208"/>
     </row>
     <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="209"/>
-      <c r="D44" s="209"/>
-      <c r="E44" s="209"/>
-      <c r="F44" s="209"/>
-      <c r="G44" s="209"/>
-      <c r="H44" s="209"/>
-      <c r="I44" s="209"/>
-      <c r="J44" s="209"/>
-      <c r="K44" s="209"/>
-      <c r="L44" s="209"/>
-      <c r="M44" s="209"/>
-      <c r="N44" s="209"/>
+      <c r="C44" s="208"/>
+      <c r="D44" s="208"/>
+      <c r="E44" s="208"/>
+      <c r="F44" s="208"/>
+      <c r="G44" s="208"/>
+      <c r="H44" s="208"/>
+      <c r="I44" s="208"/>
+      <c r="J44" s="208"/>
+      <c r="K44" s="208"/>
+      <c r="L44" s="208"/>
+      <c r="M44" s="208"/>
+      <c r="N44" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C39:N44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="M11:M12"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4771,12 +4783,6 @@
     <mergeCell ref="A9:P9"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="L11:L12"/>
-    <mergeCell ref="C39:N44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="M11:M12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4789,7 +4795,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C3" s="208" t="s">
+      <c r="C3" s="199" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4807,13 +4813,13 @@
     <col min="2" max="2" width="9" style="1" customWidth="1"/>
     <col min="3" max="3" width="6.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="13.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" style="199" customWidth="1"/>
-    <col min="6" max="6" width="13" style="199" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" style="199" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" style="199" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="190" customWidth="1"/>
+    <col min="6" max="6" width="13" style="190" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" style="190" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" style="190" customWidth="1"/>
     <col min="9" max="9" width="11.5703125" style="1" customWidth="1"/>
     <col min="10" max="10" width="15" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="199" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="190" customWidth="1"/>
     <col min="12" max="12" width="2.7109375" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -4825,10 +4831,10 @@
       <c r="C2" s="106" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="181" t="s">
+      <c r="D2" s="172" t="s">
         <v>126</v>
       </c>
-      <c r="E2" s="181" t="s">
+      <c r="E2" s="172" t="s">
         <v>127</v>
       </c>
       <c r="F2" s="106" t="s">
@@ -4841,7 +4847,7 @@
         <v>130</v>
       </c>
       <c r="I2" s="106"/>
-      <c r="J2" s="182" t="s">
+      <c r="J2" s="173" t="s">
         <v>131</v>
       </c>
       <c r="K2" s="107" t="s">
@@ -4849,31 +4855,31 @@
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="183">
+      <c r="B3" s="174">
         <v>1</v>
       </c>
-      <c r="C3" s="183" t="s">
+      <c r="C3" s="174" t="s">
         <v>81</v>
       </c>
-      <c r="D3" s="184">
+      <c r="D3" s="175">
         <v>8687.5</v>
       </c>
-      <c r="E3" s="184">
+      <c r="E3" s="175">
         <v>8687.5</v>
       </c>
-      <c r="F3" s="185">
+      <c r="F3" s="176">
         <f>(E3-D3)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="186">
+      <c r="G3" s="177">
         <f>F3/F32</f>
         <v>0</v>
       </c>
-      <c r="H3" s="187">
+      <c r="H3" s="178">
         <f>(F3/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I3" s="188">
+      <c r="I3" s="179">
         <v>0.12</v>
       </c>
       <c r="J3" s="151">
@@ -4886,31 +4892,31 @@
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="189">
+      <c r="B4" s="180">
         <v>1</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="180" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="190">
+      <c r="D4" s="181">
         <v>4488.6000000000004</v>
       </c>
-      <c r="E4" s="190">
+      <c r="E4" s="181">
         <v>4865.1000000000004</v>
       </c>
-      <c r="F4" s="191">
+      <c r="F4" s="182">
         <f>(E4-D4)</f>
         <v>376.5</v>
       </c>
-      <c r="G4" s="192">
+      <c r="G4" s="183">
         <f>F4/F32</f>
         <v>0.67412712623097581</v>
       </c>
-      <c r="H4" s="187">
+      <c r="H4" s="178">
         <f>(F4/F32)*H32</f>
         <v>132902.00501196174</v>
       </c>
-      <c r="I4" s="193">
+      <c r="I4" s="184">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J4" s="151">
@@ -4923,31 +4929,31 @@
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="189">
+      <c r="B5" s="180">
         <v>1</v>
       </c>
-      <c r="C5" s="189" t="s">
+      <c r="C5" s="180" t="s">
         <v>83</v>
       </c>
-      <c r="D5" s="184">
+      <c r="D5" s="175">
         <v>2366.38</v>
       </c>
-      <c r="E5" s="184">
+      <c r="E5" s="175">
         <v>2366.38</v>
       </c>
-      <c r="F5" s="185">
+      <c r="F5" s="176">
         <f t="shared" ref="F5:F17" si="1">(E5-D5)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="186">
+      <c r="G5" s="177">
         <f>F5/F32</f>
         <v>0</v>
       </c>
-      <c r="H5" s="187">
+      <c r="H5" s="178">
         <f>(F5/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I5" s="193">
+      <c r="I5" s="184">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J5" s="151">
@@ -4960,31 +4966,31 @@
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="183">
+      <c r="B6" s="174">
         <v>2</v>
       </c>
-      <c r="C6" s="183" t="s">
+      <c r="C6" s="174" t="s">
         <v>81</v>
       </c>
-      <c r="D6" s="184">
+      <c r="D6" s="175">
         <v>3731.1</v>
       </c>
-      <c r="E6" s="184">
+      <c r="E6" s="175">
         <v>3731.1</v>
       </c>
-      <c r="F6" s="185">
+      <c r="F6" s="176">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G6" s="186">
+      <c r="G6" s="177">
         <f>F6/F32</f>
         <v>0</v>
       </c>
-      <c r="H6" s="187">
+      <c r="H6" s="178">
         <f>(F6/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I6" s="193">
+      <c r="I6" s="184">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J6" s="151">
@@ -4997,31 +5003,31 @@
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="183">
+      <c r="B7" s="174">
         <v>2</v>
       </c>
-      <c r="C7" s="183" t="s">
+      <c r="C7" s="174" t="s">
         <v>84</v>
       </c>
-      <c r="D7" s="184">
+      <c r="D7" s="175">
         <v>3897.7</v>
       </c>
-      <c r="E7" s="184">
+      <c r="E7" s="175">
         <v>3897.7</v>
       </c>
-      <c r="F7" s="185">
+      <c r="F7" s="176">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G7" s="186">
+      <c r="G7" s="177">
         <f>F7/F32</f>
         <v>0</v>
       </c>
-      <c r="H7" s="187">
+      <c r="H7" s="178">
         <f>(F7/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I7" s="193">
+      <c r="I7" s="184">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J7" s="151">
@@ -5034,31 +5040,31 @@
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="183">
+      <c r="B8" s="174">
         <v>2</v>
       </c>
-      <c r="C8" s="183" t="s">
+      <c r="C8" s="174" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="184">
+      <c r="D8" s="175">
         <v>2956.2</v>
       </c>
-      <c r="E8" s="184">
+      <c r="E8" s="175">
         <v>2956.2</v>
       </c>
-      <c r="F8" s="185">
+      <c r="F8" s="176">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G8" s="186">
+      <c r="G8" s="177">
         <f>F8/F32</f>
         <v>0</v>
       </c>
-      <c r="H8" s="187">
+      <c r="H8" s="178">
         <f>(F8/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I8" s="193">
+      <c r="I8" s="184">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J8" s="151">
@@ -5071,31 +5077,31 @@
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="183">
+      <c r="B9" s="174">
         <v>2</v>
       </c>
-      <c r="C9" s="183" t="s">
+      <c r="C9" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="184">
+      <c r="D9" s="175">
         <v>3923.7</v>
       </c>
-      <c r="E9" s="184">
+      <c r="E9" s="175">
         <v>3923.7</v>
       </c>
-      <c r="F9" s="185">
+      <c r="F9" s="176">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G9" s="186">
+      <c r="G9" s="177">
         <f>F9/F32</f>
         <v>0</v>
       </c>
-      <c r="H9" s="194">
+      <c r="H9" s="185">
         <f>(F9/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I9" s="193">
+      <c r="I9" s="184">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J9" s="151">
@@ -5108,31 +5114,31 @@
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="183">
+      <c r="B10" s="174">
         <v>3</v>
       </c>
-      <c r="C10" s="183" t="s">
+      <c r="C10" s="174" t="s">
         <v>81</v>
       </c>
-      <c r="D10" s="184">
+      <c r="D10" s="175">
         <v>2881.8</v>
       </c>
-      <c r="E10" s="184">
+      <c r="E10" s="175">
         <v>2881.8</v>
       </c>
-      <c r="F10" s="185">
+      <c r="F10" s="176">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G10" s="186">
+      <c r="G10" s="177">
         <f>F10/F32</f>
         <v>0</v>
       </c>
-      <c r="H10" s="187">
+      <c r="H10" s="178">
         <f>(F10/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I10" s="193">
+      <c r="I10" s="184">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J10" s="151">
@@ -5145,31 +5151,31 @@
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B11" s="189">
+      <c r="B11" s="180">
         <v>3</v>
       </c>
-      <c r="C11" s="189" t="s">
+      <c r="C11" s="180" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="190">
+      <c r="D11" s="181">
         <v>4646</v>
       </c>
-      <c r="E11" s="190">
+      <c r="E11" s="181">
         <v>4828</v>
       </c>
-      <c r="F11" s="191">
+      <c r="F11" s="182">
         <f t="shared" si="1"/>
         <v>182</v>
       </c>
-      <c r="G11" s="192">
+      <c r="G11" s="183">
         <f>F11/F32</f>
         <v>0.32587287376902419</v>
       </c>
-      <c r="H11" s="187">
+      <c r="H11" s="178">
         <f>(F11/F32)*H32</f>
         <v>64244.793923444988</v>
       </c>
-      <c r="I11" s="193">
+      <c r="I11" s="184">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J11" s="151">
@@ -5182,31 +5188,31 @@
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="183">
+      <c r="B12" s="174">
         <v>3</v>
       </c>
-      <c r="C12" s="183" t="s">
+      <c r="C12" s="174" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="184">
+      <c r="D12" s="175">
         <v>4554.6000000000004</v>
       </c>
-      <c r="E12" s="184">
+      <c r="E12" s="175">
         <v>4554.6000000000004</v>
       </c>
-      <c r="F12" s="185">
+      <c r="F12" s="176">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G12" s="186">
+      <c r="G12" s="177">
         <f>F12/F32</f>
         <v>0</v>
       </c>
-      <c r="H12" s="187">
+      <c r="H12" s="178">
         <f>(F12/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I12" s="193">
+      <c r="I12" s="184">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J12" s="151">
@@ -5219,31 +5225,31 @@
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="183">
+      <c r="B13" s="174">
         <v>3</v>
       </c>
-      <c r="C13" s="183" t="s">
+      <c r="C13" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="184">
+      <c r="D13" s="175">
         <v>4138.6000000000004</v>
       </c>
-      <c r="E13" s="184">
+      <c r="E13" s="175">
         <v>4138.6000000000004</v>
       </c>
-      <c r="F13" s="185">
+      <c r="F13" s="176">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G13" s="186">
+      <c r="G13" s="177">
         <f>F13/F32</f>
         <v>0</v>
       </c>
-      <c r="H13" s="187">
+      <c r="H13" s="178">
         <f>(F13/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I13" s="193">
+      <c r="I13" s="184">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J13" s="151">
@@ -5256,31 +5262,31 @@
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="183">
+      <c r="B14" s="174">
         <v>4</v>
       </c>
-      <c r="C14" s="183" t="s">
+      <c r="C14" s="174" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="184">
+      <c r="D14" s="175">
         <v>8190.4</v>
       </c>
-      <c r="E14" s="184">
+      <c r="E14" s="175">
         <v>8190.4</v>
       </c>
-      <c r="F14" s="185">
+      <c r="F14" s="176">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G14" s="186">
+      <c r="G14" s="177">
         <f>F14/F32</f>
         <v>0</v>
       </c>
-      <c r="H14" s="187">
+      <c r="H14" s="178">
         <f>(F14/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I14" s="193">
+      <c r="I14" s="184">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J14" s="151">
@@ -5293,31 +5299,31 @@
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="183">
+      <c r="B15" s="174">
         <v>4</v>
       </c>
-      <c r="C15" s="183" t="s">
+      <c r="C15" s="174" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="184">
+      <c r="D15" s="175">
         <v>3475.3</v>
       </c>
-      <c r="E15" s="184">
+      <c r="E15" s="175">
         <v>3475.3</v>
       </c>
-      <c r="F15" s="185">
+      <c r="F15" s="176">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G15" s="186">
+      <c r="G15" s="177">
         <f>F15/F32</f>
         <v>0</v>
       </c>
-      <c r="H15" s="187">
+      <c r="H15" s="178">
         <f>(F15/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I15" s="193">
+      <c r="I15" s="184">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J15" s="151">
@@ -5330,31 +5336,31 @@
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="183">
+      <c r="B16" s="174">
         <v>4</v>
       </c>
-      <c r="C16" s="183" t="s">
+      <c r="C16" s="174" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="184">
+      <c r="D16" s="175">
         <v>4363.3</v>
       </c>
-      <c r="E16" s="184">
+      <c r="E16" s="175">
         <v>4363.3</v>
       </c>
-      <c r="F16" s="185">
+      <c r="F16" s="176">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G16" s="186">
+      <c r="G16" s="177">
         <f>F16/F32</f>
         <v>0</v>
       </c>
-      <c r="H16" s="187">
+      <c r="H16" s="178">
         <f>(F16/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I16" s="193">
+      <c r="I16" s="184">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J16" s="151">
@@ -5367,31 +5373,31 @@
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="183">
+      <c r="B17" s="174">
         <v>4</v>
       </c>
-      <c r="C17" s="183" t="s">
+      <c r="C17" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="D17" s="184">
+      <c r="D17" s="175">
         <v>6036.6</v>
       </c>
-      <c r="E17" s="184">
+      <c r="E17" s="175">
         <v>6036.6</v>
       </c>
-      <c r="F17" s="185">
+      <c r="F17" s="176">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G17" s="186">
+      <c r="G17" s="177">
         <f>F17/F32</f>
         <v>0</v>
       </c>
-      <c r="H17" s="187">
+      <c r="H17" s="178">
         <f>(F17/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I17" s="193">
+      <c r="I17" s="184">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J17" s="151">
@@ -5406,21 +5412,21 @@
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="106"/>
       <c r="C18" s="106"/>
-      <c r="D18" s="195"/>
-      <c r="E18" s="195"/>
-      <c r="F18" s="196">
+      <c r="D18" s="186"/>
+      <c r="E18" s="186"/>
+      <c r="F18" s="187">
         <f>SUM(F3:F17)</f>
         <v>558.5</v>
       </c>
       <c r="G18" s="107" t="s">
         <v>133</v>
       </c>
-      <c r="H18" s="187">
+      <c r="H18" s="178">
         <f>SUM(H3:H17)</f>
         <v>197146.79893540672</v>
       </c>
       <c r="I18" s="106"/>
-      <c r="J18" s="197">
+      <c r="J18" s="188">
         <f>SUM(J3:J17)</f>
         <v>235686.61542200952</v>
       </c>
@@ -5436,7 +5442,7 @@
       <c r="E19" s="106"/>
       <c r="F19" s="106"/>
       <c r="G19" s="106"/>
-      <c r="H19" s="198"/>
+      <c r="H19" s="189"/>
       <c r="K19" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5454,7 +5460,7 @@
       <c r="F20" s="106"/>
       <c r="G20" s="106"/>
       <c r="H20" s="106"/>
-      <c r="I20" s="193">
+      <c r="I20" s="184">
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="J20" s="151">
@@ -5478,7 +5484,7 @@
       <c r="F21" s="106"/>
       <c r="G21" s="106"/>
       <c r="H21" s="106"/>
-      <c r="I21" s="193">
+      <c r="I21" s="184">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J21" s="151">
@@ -5502,7 +5508,7 @@
       <c r="F22" s="106"/>
       <c r="G22" s="106"/>
       <c r="H22" s="106"/>
-      <c r="I22" s="193">
+      <c r="I22" s="184">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J22" s="151">
@@ -5526,7 +5532,7 @@
       <c r="F23" s="106"/>
       <c r="G23" s="106"/>
       <c r="H23" s="106"/>
-      <c r="I23" s="193">
+      <c r="I23" s="184">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J23" s="151">
@@ -5550,7 +5556,7 @@
       <c r="F24" s="106"/>
       <c r="G24" s="106"/>
       <c r="H24" s="106"/>
-      <c r="I24" s="193">
+      <c r="I24" s="184">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J24" s="151">
@@ -5574,7 +5580,7 @@
       <c r="F25" s="106"/>
       <c r="G25" s="106"/>
       <c r="H25" s="106"/>
-      <c r="I25" s="193">
+      <c r="I25" s="184">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="J25" s="151">
@@ -5598,7 +5604,7 @@
       <c r="F26" s="106"/>
       <c r="G26" s="106"/>
       <c r="H26" s="106"/>
-      <c r="I26" s="193">
+      <c r="I26" s="184">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="J26" s="151">
@@ -5622,7 +5628,7 @@
       <c r="F27" s="106"/>
       <c r="G27" s="106"/>
       <c r="H27" s="106"/>
-      <c r="I27" s="193">
+      <c r="I27" s="184">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="J27" s="151">
@@ -5658,17 +5664,17 @@
       <c r="F29" s="109"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D30" s="250" t="s">
+      <c r="D30" s="241" t="s">
         <v>135</v>
       </c>
-      <c r="E30" s="251"/>
+      <c r="E30" s="242"/>
       <c r="F30" s="108">
         <v>1254</v>
       </c>
       <c r="G30" s="107" t="s">
         <v>136</v>
       </c>
-      <c r="H30" s="200">
+      <c r="H30" s="191">
         <v>442653.69</v>
       </c>
       <c r="K30" s="150">
@@ -5680,90 +5686,90 @@
       <c r="D31" s="109"/>
       <c r="E31" s="109"/>
       <c r="F31" s="110"/>
-      <c r="H31" s="201"/>
-      <c r="K31" s="202"/>
+      <c r="H31" s="192"/>
+      <c r="K31" s="193"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D32" s="250" t="s">
+      <c r="D32" s="241" t="s">
         <v>137</v>
       </c>
-      <c r="E32" s="251"/>
-      <c r="F32" s="196">
+      <c r="E32" s="242"/>
+      <c r="F32" s="187">
         <f>SUM(F3:F17)</f>
         <v>558.5</v>
       </c>
       <c r="G32" s="107" t="s">
         <v>133</v>
       </c>
-      <c r="H32" s="203">
+      <c r="H32" s="194">
         <f>H30-H34</f>
         <v>197146.79893540672</v>
       </c>
-      <c r="K32" s="202"/>
+      <c r="K32" s="193"/>
     </row>
     <row r="33" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D33" s="250"/>
-      <c r="E33" s="251"/>
+      <c r="D33" s="241"/>
+      <c r="E33" s="242"/>
       <c r="F33" s="108"/>
       <c r="G33" s="107"/>
-      <c r="H33" s="204"/>
-      <c r="K33" s="202"/>
+      <c r="H33" s="195"/>
+      <c r="K33" s="193"/>
     </row>
     <row r="34" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D34" s="250" t="s">
+      <c r="D34" s="241" t="s">
         <v>138</v>
       </c>
-      <c r="E34" s="251"/>
-      <c r="F34" s="196">
+      <c r="E34" s="242"/>
+      <c r="F34" s="187">
         <f>F30-F32</f>
         <v>695.5</v>
       </c>
       <c r="G34" s="107" t="s">
         <v>139</v>
       </c>
-      <c r="H34" s="203">
+      <c r="H34" s="194">
         <f>(H30*F34)/F30</f>
         <v>245506.89106459328</v>
       </c>
       <c r="K34" s="1"/>
     </row>
     <row r="36" spans="4:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="F36" s="246" t="s">
+      <c r="F36" s="237" t="s">
         <v>140</v>
       </c>
-      <c r="G36" s="247"/>
-      <c r="H36" s="205">
+      <c r="G36" s="238"/>
+      <c r="H36" s="196">
         <f>H32+H33+H34</f>
         <v>442653.69</v>
       </c>
     </row>
     <row r="38" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D38" s="248" t="s">
+      <c r="D38" s="239" t="s">
         <v>141</v>
       </c>
-      <c r="E38" s="249"/>
-      <c r="F38" s="206">
+      <c r="E38" s="240"/>
+      <c r="F38" s="197">
         <v>46164</v>
       </c>
-      <c r="G38" s="206">
+      <c r="G38" s="197">
         <v>46197</v>
       </c>
-      <c r="H38" s="207" t="s">
+      <c r="H38" s="198" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="39" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D39" s="248" t="s">
+      <c r="D39" s="239" t="s">
         <v>143</v>
       </c>
-      <c r="E39" s="249"/>
-      <c r="F39" s="207">
+      <c r="E39" s="240"/>
+      <c r="F39" s="198">
         <v>274268</v>
       </c>
-      <c r="G39" s="207">
+      <c r="G39" s="198">
         <v>275522</v>
       </c>
-      <c r="H39" s="207">
+      <c r="H39" s="198">
         <f>G39-F39</f>
         <v>1254</v>
       </c>

--- a/2026/SALTA 1167/Agosto/SALTA1167-Agosto.xlsx
+++ b/2026/SALTA 1167/Agosto/SALTA1167-Agosto.xlsx
@@ -1,38 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\SALTA 1167\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29C2953-C4A2-4A21-9AEE-551C82D36185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F420E782-441A-4179-8365-1D3412C3BC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
-    <sheet name="Anotaciones" sheetId="4" r:id="rId3"/>
-    <sheet name="EDESUR" sheetId="5" r:id="rId4"/>
+    <sheet name="EDESUR" sheetId="6" r:id="rId3"/>
+    <sheet name="Anotaciones" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$96</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="155">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -416,12 +411,6 @@
     <t>Saldo al 01/07</t>
   </si>
   <si>
-    <t>26/052026</t>
-  </si>
-  <si>
-    <t>25/062026</t>
-  </si>
-  <si>
     <t>Consumo Kw</t>
   </si>
   <si>
@@ -434,42 +423,12 @@
     <t>Cons Esp Com</t>
   </si>
   <si>
-    <t>Total x Depto</t>
-  </si>
-  <si>
-    <t>Cons Deptos</t>
-  </si>
-  <si>
     <t>Cons Coch</t>
   </si>
   <si>
-    <t>Total Consumo s/Edesur</t>
-  </si>
-  <si>
-    <t>Total x cons Edesur</t>
-  </si>
-  <si>
-    <t>Total Consumo Medidores</t>
-  </si>
-  <si>
-    <t>Consumo Esp Comunes</t>
-  </si>
-  <si>
-    <t>Cons Esp Com $</t>
-  </si>
-  <si>
     <t>TOTAL FACT EDESUR</t>
   </si>
   <si>
-    <t>Lecturas EDESUR s/facturas</t>
-  </si>
-  <si>
-    <t>Cons s/EDESUR</t>
-  </si>
-  <si>
-    <t>Lect Med Edesur 01</t>
-  </si>
-  <si>
     <t>A gaston le doble cobramos un sum erroneamente el mes pasado, corregir en agosto - Debe abonar 132.216,09 , pago 182.216,09</t>
   </si>
   <si>
@@ -513,13 +472,37 @@
   </si>
   <si>
     <t>Bonificado</t>
+  </si>
+  <si>
+    <t>Consumos PARTICULARES</t>
+  </si>
+  <si>
+    <t>Consumos GENERALES</t>
+  </si>
+  <si>
+    <t>Total Edesur x Depto</t>
+  </si>
+  <si>
+    <t>Bonificado x EDESUR</t>
+  </si>
+  <si>
+    <t>SALDO a PAGAR</t>
+  </si>
+  <si>
+    <t>Porcentaje</t>
+  </si>
+  <si>
+    <t>Totales</t>
+  </si>
+  <si>
+    <t>Mes ANTERIOR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="11">
+  <numFmts count="10">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
@@ -530,9 +513,8 @@
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.0_-;\-[$$-2C0A]\ * #,##0.0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -722,14 +704,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0" tint="-0.34998626667073579"/>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
       <name val="Calibri"/>
@@ -739,15 +721,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="8" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1189,7 +1162,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="253">
+  <cellXfs count="246">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1425,9 +1398,6 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1462,215 +1432,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="25" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="17" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1687,6 +1468,173 @@
     </xf>
     <xf numFmtId="8" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1766,9 +1714,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1806,9 +1754,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1841,26 +1789,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1893,26 +1824,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2087,21 +2001,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.42578125" customWidth="1"/>
+    <col min="12" max="12" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="12"/>
       <c r="B1" s="44" t="s">
         <v>73</v>
@@ -2110,7 +2024,7 @@
       <c r="D1" s="44"/>
       <c r="E1" s="45"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="13"/>
       <c r="B2" s="46" t="s">
         <v>14</v>
@@ -2119,16 +2033,16 @@
       <c r="D2" s="46"/>
       <c r="E2" s="47"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="13"/>
-      <c r="B3" s="204" t="s">
+      <c r="B3" s="196" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="204"/>
-      <c r="D3" s="204"/>
-      <c r="E3" s="205"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="197"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
         <v>0</v>
       </c>
@@ -2139,12 +2053,12 @@
       <c r="D4" s="17"/>
       <c r="E4" s="18"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
         <v>74</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="46" t="s">
@@ -2152,7 +2066,7 @@
       </c>
       <c r="E5" s="15"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>122</v>
       </c>
@@ -2163,57 +2077,57 @@
       </c>
       <c r="E6" s="18"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="207" t="s">
-        <v>145</v>
-      </c>
-      <c r="C8" s="207"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="207"/>
-      <c r="C9" s="207"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="207"/>
-      <c r="C10" s="207"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="206" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="199" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="199"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="199"/>
+      <c r="C9" s="199"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="199"/>
+      <c r="C10" s="199"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="198" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="206"/>
-      <c r="C13" s="206"/>
-      <c r="D13" s="206"/>
-      <c r="E13" s="206"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="206"/>
-      <c r="B14" s="206"/>
-      <c r="C14" s="206"/>
-      <c r="D14" s="206"/>
-      <c r="E14" s="206"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="206"/>
-      <c r="B15" s="206"/>
-      <c r="C15" s="206"/>
-      <c r="D15" s="206"/>
-      <c r="E15" s="206"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="206"/>
-      <c r="B16" s="206"/>
-      <c r="C16" s="206"/>
-      <c r="D16" s="206"/>
-      <c r="E16" s="206"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="198"/>
+      <c r="C13" s="198"/>
+      <c r="D13" s="198"/>
+      <c r="E13" s="198"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="198"/>
+      <c r="B14" s="198"/>
+      <c r="C14" s="198"/>
+      <c r="D14" s="198"/>
+      <c r="E14" s="198"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="198"/>
+      <c r="B15" s="198"/>
+      <c r="C15" s="198"/>
+      <c r="D15" s="198"/>
+      <c r="E15" s="198"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="198"/>
+      <c r="B16" s="198"/>
+      <c r="C16" s="198"/>
+      <c r="D16" s="198"/>
+      <c r="E16" s="198"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>101</v>
       </c>
@@ -2222,7 +2136,7 @@
       <c r="D20" s="6"/>
       <c r="E20" s="11"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
         <v>76</v>
       </c>
@@ -2231,84 +2145,84 @@
       <c r="D21" s="98"/>
       <c r="E21" s="93"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="202" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="192" t="s">
         <v>112</v>
       </c>
-      <c r="B22" s="203"/>
-      <c r="C22" s="152"/>
-      <c r="D22" s="244">
+      <c r="B22" s="193"/>
+      <c r="C22" s="151"/>
+      <c r="D22" s="180">
         <v>510846.85</v>
       </c>
       <c r="E22" s="146" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="H22" s="82"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="202"/>
-      <c r="B23" s="203"/>
-      <c r="C23" s="152"/>
-      <c r="D23" s="244"/>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="192"/>
+      <c r="B23" s="193"/>
+      <c r="C23" s="151"/>
+      <c r="D23" s="180"/>
       <c r="E23" s="94"/>
       <c r="H23" s="82"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="153" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="152" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="153"/>
-      <c r="C24" s="153"/>
-      <c r="D24" s="245"/>
+      <c r="B24" s="152"/>
+      <c r="C24" s="152"/>
+      <c r="D24" s="181"/>
       <c r="E24" s="137">
         <f>SUM(D22:D23)</f>
         <v>510846.85</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="154" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="153" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="153"/>
-      <c r="C25" s="153"/>
-      <c r="D25" s="246"/>
+      <c r="B25" s="152"/>
+      <c r="C25" s="152"/>
+      <c r="D25" s="182"/>
       <c r="E25" s="138"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="202" t="s">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="192" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="203"/>
-      <c r="C26" s="155"/>
-      <c r="D26" s="247">
+      <c r="B26" s="193"/>
+      <c r="C26" s="154"/>
+      <c r="D26" s="183">
         <v>79873.05</v>
       </c>
       <c r="E26" s="96" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="153" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="152" t="s">
         <v>1</v>
       </c>
-      <c r="B27" s="153"/>
-      <c r="C27" s="153"/>
-      <c r="D27" s="245"/>
+      <c r="B27" s="152"/>
+      <c r="C27" s="152"/>
+      <c r="D27" s="181"/>
       <c r="E27" s="104">
         <f>SUM(D26:D26)</f>
         <v>79873.05</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="154" t="s">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="153" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="156"/>
-      <c r="C28" s="156"/>
-      <c r="D28" s="248"/>
+      <c r="B28" s="155"/>
+      <c r="C28" s="155"/>
+      <c r="D28" s="184"/>
       <c r="E28" s="139"/>
     </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="65" t="s">
         <v>66</v>
       </c>
@@ -2318,10 +2232,10 @@
         <v>14396.25</v>
       </c>
       <c r="E29" s="96" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="65" t="s">
         <v>66</v>
       </c>
@@ -2331,10 +2245,10 @@
         <v>265234.65000000002</v>
       </c>
       <c r="E30" s="96" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="65" t="s">
         <v>65</v>
       </c>
@@ -2348,169 +2262,169 @@
         <v>Transf 04/08</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="157"/>
+      <c r="B32" s="156"/>
       <c r="C32" s="65"/>
       <c r="D32" s="95">
         <v>482119.34</v>
       </c>
       <c r="E32" s="96" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="200" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="194" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="201"/>
+      <c r="B33" s="195"/>
       <c r="C33" s="65"/>
       <c r="D33" s="95">
         <v>872785.72</v>
       </c>
       <c r="E33" s="96" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="158" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="157" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="159"/>
+      <c r="B34" s="158"/>
       <c r="C34" s="65"/>
       <c r="D34" s="95">
         <v>28704.880000000001</v>
       </c>
       <c r="E34" s="96" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="153" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="152" t="s">
         <v>2</v>
       </c>
-      <c r="B35" s="153"/>
-      <c r="C35" s="153"/>
-      <c r="D35" s="249"/>
+      <c r="B35" s="152"/>
+      <c r="C35" s="152"/>
+      <c r="D35" s="185"/>
       <c r="E35" s="140">
         <f>SUM(D29:D34)</f>
         <v>1669885.23</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="154"/>
-      <c r="B36" s="153"/>
-      <c r="C36" s="153"/>
-      <c r="D36" s="245"/>
+    <row r="36" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="153"/>
+      <c r="B36" s="152"/>
+      <c r="C36" s="152"/>
+      <c r="D36" s="181"/>
       <c r="E36" s="141"/>
     </row>
-    <row r="37" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="202" t="s">
+    <row r="37" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="192" t="s">
         <v>114</v>
       </c>
-      <c r="B37" s="203"/>
+      <c r="B37" s="193"/>
       <c r="C37" s="65"/>
       <c r="D37" s="95">
         <v>82000</v>
       </c>
       <c r="E37" s="96" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="160" t="s">
-        <v>152</v>
-      </c>
-      <c r="B38" s="161"/>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="159" t="s">
+        <v>140</v>
+      </c>
+      <c r="B38" s="160"/>
       <c r="C38" s="65"/>
       <c r="D38" s="95">
         <f>199530</f>
         <v>199530</v>
       </c>
       <c r="E38" s="96" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="202" t="s">
-        <v>154</v>
-      </c>
-      <c r="B39" s="203"/>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="B39" s="193"/>
       <c r="C39" s="65"/>
       <c r="D39" s="68">
         <v>157988.29</v>
       </c>
       <c r="E39" s="96"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="153" t="s">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="152" t="s">
         <v>6</v>
       </c>
-      <c r="B40" s="154"/>
-      <c r="C40" s="154"/>
-      <c r="D40" s="154"/>
+      <c r="B40" s="153"/>
+      <c r="C40" s="153"/>
+      <c r="D40" s="153"/>
       <c r="E40" s="104">
         <f>SUM(D37:D39)</f>
         <v>439518.29000000004</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="154" t="s">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="B41" s="154"/>
-      <c r="C41" s="154"/>
+      <c r="B41" s="153"/>
+      <c r="C41" s="153"/>
       <c r="D41" s="98"/>
       <c r="E41" s="142"/>
     </row>
-    <row r="42" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="202" t="s">
-        <v>147</v>
-      </c>
-      <c r="B42" s="203"/>
-      <c r="C42" s="152"/>
-      <c r="D42" s="250">
+    <row r="42" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="192" t="s">
+        <v>135</v>
+      </c>
+      <c r="B42" s="193"/>
+      <c r="C42" s="151"/>
+      <c r="D42" s="186">
         <v>190000</v>
       </c>
       <c r="E42" s="143" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="153" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="152" t="s">
         <v>9</v>
       </c>
-      <c r="B43" s="153"/>
-      <c r="C43" s="153"/>
-      <c r="D43" s="245"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="181"/>
       <c r="E43" s="137">
         <f>SUM(D42:D42)</f>
         <v>190000</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="154" t="s">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="153" t="s">
         <v>8</v>
       </c>
-      <c r="B44" s="162"/>
-      <c r="C44" s="153"/>
-      <c r="D44" s="251"/>
+      <c r="B44" s="161"/>
+      <c r="C44" s="152"/>
+      <c r="D44" s="187"/>
       <c r="E44" s="104"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="65" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="B45" s="65" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="C45" s="65"/>
       <c r="D45" s="95"/>
       <c r="E45" s="144"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="65" t="s">
         <v>113</v>
       </c>
@@ -2522,47 +2436,47 @@
       </c>
       <c r="E46" s="145"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="163" t="s">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="162" t="s">
         <v>9</v>
       </c>
-      <c r="B47" s="163"/>
-      <c r="C47" s="163"/>
-      <c r="D47" s="252"/>
+      <c r="B47" s="162"/>
+      <c r="C47" s="162"/>
+      <c r="D47" s="188"/>
       <c r="E47" s="104">
         <f>SUM(D45:D46)</f>
         <v>36608.320000000007</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="65"/>
       <c r="B48" s="65"/>
       <c r="C48" s="65"/>
       <c r="D48" s="65"/>
       <c r="E48" s="70"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="164" t="s">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="B49" s="164"/>
-      <c r="C49" s="164"/>
+      <c r="B49" s="163"/>
+      <c r="C49" s="163"/>
       <c r="D49" s="71"/>
       <c r="E49" s="105"/>
     </row>
-    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="165"/>
+    <row r="50" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="164"/>
       <c r="B50" s="72"/>
       <c r="C50" s="72"/>
       <c r="D50" s="72"/>
       <c r="E50" s="73"/>
       <c r="F50" s="27"/>
     </row>
-    <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="166" t="s">
+    <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="165" t="s">
         <v>93</v>
       </c>
-      <c r="B51" s="167"/>
+      <c r="B51" s="166"/>
       <c r="C51" s="74"/>
       <c r="D51" s="74"/>
       <c r="E51" s="75">
@@ -2572,14 +2486,14 @@
       <c r="F51" s="92"/>
       <c r="G51" s="27"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="72"/>
       <c r="B52" s="72"/>
       <c r="C52" s="72"/>
       <c r="D52" s="72"/>
       <c r="E52" s="72"/>
     </row>
-    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="72"/>
       <c r="B53" s="72"/>
       <c r="C53" s="72"/>
@@ -2587,44 +2501,44 @@
       <c r="E53" s="72"/>
       <c r="H53" s="99"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="168" t="s">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="167" t="s">
         <v>94</v>
       </c>
-      <c r="B54" s="169"/>
-      <c r="C54" s="170"/>
+      <c r="B54" s="168"/>
+      <c r="C54" s="169"/>
       <c r="D54" s="76"/>
       <c r="E54" s="77"/>
     </row>
-    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="171"/>
-      <c r="B55" s="159"/>
+    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="170"/>
+      <c r="B55" s="158"/>
       <c r="C55" s="65"/>
       <c r="D55" s="68"/>
       <c r="E55" s="66"/>
     </row>
-    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="210"/>
-      <c r="B56" s="210"/>
+    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="191"/>
+      <c r="B56" s="191"/>
       <c r="C56" s="65"/>
       <c r="D56" s="95"/>
       <c r="E56" s="66"/>
     </row>
-    <row r="57" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="67"/>
       <c r="B58" s="69"/>
       <c r="C58" s="4"/>
       <c r="D58" s="68"/>
       <c r="E58" s="66"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="32"/>
       <c r="B59" s="31"/>
       <c r="C59" s="31"/>
@@ -2634,9 +2548,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="20" t="s">
         <v>96</v>
       </c>
@@ -2645,8 +2559,8 @@
       <c r="D62" s="21"/>
       <c r="E62" s="135"/>
     </row>
-    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="64" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>95</v>
       </c>
@@ -2658,8 +2572,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="63" t="s">
         <v>102</v>
       </c>
@@ -2668,7 +2582,7 @@
         <v>2926731.7399999998</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="63" t="s">
         <v>103</v>
       </c>
@@ -2677,7 +2591,7 @@
         <v>2926731.7399999998</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="63" t="s">
         <v>104</v>
       </c>
@@ -2686,7 +2600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="63" t="s">
         <v>105</v>
       </c>
@@ -2695,12 +2609,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71"/>
       <c r="B71" s="26"/>
       <c r="C71" s="24"/>
     </row>
-    <row r="72" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="84" t="s">
         <v>106</v>
       </c>
@@ -2710,7 +2624,7 @@
       <c r="C72" s="24"/>
       <c r="D72" s="30"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="35" t="s">
         <v>99</v>
       </c>
@@ -2720,7 +2634,7 @@
       </c>
       <c r="E73" s="27"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="35" t="s">
         <v>25</v>
       </c>
@@ -2729,7 +2643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="35" t="s">
         <v>108</v>
       </c>
@@ -2738,15 +2652,15 @@
         <v>3248082.4500000007</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="91" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="B76" s="100">
         <v>-50000</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="87" t="s">
         <v>110</v>
       </c>
@@ -2756,13 +2670,13 @@
       </c>
       <c r="D77" s="27"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="85"/>
       <c r="B78" s="85"/>
       <c r="D78" s="27"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="84" t="s">
         <v>107</v>
       </c>
@@ -2772,7 +2686,7 @@
       <c r="D79" s="26"/>
       <c r="E79" s="27"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="35" t="s">
         <v>100</v>
       </c>
@@ -2783,7 +2697,7 @@
       <c r="D80" s="27"/>
       <c r="E80" s="27"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="35" t="s">
         <v>25</v>
       </c>
@@ -2793,7 +2707,7 @@
       </c>
       <c r="D81" s="27"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="35" t="s">
         <v>109</v>
       </c>
@@ -2802,7 +2716,7 @@
       </c>
       <c r="D82" s="136"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="91" t="s">
         <v>24</v>
       </c>
@@ -2811,7 +2725,7 @@
       <c r="E83" s="27"/>
       <c r="F83" s="26"/>
     </row>
-    <row r="84" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="87" t="s">
         <v>111</v>
       </c>
@@ -2822,15 +2736,15 @@
       <c r="D84" s="27"/>
       <c r="F84" s="27"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="85"/>
       <c r="B85" s="85"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="85"/>
       <c r="B86" s="85"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="84" t="s">
         <v>124</v>
       </c>
@@ -2838,7 +2752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="35" t="s">
         <v>125</v>
       </c>
@@ -2846,28 +2760,28 @@
         <v>1025063.51</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="87" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="B89" s="88">
         <v>1054849.6000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A91" s="209" t="s">
+    <row r="90" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A91" s="190" t="s">
         <v>18</v>
       </c>
-      <c r="B91" s="209"/>
-      <c r="C91" s="209"/>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A92" s="209"/>
-      <c r="B92" s="209"/>
-      <c r="C92" s="209"/>
-    </row>
-    <row r="93" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="190"/>
+      <c r="C91" s="190"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A92" s="190"/>
+      <c r="B92" s="190"/>
+      <c r="C92" s="190"/>
+    </row>
+    <row r="93" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="79"/>
       <c r="B93" s="23"/>
       <c r="C93" s="23">
@@ -2875,13 +2789,13 @@
       </c>
       <c r="E93" s="92"/>
     </row>
-    <row r="94" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="79"/>
       <c r="B94" s="81"/>
       <c r="C94" s="78"/>
       <c r="D94" s="92"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="28" t="s">
         <v>6</v>
       </c>
@@ -2891,45 +2805,39 @@
       </c>
       <c r="C95" s="29"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M96" s="5"/>
     </row>
-    <row r="97" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="208"/>
-      <c r="B97" s="208"/>
-      <c r="C97" s="208"/>
-      <c r="D97" s="208"/>
-      <c r="E97" s="208"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="208"/>
-      <c r="B98" s="208"/>
-      <c r="C98" s="208"/>
-      <c r="D98" s="208"/>
-      <c r="E98" s="208"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="208"/>
-      <c r="B99" s="208"/>
-      <c r="C99" s="208"/>
-      <c r="D99" s="208"/>
-      <c r="E99" s="208"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="208"/>
-      <c r="B100" s="208"/>
-      <c r="C100" s="208"/>
-      <c r="D100" s="208"/>
-      <c r="E100" s="208"/>
+    <row r="97" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="189"/>
+      <c r="B97" s="189"/>
+      <c r="C97" s="189"/>
+      <c r="D97" s="189"/>
+      <c r="E97" s="189"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="189"/>
+      <c r="B98" s="189"/>
+      <c r="C98" s="189"/>
+      <c r="D98" s="189"/>
+      <c r="E98" s="189"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="189"/>
+      <c r="B99" s="189"/>
+      <c r="C99" s="189"/>
+      <c r="D99" s="189"/>
+      <c r="E99" s="189"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="189"/>
+      <c r="B100" s="189"/>
+      <c r="C100" s="189"/>
+      <c r="D100" s="189"/>
+      <c r="E100" s="189"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A97:E100"/>
-    <mergeCell ref="A91:C92"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A42:B42"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
@@ -2937,6 +2845,12 @@
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A97:E100"/>
+    <mergeCell ref="A91:C92"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A42:B42"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2947,47 +2861,47 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="4.42578125" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="1" max="2" width="4.44140625" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" customWidth="1"/>
     <col min="15" max="15" width="12" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" customWidth="1"/>
-    <col min="17" max="17" width="7.42578125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.44140625" customWidth="1"/>
+    <col min="17" max="17" width="7.44140625" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="112"/>
       <c r="B1" s="113"/>
       <c r="C1" s="114"/>
       <c r="D1" s="114"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211"/>
-      <c r="L1" s="211"/>
-      <c r="M1" s="211"/>
-      <c r="N1" s="211"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="205"/>
+      <c r="G1" s="205"/>
+      <c r="H1" s="205"/>
+      <c r="I1" s="205"/>
+      <c r="J1" s="205"/>
+      <c r="K1" s="205"/>
+      <c r="L1" s="205"/>
+      <c r="M1" s="205"/>
+      <c r="N1" s="205"/>
       <c r="O1" s="113"/>
       <c r="P1" s="115"/>
     </row>
-    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="116"/>
       <c r="B2" s="117"/>
       <c r="C2" s="118"/>
@@ -3014,7 +2928,7 @@
       <c r="P2" s="124"/>
       <c r="Q2" s="19"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="116"/>
       <c r="B3" s="117"/>
       <c r="C3" s="118"/>
@@ -3033,212 +2947,212 @@
       <c r="P3" s="124"/>
       <c r="Q3" s="19"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="222" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="212" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="223"/>
-      <c r="C4" s="223"/>
-      <c r="D4" s="223"/>
-      <c r="E4" s="223"/>
-      <c r="F4" s="223"/>
-      <c r="G4" s="223"/>
-      <c r="H4" s="223"/>
-      <c r="I4" s="223"/>
-      <c r="J4" s="223"/>
-      <c r="K4" s="223"/>
-      <c r="L4" s="223"/>
-      <c r="M4" s="223"/>
-      <c r="N4" s="223"/>
-      <c r="O4" s="223"/>
-      <c r="P4" s="224"/>
+      <c r="B4" s="213"/>
+      <c r="C4" s="213"/>
+      <c r="D4" s="213"/>
+      <c r="E4" s="213"/>
+      <c r="F4" s="213"/>
+      <c r="G4" s="213"/>
+      <c r="H4" s="213"/>
+      <c r="I4" s="213"/>
+      <c r="J4" s="213"/>
+      <c r="K4" s="213"/>
+      <c r="L4" s="213"/>
+      <c r="M4" s="213"/>
+      <c r="N4" s="213"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="214"/>
       <c r="Q4" s="19"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="225"/>
-      <c r="B5" s="226"/>
-      <c r="C5" s="226"/>
-      <c r="D5" s="226"/>
-      <c r="E5" s="226"/>
-      <c r="F5" s="226"/>
-      <c r="G5" s="226"/>
-      <c r="H5" s="226"/>
-      <c r="I5" s="226"/>
-      <c r="J5" s="226"/>
-      <c r="K5" s="226"/>
-      <c r="L5" s="226"/>
-      <c r="M5" s="226"/>
-      <c r="N5" s="226"/>
-      <c r="O5" s="226"/>
-      <c r="P5" s="227"/>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="215"/>
+      <c r="B5" s="216"/>
+      <c r="C5" s="216"/>
+      <c r="D5" s="216"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="216"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="216"/>
+      <c r="K5" s="216"/>
+      <c r="L5" s="216"/>
+      <c r="M5" s="216"/>
+      <c r="N5" s="216"/>
+      <c r="O5" s="216"/>
+      <c r="P5" s="217"/>
       <c r="Q5" s="19"/>
     </row>
-    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="225"/>
-      <c r="B6" s="226"/>
-      <c r="C6" s="226"/>
-      <c r="D6" s="226"/>
-      <c r="E6" s="226"/>
-      <c r="F6" s="226"/>
-      <c r="G6" s="226"/>
-      <c r="H6" s="226"/>
-      <c r="I6" s="226"/>
-      <c r="J6" s="226"/>
-      <c r="K6" s="226"/>
-      <c r="L6" s="226"/>
-      <c r="M6" s="226"/>
-      <c r="N6" s="226"/>
-      <c r="O6" s="226"/>
-      <c r="P6" s="227"/>
+    <row r="6" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="215"/>
+      <c r="B6" s="216"/>
+      <c r="C6" s="216"/>
+      <c r="D6" s="216"/>
+      <c r="E6" s="216"/>
+      <c r="F6" s="216"/>
+      <c r="G6" s="216"/>
+      <c r="H6" s="216"/>
+      <c r="I6" s="216"/>
+      <c r="J6" s="216"/>
+      <c r="K6" s="216"/>
+      <c r="L6" s="216"/>
+      <c r="M6" s="216"/>
+      <c r="N6" s="216"/>
+      <c r="O6" s="216"/>
+      <c r="P6" s="217"/>
       <c r="Q6" s="19"/>
     </row>
-    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="225"/>
-      <c r="B7" s="226"/>
-      <c r="C7" s="226"/>
-      <c r="D7" s="226"/>
-      <c r="E7" s="226"/>
-      <c r="F7" s="226"/>
-      <c r="G7" s="226"/>
-      <c r="H7" s="226"/>
-      <c r="I7" s="226"/>
-      <c r="J7" s="226"/>
-      <c r="K7" s="226"/>
-      <c r="L7" s="226"/>
-      <c r="M7" s="226"/>
-      <c r="N7" s="226"/>
-      <c r="O7" s="226"/>
-      <c r="P7" s="227"/>
+    <row r="7" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="215"/>
+      <c r="B7" s="216"/>
+      <c r="C7" s="216"/>
+      <c r="D7" s="216"/>
+      <c r="E7" s="216"/>
+      <c r="F7" s="216"/>
+      <c r="G7" s="216"/>
+      <c r="H7" s="216"/>
+      <c r="I7" s="216"/>
+      <c r="J7" s="216"/>
+      <c r="K7" s="216"/>
+      <c r="L7" s="216"/>
+      <c r="M7" s="216"/>
+      <c r="N7" s="216"/>
+      <c r="O7" s="216"/>
+      <c r="P7" s="217"/>
       <c r="Q7" s="19"/>
     </row>
-    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="228"/>
-      <c r="B8" s="229"/>
-      <c r="C8" s="229"/>
-      <c r="D8" s="229"/>
-      <c r="E8" s="229"/>
-      <c r="F8" s="229"/>
-      <c r="G8" s="229"/>
-      <c r="H8" s="229"/>
-      <c r="I8" s="229"/>
-      <c r="J8" s="229"/>
-      <c r="K8" s="229"/>
-      <c r="L8" s="229"/>
-      <c r="M8" s="229"/>
-      <c r="N8" s="229"/>
-      <c r="O8" s="229"/>
-      <c r="P8" s="230"/>
-    </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="233" t="s">
+    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="218"/>
+      <c r="B8" s="219"/>
+      <c r="C8" s="219"/>
+      <c r="D8" s="219"/>
+      <c r="E8" s="219"/>
+      <c r="F8" s="219"/>
+      <c r="G8" s="219"/>
+      <c r="H8" s="219"/>
+      <c r="I8" s="219"/>
+      <c r="J8" s="219"/>
+      <c r="K8" s="219"/>
+      <c r="L8" s="219"/>
+      <c r="M8" s="219"/>
+      <c r="N8" s="219"/>
+      <c r="O8" s="219"/>
+      <c r="P8" s="220"/>
+    </row>
+    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="223" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="234"/>
-      <c r="C9" s="234"/>
-      <c r="D9" s="234"/>
-      <c r="E9" s="234"/>
-      <c r="F9" s="234"/>
-      <c r="G9" s="234"/>
-      <c r="H9" s="234"/>
-      <c r="I9" s="234"/>
-      <c r="J9" s="234"/>
-      <c r="K9" s="234"/>
-      <c r="L9" s="234"/>
-      <c r="M9" s="234"/>
-      <c r="N9" s="234"/>
-      <c r="O9" s="234"/>
-      <c r="P9" s="234"/>
-    </row>
-    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="235" t="s">
+      <c r="B9" s="224"/>
+      <c r="C9" s="224"/>
+      <c r="D9" s="224"/>
+      <c r="E9" s="224"/>
+      <c r="F9" s="224"/>
+      <c r="G9" s="224"/>
+      <c r="H9" s="224"/>
+      <c r="I9" s="224"/>
+      <c r="J9" s="224"/>
+      <c r="K9" s="224"/>
+      <c r="L9" s="224"/>
+      <c r="M9" s="224"/>
+      <c r="N9" s="224"/>
+      <c r="O9" s="224"/>
+      <c r="P9" s="224"/>
+    </row>
+    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="225" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="235"/>
-      <c r="C10" s="235"/>
-      <c r="D10" s="235"/>
-      <c r="E10" s="235"/>
-      <c r="F10" s="235"/>
-      <c r="G10" s="235"/>
-      <c r="H10" s="235"/>
-      <c r="I10" s="235"/>
-      <c r="J10" s="235"/>
-      <c r="K10" s="235"/>
-      <c r="L10" s="235"/>
-      <c r="M10" s="235"/>
-      <c r="N10" s="235"/>
-      <c r="O10" s="235"/>
-      <c r="P10" s="235"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="216" t="s">
+      <c r="B10" s="225"/>
+      <c r="C10" s="225"/>
+      <c r="D10" s="225"/>
+      <c r="E10" s="225"/>
+      <c r="F10" s="225"/>
+      <c r="G10" s="225"/>
+      <c r="H10" s="225"/>
+      <c r="I10" s="225"/>
+      <c r="J10" s="225"/>
+      <c r="K10" s="225"/>
+      <c r="L10" s="225"/>
+      <c r="M10" s="225"/>
+      <c r="N10" s="225"/>
+      <c r="O10" s="225"/>
+      <c r="P10" s="225"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="200" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="101"/>
-      <c r="C11" s="216" t="s">
+      <c r="C11" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="216" t="s">
+      <c r="D11" s="200" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="216" t="s">
+      <c r="E11" s="200" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="212" t="s">
+      <c r="F11" s="203" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="216" t="s">
+      <c r="G11" s="200" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="218" t="s">
+      <c r="H11" s="208" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="212" t="s">
+      <c r="I11" s="203" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="212" t="s">
+      <c r="J11" s="203" t="s">
         <v>91</v>
       </c>
-      <c r="K11" s="220" t="s">
+      <c r="K11" s="210" t="s">
         <v>92</v>
       </c>
-      <c r="L11" s="212" t="s">
+      <c r="L11" s="203" t="s">
         <v>78</v>
       </c>
-      <c r="M11" s="212" t="s">
+      <c r="M11" s="203" t="s">
         <v>123</v>
       </c>
       <c r="N11" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="214" t="s">
+      <c r="O11" s="206" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="231" t="s">
+      <c r="P11" s="221" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="217"/>
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="202"/>
       <c r="B12" s="102"/>
-      <c r="C12" s="217"/>
-      <c r="D12" s="236"/>
-      <c r="E12" s="217"/>
-      <c r="F12" s="213"/>
-      <c r="G12" s="217"/>
-      <c r="H12" s="219"/>
-      <c r="I12" s="213"/>
-      <c r="J12" s="213"/>
-      <c r="K12" s="221"/>
-      <c r="L12" s="213"/>
-      <c r="M12" s="213"/>
+      <c r="C12" s="202"/>
+      <c r="D12" s="201"/>
+      <c r="E12" s="202"/>
+      <c r="F12" s="204"/>
+      <c r="G12" s="202"/>
+      <c r="H12" s="209"/>
+      <c r="I12" s="204"/>
+      <c r="J12" s="204"/>
+      <c r="K12" s="211"/>
+      <c r="L12" s="204"/>
+      <c r="M12" s="204"/>
       <c r="N12" s="37" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="O12" s="215"/>
-      <c r="P12" s="232"/>
-    </row>
-    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O12" s="207"/>
+      <c r="P12" s="222"/>
+    </row>
+    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="40">
         <v>1</v>
       </c>
@@ -3276,27 +3190,27 @@
         <v>0</v>
       </c>
       <c r="L13" s="134">
-        <f>EDESUR!K3</f>
-        <v>29460.826927751194</v>
+        <f>EDESUR!O4</f>
+        <v>0</v>
       </c>
       <c r="M13" s="148"/>
       <c r="N13" s="133">
         <f>ROUND(SUM(H13:M13),0) + Q13</f>
-        <v>353461.01</v>
+        <v>324000.01</v>
       </c>
       <c r="O13" s="52">
         <f>ROUND(N13*6% + N13,0) + Q13</f>
-        <v>374669.01</v>
+        <v>343440.01</v>
       </c>
       <c r="P13" s="53">
         <f>ROUND(N13*3%,0) + N13</f>
-        <v>364065.01</v>
+        <v>333720.01</v>
       </c>
       <c r="Q13" s="27">
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="126">
         <v>2</v>
       </c>
@@ -3334,30 +3248,30 @@
         <v>0</v>
       </c>
       <c r="L14" s="134">
-        <f>EDESUR!K4</f>
-        <v>149105.45982222489</v>
+        <f>EDESUR!O5</f>
+        <v>131673.44765485809</v>
       </c>
       <c r="M14" s="149">
         <v>10000</v>
       </c>
       <c r="N14" s="133">
         <f t="shared" ref="N14:N35" si="4">ROUND(SUM(H14:M14),0) + Q14</f>
-        <v>337305.02</v>
+        <v>319873.02</v>
       </c>
       <c r="O14" s="131">
         <f t="shared" ref="O14:O30" si="5">ROUND(N14*6% + N14,0) + Q14</f>
-        <v>357543.02</v>
+        <v>339065.02</v>
       </c>
       <c r="P14" s="132">
         <f t="shared" ref="P14:P35" si="6">ROUND(N14*3%,0) + N14</f>
-        <v>347424.02</v>
+        <v>329469.02</v>
       </c>
       <c r="Q14" s="27">
         <f>Q13+0.01</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="40">
         <v>3</v>
       </c>
@@ -3397,28 +3311,28 @@
         <v>0</v>
       </c>
       <c r="L15" s="134">
-        <f>EDESUR!K5</f>
-        <v>13257.372117488037</v>
+        <f>EDESUR!O6</f>
+        <v>0</v>
       </c>
       <c r="M15" s="147"/>
       <c r="N15" s="133">
         <f t="shared" si="4"/>
-        <v>159057.03</v>
+        <v>145800.03</v>
       </c>
       <c r="O15" s="52">
         <f t="shared" si="5"/>
-        <v>168600.03</v>
+        <v>154548.03</v>
       </c>
       <c r="P15" s="53">
         <f t="shared" si="6"/>
-        <v>163829.03</v>
+        <v>150174.03</v>
       </c>
       <c r="Q15" s="27">
         <f t="shared" ref="Q15:Q30" si="7">Q14+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="40">
         <v>4</v>
       </c>
@@ -3458,28 +3372,28 @@
         <v>0</v>
       </c>
       <c r="L16" s="134">
-        <f>EDESUR!K7</f>
-        <v>16203.454810263158</v>
+        <f>EDESUR!O8</f>
+        <v>0</v>
       </c>
       <c r="M16" s="148"/>
       <c r="N16" s="133">
         <f t="shared" si="4"/>
-        <v>188042.04</v>
+        <v>171838.04</v>
       </c>
       <c r="O16" s="52">
         <f t="shared" si="5"/>
-        <v>199325.04</v>
+        <v>182148.04</v>
       </c>
       <c r="P16" s="53">
         <f t="shared" si="6"/>
-        <v>193683.04</v>
+        <v>176993.04</v>
       </c>
       <c r="Q16" s="27">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="126">
         <v>5</v>
       </c>
@@ -3519,23 +3433,23 @@
         <v>0</v>
       </c>
       <c r="L17" s="134">
-        <f>EDESUR!K8</f>
-        <v>16203.454810263158</v>
+        <f>EDESUR!O9</f>
+        <v>0</v>
       </c>
       <c r="M17" s="149">
         <v>0</v>
       </c>
       <c r="N17" s="133">
         <f t="shared" si="4"/>
-        <v>194403.05</v>
+        <v>178200.05</v>
       </c>
       <c r="O17" s="131">
         <f t="shared" si="5"/>
-        <v>206067.05</v>
+        <v>188892.05</v>
       </c>
       <c r="P17" s="132">
         <f t="shared" si="6"/>
-        <v>200235.05</v>
+        <v>183546.05</v>
       </c>
       <c r="Q17" s="27">
         <f t="shared" si="7"/>
@@ -3545,7 +3459,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <v>6</v>
       </c>
@@ -3585,28 +3499,28 @@
         <v>0</v>
       </c>
       <c r="L18" s="134">
-        <f>EDESUR!K9</f>
-        <v>13257.372117488037</v>
+        <f>EDESUR!O10</f>
+        <v>0</v>
       </c>
       <c r="M18" s="148"/>
       <c r="N18" s="133">
         <f t="shared" si="4"/>
-        <v>159057.06</v>
+        <v>145800.06</v>
       </c>
       <c r="O18" s="52">
         <f t="shared" si="5"/>
-        <v>168600.06</v>
+        <v>154548.06</v>
       </c>
       <c r="P18" s="53">
         <f t="shared" si="6"/>
-        <v>163829.06</v>
+        <v>150174.06</v>
       </c>
       <c r="Q18" s="27">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="126">
         <v>7</v>
       </c>
@@ -3646,28 +3560,28 @@
         <v>0</v>
       </c>
       <c r="L19" s="134">
-        <f>EDESUR!K6</f>
-        <v>13257.372117488037</v>
+        <f>EDESUR!O7</f>
+        <v>0</v>
       </c>
       <c r="M19" s="148"/>
       <c r="N19" s="133">
         <f t="shared" si="4"/>
-        <v>159057.07</v>
+        <v>145800.07</v>
       </c>
       <c r="O19" s="131">
         <f t="shared" si="5"/>
-        <v>168600.07</v>
+        <v>154548.07</v>
       </c>
       <c r="P19" s="132">
         <f t="shared" si="6"/>
-        <v>163829.07</v>
+        <v>150174.07</v>
       </c>
       <c r="Q19" s="27">
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="126">
         <v>8</v>
       </c>
@@ -3707,28 +3621,28 @@
         <v>0</v>
       </c>
       <c r="L20" s="134">
-        <f>EDESUR!K11</f>
-        <v>80448.24873370814</v>
+        <f>EDESUR!O12</f>
+        <v>77012.898489841638</v>
       </c>
       <c r="M20" s="148"/>
       <c r="N20" s="133">
         <f t="shared" si="4"/>
-        <v>258648.08</v>
+        <v>255213.08</v>
       </c>
       <c r="O20" s="131">
         <f t="shared" si="5"/>
-        <v>274167.08</v>
+        <v>270526.08000000002</v>
       </c>
       <c r="P20" s="132">
         <f t="shared" si="6"/>
-        <v>266407.07999999996</v>
+        <v>262869.07999999996</v>
       </c>
       <c r="Q20" s="27">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="126">
         <v>9</v>
       </c>
@@ -3769,30 +3683,30 @@
         <v>0</v>
       </c>
       <c r="L21" s="134">
-        <f>EDESUR!K12</f>
-        <v>16203.454810263158</v>
+        <f>EDESUR!O13</f>
+        <v>0</v>
       </c>
       <c r="M21" s="148">
         <v>0</v>
       </c>
       <c r="N21" s="133">
         <f t="shared" si="4"/>
-        <v>194403.09</v>
+        <v>178200.09</v>
       </c>
       <c r="O21" s="52">
         <f t="shared" si="5"/>
-        <v>206067.09</v>
+        <v>188892.09</v>
       </c>
       <c r="P21" s="53">
         <f t="shared" si="6"/>
-        <v>200235.09</v>
+        <v>183546.09</v>
       </c>
       <c r="Q21" s="27">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="126">
         <v>10</v>
       </c>
@@ -3832,28 +3746,28 @@
         <v>0</v>
       </c>
       <c r="L22" s="134">
-        <f>EDESUR!K13</f>
-        <v>13257.372117488037</v>
+        <f>EDESUR!O14</f>
+        <v>0</v>
       </c>
       <c r="M22" s="148"/>
       <c r="N22" s="133">
         <f t="shared" si="4"/>
-        <v>1069.0999999999999</v>
+        <v>-12187.9</v>
       </c>
       <c r="O22" s="52">
         <f t="shared" si="5"/>
-        <v>1133.0999999999999</v>
+        <v>-12918.9</v>
       </c>
       <c r="P22" s="53">
         <f t="shared" si="6"/>
-        <v>1101.0999999999999</v>
+        <v>-12553.9</v>
       </c>
       <c r="Q22" s="27">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="40">
         <v>11</v>
       </c>
@@ -3891,21 +3805,21 @@
         <v>0</v>
       </c>
       <c r="L23" s="134">
-        <f>EDESUR!K10</f>
-        <v>13257.372117488037</v>
+        <f>EDESUR!O11</f>
+        <v>0</v>
       </c>
       <c r="M23" s="148"/>
       <c r="N23" s="133">
         <f t="shared" si="4"/>
-        <v>159057.10999999999</v>
+        <v>145800.10999999999</v>
       </c>
       <c r="O23" s="52">
         <f t="shared" si="5"/>
-        <v>168601.11</v>
+        <v>154548.10999999999</v>
       </c>
       <c r="P23" s="53">
         <f t="shared" si="6"/>
-        <v>163829.10999999999</v>
+        <v>150174.10999999999</v>
       </c>
       <c r="Q23" s="27">
         <f t="shared" si="7"/>
@@ -3915,7 +3829,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="40">
         <v>12</v>
       </c>
@@ -3955,28 +3869,28 @@
         <v>0</v>
       </c>
       <c r="L24" s="134">
-        <f>EDESUR!K15</f>
-        <v>16203.454810263158</v>
+        <f>EDESUR!O16</f>
+        <v>0</v>
       </c>
       <c r="M24" s="148"/>
       <c r="N24" s="133">
         <f t="shared" si="4"/>
-        <v>194403.12</v>
+        <v>178200.12</v>
       </c>
       <c r="O24" s="52">
         <f t="shared" si="5"/>
-        <v>206067.12</v>
+        <v>188892.12</v>
       </c>
       <c r="P24" s="53">
         <f t="shared" si="6"/>
-        <v>200235.12</v>
+        <v>183546.12</v>
       </c>
       <c r="Q24" s="27">
         <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="40">
         <v>13</v>
       </c>
@@ -4015,28 +3929,28 @@
         <v>0</v>
       </c>
       <c r="L25" s="134">
-        <f>EDESUR!K16</f>
-        <v>16203.454810263158</v>
+        <f>EDESUR!O17</f>
+        <v>0</v>
       </c>
       <c r="M25" s="148"/>
       <c r="N25" s="133">
         <f t="shared" si="4"/>
-        <v>188571.13</v>
+        <v>172368.13</v>
       </c>
       <c r="O25" s="52">
         <f t="shared" si="5"/>
-        <v>199885.13</v>
+        <v>182710.13</v>
       </c>
       <c r="P25" s="53">
         <f t="shared" si="6"/>
-        <v>194228.13</v>
+        <v>177539.13</v>
       </c>
       <c r="Q25" s="27">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="126">
         <v>14</v>
       </c>
@@ -4074,28 +3988,28 @@
         <v>0</v>
       </c>
       <c r="L26" s="134">
-        <f>EDESUR!K17</f>
-        <v>13257.372117488037</v>
+        <f>EDESUR!O18</f>
+        <v>0</v>
       </c>
       <c r="M26" s="149"/>
       <c r="N26" s="133">
         <f t="shared" si="4"/>
-        <v>159057.14000000001</v>
+        <v>145800.14000000001</v>
       </c>
       <c r="O26" s="131">
         <f t="shared" si="5"/>
-        <v>168601.14</v>
+        <v>154548.14000000001</v>
       </c>
       <c r="P26" s="132">
         <f t="shared" si="6"/>
-        <v>163829.14000000001</v>
+        <v>150174.14000000001</v>
       </c>
       <c r="Q26" s="27">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="40">
         <v>15</v>
       </c>
@@ -4133,28 +4047,28 @@
         <v>0</v>
       </c>
       <c r="L27" s="134">
-        <f>EDESUR!K14</f>
-        <v>13257.372117488037</v>
+        <f>EDESUR!O15</f>
+        <v>0</v>
       </c>
       <c r="M27" s="148"/>
       <c r="N27" s="133">
         <f t="shared" si="4"/>
-        <v>159057.15</v>
+        <v>145800.15</v>
       </c>
       <c r="O27" s="52">
         <f t="shared" si="5"/>
-        <v>168601.15</v>
+        <v>154548.15</v>
       </c>
       <c r="P27" s="53">
         <f t="shared" si="6"/>
-        <v>163829.15</v>
+        <v>150174.15</v>
       </c>
       <c r="Q27" s="27">
         <f t="shared" si="7"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="126">
         <v>16</v>
       </c>
@@ -4194,28 +4108,28 @@
         <v>0</v>
       </c>
       <c r="L28" s="134">
-        <f>EDESUR!K20</f>
-        <v>1718.548237452153</v>
+        <f>EDESUR!O22</f>
+        <v>163.15059560726027</v>
       </c>
       <c r="M28" s="148"/>
       <c r="N28" s="133">
         <f t="shared" si="4"/>
-        <v>20619.16</v>
+        <v>19063.16</v>
       </c>
       <c r="O28" s="52">
         <f t="shared" si="5"/>
-        <v>21856.16</v>
+        <v>20207.16</v>
       </c>
       <c r="P28" s="53">
         <f t="shared" si="6"/>
-        <v>21238.16</v>
+        <v>19635.16</v>
       </c>
       <c r="Q28" s="27">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="126">
         <v>17</v>
       </c>
@@ -4253,28 +4167,28 @@
         <v>0</v>
       </c>
       <c r="L29" s="134">
-        <f>EDESUR!K21</f>
-        <v>1473.0413463875598</v>
+        <f>EDESUR!O23</f>
+        <v>139.84336766336594</v>
       </c>
       <c r="M29" s="148"/>
       <c r="N29" s="133">
         <f t="shared" si="4"/>
-        <v>17673.169999999998</v>
+        <v>16340.17</v>
       </c>
       <c r="O29" s="52">
         <f t="shared" si="5"/>
-        <v>18734.169999999998</v>
+        <v>17321.169999999998</v>
       </c>
       <c r="P29" s="53">
         <f t="shared" si="6"/>
-        <v>18203.169999999998</v>
+        <v>16830.169999999998</v>
       </c>
       <c r="Q29" s="27">
         <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="40">
         <v>18</v>
       </c>
@@ -4312,28 +4226,28 @@
         <v>0</v>
       </c>
       <c r="L30" s="134">
-        <f>EDESUR!K22</f>
-        <v>1473.0413463875598</v>
+        <f>EDESUR!O24</f>
+        <v>139.84336766336594</v>
       </c>
       <c r="M30" s="148"/>
       <c r="N30" s="133">
         <f t="shared" si="4"/>
-        <v>17673.18</v>
+        <v>16340.18</v>
       </c>
       <c r="O30" s="52">
         <f t="shared" si="5"/>
-        <v>18734.18</v>
+        <v>17321.18</v>
       </c>
       <c r="P30" s="53">
         <f t="shared" si="6"/>
-        <v>18203.18</v>
+        <v>16830.18</v>
       </c>
       <c r="Q30" s="27">
         <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="126">
         <v>19</v>
       </c>
@@ -4371,25 +4285,25 @@
         <v>0</v>
       </c>
       <c r="L31" s="134">
-        <f>EDESUR!K23</f>
-        <v>1473.0413463875598</v>
+        <f>EDESUR!O25</f>
+        <v>139.84336766336594</v>
       </c>
       <c r="M31" s="149"/>
       <c r="N31" s="133">
         <f t="shared" si="4"/>
-        <v>17673.189999999999</v>
+        <v>16340.19</v>
       </c>
       <c r="O31" s="131"/>
       <c r="P31" s="132">
         <f t="shared" si="6"/>
-        <v>18203.189999999999</v>
+        <v>16830.190000000002</v>
       </c>
       <c r="Q31" s="27">
         <f>Q30+0.01</f>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A32" s="54">
         <v>20</v>
       </c>
@@ -4429,25 +4343,25 @@
         <v>0</v>
       </c>
       <c r="L32" s="134">
-        <f>EDESUR!K24</f>
-        <v>1473.0413463875598</v>
+        <f>EDESUR!O26</f>
+        <v>139.84336766336594</v>
       </c>
       <c r="M32" s="148"/>
       <c r="N32" s="133">
         <f t="shared" si="4"/>
-        <v>17673.2</v>
+        <v>16340.2</v>
       </c>
       <c r="O32" s="52"/>
       <c r="P32" s="53">
         <f t="shared" si="6"/>
-        <v>18203.2</v>
+        <v>16830.2</v>
       </c>
       <c r="Q32" s="27">
         <f t="shared" ref="Q32:Q35" si="9">Q31+0.01</f>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="54">
         <v>21</v>
       </c>
@@ -4487,25 +4401,25 @@
         <v>0</v>
       </c>
       <c r="L33" s="134">
-        <f>EDESUR!K25</f>
-        <v>736.52067319377988</v>
+        <f>EDESUR!O27</f>
+        <v>69.921683831682969</v>
       </c>
       <c r="M33" s="148"/>
       <c r="N33" s="133">
         <f t="shared" si="4"/>
-        <v>8837.2099999999991</v>
+        <v>8170.21</v>
       </c>
       <c r="O33" s="52"/>
       <c r="P33" s="53">
         <f t="shared" si="6"/>
-        <v>9102.2099999999991</v>
+        <v>8415.2099999999991</v>
       </c>
       <c r="Q33" s="27">
         <f t="shared" si="9"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="55">
         <v>22</v>
       </c>
@@ -4522,7 +4436,7 @@
       <c r="F34" s="56">
         <v>8837.2199999999993</v>
       </c>
-      <c r="G34" s="243">
+      <c r="G34" s="179">
         <f t="shared" ref="G34" si="10">F34</f>
         <v>8837.2199999999993</v>
       </c>
@@ -4543,25 +4457,25 @@
         <v>0</v>
       </c>
       <c r="L34" s="134">
-        <f>EDESUR!K26</f>
-        <v>736.52067319377988</v>
+        <f>EDESUR!O28</f>
+        <v>69.921683831682969</v>
       </c>
       <c r="M34" s="148"/>
       <c r="N34" s="133">
         <f t="shared" si="4"/>
-        <v>8837.2199999999993</v>
+        <v>8170.22</v>
       </c>
       <c r="O34" s="52"/>
       <c r="P34" s="53">
         <f t="shared" si="6"/>
-        <v>9102.2199999999993</v>
+        <v>8415.2200000000012</v>
       </c>
       <c r="Q34" s="27">
         <f t="shared" si="9"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="40">
         <v>23</v>
       </c>
@@ -4601,25 +4515,25 @@
         <v>0</v>
       </c>
       <c r="L35" s="134">
-        <f>EDESUR!K27</f>
-        <v>736.52067319377988</v>
+        <f>EDESUR!O29</f>
+        <v>69.921683831682969</v>
       </c>
       <c r="M35" s="148"/>
       <c r="N35" s="133">
         <f t="shared" si="4"/>
-        <v>8837.23</v>
+        <v>8170.23</v>
       </c>
       <c r="O35" s="58"/>
       <c r="P35" s="53">
         <f t="shared" si="6"/>
-        <v>9102.23</v>
+        <v>8415.23</v>
       </c>
       <c r="Q35" s="27">
         <f t="shared" si="9"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="59"/>
       <c r="B36" s="59"/>
       <c r="C36" s="60"/>
@@ -4654,122 +4568,116 @@
       </c>
       <c r="L36" s="61">
         <f>SUM(L13:L35)</f>
-        <v>442653.69000000029</v>
+        <v>209618.6352624555</v>
       </c>
       <c r="M36" s="61"/>
       <c r="N36" s="61">
         <f>SUM(N13:N35)</f>
-        <v>2982471.7600000012</v>
+        <v>2749439.7600000012</v>
       </c>
       <c r="O36" s="61">
         <f t="shared" si="11"/>
-        <v>3095851.7100000004</v>
+        <v>2853784.7100000009</v>
       </c>
       <c r="P36" s="61">
         <f>SUM(P13:P35)</f>
-        <v>3071945.7600000012</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2831920.7600000012</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="33"/>
       <c r="D37" s="33"/>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="208" t="str">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="189" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="208"/>
-      <c r="E39" s="208"/>
-      <c r="F39" s="208"/>
-      <c r="G39" s="208"/>
-      <c r="H39" s="208"/>
-      <c r="I39" s="208"/>
-      <c r="J39" s="208"/>
-      <c r="K39" s="208"/>
-      <c r="L39" s="208"/>
-      <c r="M39" s="208"/>
-      <c r="N39" s="208"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="208"/>
-      <c r="D40" s="208"/>
-      <c r="E40" s="208"/>
-      <c r="F40" s="208"/>
-      <c r="G40" s="208"/>
-      <c r="H40" s="208"/>
-      <c r="I40" s="208"/>
-      <c r="J40" s="208"/>
-      <c r="K40" s="208"/>
-      <c r="L40" s="208"/>
-      <c r="M40" s="208"/>
-      <c r="N40" s="208"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="208"/>
-      <c r="D41" s="208"/>
-      <c r="E41" s="208"/>
-      <c r="F41" s="208"/>
-      <c r="G41" s="208"/>
-      <c r="H41" s="208"/>
-      <c r="I41" s="208"/>
-      <c r="J41" s="208"/>
-      <c r="K41" s="208"/>
-      <c r="L41" s="208"/>
-      <c r="M41" s="208"/>
-      <c r="N41" s="208"/>
-    </row>
-    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="208"/>
-      <c r="D42" s="208"/>
-      <c r="E42" s="208"/>
-      <c r="F42" s="208"/>
-      <c r="G42" s="208"/>
-      <c r="H42" s="208"/>
-      <c r="I42" s="208"/>
-      <c r="J42" s="208"/>
-      <c r="K42" s="208"/>
-      <c r="L42" s="208"/>
-      <c r="M42" s="208"/>
-      <c r="N42" s="208"/>
-    </row>
-    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="208"/>
-      <c r="D43" s="208"/>
-      <c r="E43" s="208"/>
-      <c r="F43" s="208"/>
-      <c r="G43" s="208"/>
-      <c r="H43" s="208"/>
-      <c r="I43" s="208"/>
-      <c r="J43" s="208"/>
-      <c r="K43" s="208"/>
-      <c r="L43" s="208"/>
-      <c r="M43" s="208"/>
-      <c r="N43" s="208"/>
-    </row>
-    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="208"/>
-      <c r="D44" s="208"/>
-      <c r="E44" s="208"/>
-      <c r="F44" s="208"/>
-      <c r="G44" s="208"/>
-      <c r="H44" s="208"/>
-      <c r="I44" s="208"/>
-      <c r="J44" s="208"/>
-      <c r="K44" s="208"/>
-      <c r="L44" s="208"/>
-      <c r="M44" s="208"/>
-      <c r="N44" s="208"/>
+      <c r="D39" s="189"/>
+      <c r="E39" s="189"/>
+      <c r="F39" s="189"/>
+      <c r="G39" s="189"/>
+      <c r="H39" s="189"/>
+      <c r="I39" s="189"/>
+      <c r="J39" s="189"/>
+      <c r="K39" s="189"/>
+      <c r="L39" s="189"/>
+      <c r="M39" s="189"/>
+      <c r="N39" s="189"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="189"/>
+      <c r="D40" s="189"/>
+      <c r="E40" s="189"/>
+      <c r="F40" s="189"/>
+      <c r="G40" s="189"/>
+      <c r="H40" s="189"/>
+      <c r="I40" s="189"/>
+      <c r="J40" s="189"/>
+      <c r="K40" s="189"/>
+      <c r="L40" s="189"/>
+      <c r="M40" s="189"/>
+      <c r="N40" s="189"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="189"/>
+      <c r="D41" s="189"/>
+      <c r="E41" s="189"/>
+      <c r="F41" s="189"/>
+      <c r="G41" s="189"/>
+      <c r="H41" s="189"/>
+      <c r="I41" s="189"/>
+      <c r="J41" s="189"/>
+      <c r="K41" s="189"/>
+      <c r="L41" s="189"/>
+      <c r="M41" s="189"/>
+      <c r="N41" s="189"/>
+    </row>
+    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="189"/>
+      <c r="D42" s="189"/>
+      <c r="E42" s="189"/>
+      <c r="F42" s="189"/>
+      <c r="G42" s="189"/>
+      <c r="H42" s="189"/>
+      <c r="I42" s="189"/>
+      <c r="J42" s="189"/>
+      <c r="K42" s="189"/>
+      <c r="L42" s="189"/>
+      <c r="M42" s="189"/>
+      <c r="N42" s="189"/>
+    </row>
+    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C43" s="189"/>
+      <c r="D43" s="189"/>
+      <c r="E43" s="189"/>
+      <c r="F43" s="189"/>
+      <c r="G43" s="189"/>
+      <c r="H43" s="189"/>
+      <c r="I43" s="189"/>
+      <c r="J43" s="189"/>
+      <c r="K43" s="189"/>
+      <c r="L43" s="189"/>
+      <c r="M43" s="189"/>
+      <c r="N43" s="189"/>
+    </row>
+    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C44" s="189"/>
+      <c r="D44" s="189"/>
+      <c r="E44" s="189"/>
+      <c r="F44" s="189"/>
+      <c r="G44" s="189"/>
+      <c r="H44" s="189"/>
+      <c r="I44" s="189"/>
+      <c r="J44" s="189"/>
+      <c r="K44" s="189"/>
+      <c r="L44" s="189"/>
+      <c r="M44" s="189"/>
+      <c r="N44" s="189"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C39:N44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="M11:M12"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4783,6 +4691,12 @@
     <mergeCell ref="A9:P9"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="L11:L12"/>
+    <mergeCell ref="C39:N44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="M11:M12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4790,1000 +4704,929 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B474AF3-BA14-4AC3-BE41-D99CD4C43EE8}">
-  <dimension ref="C3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFC03CC8-EEB1-4121-A90D-748455B927ED}">
+  <dimension ref="B2:O32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" customWidth="1"/>
+    <col min="7" max="7" width="1.77734375" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" customWidth="1"/>
+    <col min="9" max="9" width="14.21875" customWidth="1"/>
+    <col min="10" max="10" width="1.77734375" customWidth="1"/>
+    <col min="11" max="11" width="19.5546875" style="109" customWidth="1"/>
+    <col min="12" max="12" width="2.109375" customWidth="1"/>
+    <col min="13" max="13" width="19.77734375" style="110" customWidth="1"/>
+    <col min="14" max="14" width="2" customWidth="1"/>
+    <col min="15" max="15" width="15.33203125" style="176" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C3" s="199" t="s">
-        <v>144</v>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="D2" s="228" t="s">
+        <v>147</v>
+      </c>
+      <c r="E2" s="228"/>
+      <c r="F2" s="228"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="229" t="s">
+        <v>148</v>
+      </c>
+      <c r="I2" s="230"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="107" t="s">
+        <v>149</v>
+      </c>
+      <c r="M2" s="231" t="s">
+        <v>150</v>
+      </c>
+      <c r="O2" s="107" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B3" s="106" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="106" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="106" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="106" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="107" t="s">
+        <v>128</v>
+      </c>
+      <c r="H3" s="106" t="s">
+        <v>152</v>
+      </c>
+      <c r="I3" s="171" t="s">
+        <v>129</v>
+      </c>
+      <c r="K3" s="106"/>
+      <c r="M3" s="108"/>
+      <c r="O3" s="107"/>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B4" s="232">
+        <v>1</v>
+      </c>
+      <c r="C4" s="232" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="233">
+        <v>0</v>
+      </c>
+      <c r="E4" s="234">
+        <v>0</v>
+      </c>
+      <c r="F4" s="235">
+        <v>0</v>
+      </c>
+      <c r="H4" s="172">
+        <v>0.12</v>
+      </c>
+      <c r="I4" s="236">
+        <v>2796.8673532673188</v>
+      </c>
+      <c r="K4" s="150">
+        <f>I4+F4</f>
+        <v>2796.8673532673188</v>
+      </c>
+      <c r="M4" s="237">
+        <f>K4</f>
+        <v>2796.8673532673188</v>
+      </c>
+      <c r="O4" s="150">
+        <f>K4-M4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B5" s="106">
+        <v>1</v>
+      </c>
+      <c r="C5" s="106" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="174">
+        <v>344.5</v>
+      </c>
+      <c r="E5" s="234">
+        <v>0.63292302039316528</v>
+      </c>
+      <c r="F5" s="235">
+        <v>130135.17061056105</v>
+      </c>
+      <c r="H5" s="173">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="I5" s="236">
+        <v>1538.2770442970254</v>
+      </c>
+      <c r="K5" s="150">
+        <f t="shared" ref="K5:K18" si="0">I5+F5</f>
+        <v>131673.44765485809</v>
+      </c>
+      <c r="M5" s="237">
+        <v>0</v>
+      </c>
+      <c r="O5" s="150">
+        <f t="shared" ref="O5:O18" si="1">K5-M5</f>
+        <v>131673.44765485809</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B6" s="232">
+        <v>1</v>
+      </c>
+      <c r="C6" s="232" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="233">
+        <v>0</v>
+      </c>
+      <c r="E6" s="234">
+        <v>0</v>
+      </c>
+      <c r="F6" s="235">
+        <v>0</v>
+      </c>
+      <c r="H6" s="173">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I6" s="236">
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="K6" s="150">
+        <f t="shared" si="0"/>
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="M6" s="237">
+        <f t="shared" ref="M6:M18" si="2">K6</f>
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="O6" s="150">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B7" s="232">
+        <v>2</v>
+      </c>
+      <c r="C7" s="232" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="233">
+        <v>0</v>
+      </c>
+      <c r="E7" s="234">
+        <v>0</v>
+      </c>
+      <c r="F7" s="235">
+        <v>0</v>
+      </c>
+      <c r="H7" s="173">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I7" s="236">
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="K7" s="150">
+        <f t="shared" si="0"/>
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="M7" s="237">
+        <f t="shared" si="2"/>
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="O7" s="150">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B8" s="232">
+        <v>2</v>
+      </c>
+      <c r="C8" s="232" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="233">
+        <v>0</v>
+      </c>
+      <c r="E8" s="234">
+        <v>0</v>
+      </c>
+      <c r="F8" s="235">
+        <v>0</v>
+      </c>
+      <c r="H8" s="173">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="I8" s="236">
+        <v>1538.2770442970254</v>
+      </c>
+      <c r="K8" s="150">
+        <f t="shared" si="0"/>
+        <v>1538.2770442970254</v>
+      </c>
+      <c r="M8" s="237">
+        <f t="shared" si="2"/>
+        <v>1538.2770442970254</v>
+      </c>
+      <c r="O8" s="150">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B9" s="232">
+        <v>2</v>
+      </c>
+      <c r="C9" s="232" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="233">
+        <v>0</v>
+      </c>
+      <c r="E9" s="234">
+        <v>0</v>
+      </c>
+      <c r="F9" s="235">
+        <v>0</v>
+      </c>
+      <c r="H9" s="173">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="I9" s="236">
+        <v>1538.2770442970254</v>
+      </c>
+      <c r="K9" s="150">
+        <f t="shared" si="0"/>
+        <v>1538.2770442970254</v>
+      </c>
+      <c r="M9" s="237">
+        <f t="shared" si="2"/>
+        <v>1538.2770442970254</v>
+      </c>
+      <c r="O9" s="150">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B10" s="232">
+        <v>2</v>
+      </c>
+      <c r="C10" s="232" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="233">
+        <v>0</v>
+      </c>
+      <c r="E10" s="234">
+        <v>0</v>
+      </c>
+      <c r="F10" s="238">
+        <v>0</v>
+      </c>
+      <c r="H10" s="173">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I10" s="236">
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="K10" s="150">
+        <f t="shared" si="0"/>
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="M10" s="237">
+        <f t="shared" si="2"/>
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="O10" s="150">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B11" s="232">
+        <v>3</v>
+      </c>
+      <c r="C11" s="232" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="233">
+        <v>0</v>
+      </c>
+      <c r="E11" s="234">
+        <v>0</v>
+      </c>
+      <c r="F11" s="235">
+        <v>0</v>
+      </c>
+      <c r="H11" s="173">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I11" s="236">
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="K11" s="150">
+        <f t="shared" si="0"/>
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="M11" s="237">
+        <f t="shared" si="2"/>
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="O11" s="150">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B12" s="106">
+        <v>3</v>
+      </c>
+      <c r="C12" s="106" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="174">
+        <v>199.80000000000018</v>
+      </c>
+      <c r="E12" s="234">
+        <v>0.36707697960683466</v>
+      </c>
+      <c r="F12" s="235">
+        <v>75474.621445544617</v>
+      </c>
+      <c r="H12" s="173">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="I12" s="236">
+        <v>1538.2770442970254</v>
+      </c>
+      <c r="K12" s="150">
+        <f t="shared" si="0"/>
+        <v>77012.898489841638</v>
+      </c>
+      <c r="M12" s="237">
+        <v>0</v>
+      </c>
+      <c r="O12" s="150">
+        <f t="shared" si="1"/>
+        <v>77012.898489841638</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B13" s="232">
+        <v>3</v>
+      </c>
+      <c r="C13" s="232" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="233">
+        <v>0</v>
+      </c>
+      <c r="E13" s="234">
+        <v>0</v>
+      </c>
+      <c r="F13" s="235">
+        <v>0</v>
+      </c>
+      <c r="H13" s="173">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="I13" s="236">
+        <v>1538.2770442970254</v>
+      </c>
+      <c r="K13" s="150">
+        <f t="shared" si="0"/>
+        <v>1538.2770442970254</v>
+      </c>
+      <c r="M13" s="237">
+        <f t="shared" si="2"/>
+        <v>1538.2770442970254</v>
+      </c>
+      <c r="O13" s="150">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B14" s="232">
+        <v>3</v>
+      </c>
+      <c r="C14" s="232" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="233">
+        <v>0</v>
+      </c>
+      <c r="E14" s="234">
+        <v>0</v>
+      </c>
+      <c r="F14" s="235">
+        <v>0</v>
+      </c>
+      <c r="H14" s="173">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I14" s="236">
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="K14" s="150">
+        <f t="shared" si="0"/>
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="M14" s="237">
+        <f t="shared" si="2"/>
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="O14" s="150">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B15" s="232">
+        <v>4</v>
+      </c>
+      <c r="C15" s="232" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="233">
+        <v>0</v>
+      </c>
+      <c r="E15" s="234">
+        <v>0</v>
+      </c>
+      <c r="F15" s="235">
+        <v>0</v>
+      </c>
+      <c r="H15" s="173">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I15" s="236">
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="K15" s="150">
+        <f t="shared" si="0"/>
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="M15" s="237">
+        <f t="shared" si="2"/>
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="O15" s="150">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B16" s="232">
+        <v>4</v>
+      </c>
+      <c r="C16" s="232" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="233">
+        <v>0</v>
+      </c>
+      <c r="E16" s="234">
+        <v>0</v>
+      </c>
+      <c r="F16" s="235">
+        <v>0</v>
+      </c>
+      <c r="H16" s="173">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="I16" s="236">
+        <v>1538.2770442970254</v>
+      </c>
+      <c r="K16" s="150">
+        <f t="shared" si="0"/>
+        <v>1538.2770442970254</v>
+      </c>
+      <c r="M16" s="237">
+        <f t="shared" si="2"/>
+        <v>1538.2770442970254</v>
+      </c>
+      <c r="O16" s="150">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B17" s="232">
+        <v>4</v>
+      </c>
+      <c r="C17" s="232" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="233">
+        <v>0</v>
+      </c>
+      <c r="E17" s="234">
+        <v>0</v>
+      </c>
+      <c r="F17" s="235">
+        <v>0</v>
+      </c>
+      <c r="H17" s="173">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="I17" s="236">
+        <v>1538.2770442970254</v>
+      </c>
+      <c r="K17" s="150">
+        <f t="shared" si="0"/>
+        <v>1538.2770442970254</v>
+      </c>
+      <c r="M17" s="237">
+        <f t="shared" si="2"/>
+        <v>1538.2770442970254</v>
+      </c>
+      <c r="O17" s="150">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B18" s="232">
+        <v>4</v>
+      </c>
+      <c r="C18" s="232" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" s="233">
+        <v>0</v>
+      </c>
+      <c r="E18" s="234">
+        <v>0</v>
+      </c>
+      <c r="F18" s="235">
+        <v>0</v>
+      </c>
+      <c r="H18" s="173">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I18" s="236">
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="K18" s="150">
+        <f t="shared" si="0"/>
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="M18" s="237">
+        <f t="shared" si="2"/>
+        <v>1258.5903089702933</v>
+      </c>
+      <c r="O18" s="150">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B19" s="232"/>
+      <c r="C19" s="232"/>
+      <c r="D19" s="233"/>
+      <c r="E19" s="234"/>
+      <c r="F19" s="239"/>
+      <c r="H19" s="106"/>
+      <c r="I19" s="175"/>
+      <c r="K19" s="106"/>
+      <c r="M19" s="108"/>
+      <c r="O19" s="107"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B20" s="106"/>
+      <c r="C20" s="106" t="s">
+        <v>153</v>
+      </c>
+      <c r="D20" s="174">
+        <f>SUM(D4:D19)</f>
+        <v>544.30000000000018</v>
+      </c>
+      <c r="E20" s="107"/>
+      <c r="F20" s="239">
+        <f>SUM(F4:F19)</f>
+        <v>205609.79205610568</v>
+      </c>
+      <c r="H20" s="240"/>
+      <c r="I20" s="175">
+        <f>SUM(I4:I19)</f>
+        <v>22374.938826138547</v>
+      </c>
+      <c r="K20" s="150">
+        <f>SUM(K4:K19)</f>
+        <v>227984.7308822443</v>
+      </c>
+      <c r="M20" s="241">
+        <f>SUM(M4:M19)</f>
+        <v>19298.384737544497</v>
+      </c>
+      <c r="O20" s="150">
+        <f>SUM(O4:O19)</f>
+        <v>208686.34614469972</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B21" s="106"/>
+      <c r="C21" s="106"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B22" s="106" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="106">
+        <v>1</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="H22" s="173">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="I22" s="236">
+        <v>163.15059560726027</v>
+      </c>
+      <c r="K22" s="242">
+        <f>I22</f>
+        <v>163.15059560726027</v>
+      </c>
+      <c r="M22" s="243"/>
+      <c r="O22" s="150">
+        <f>K22-M22</f>
+        <v>163.15059560726027</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B23" s="106" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="106">
+        <v>2</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="H23" s="173">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="I23" s="236">
+        <v>139.84336766336594</v>
+      </c>
+      <c r="K23" s="242">
+        <f t="shared" ref="K23:K29" si="3">I23</f>
+        <v>139.84336766336594</v>
+      </c>
+      <c r="M23" s="243"/>
+      <c r="O23" s="150">
+        <f t="shared" ref="O23:O29" si="4">K23-M23</f>
+        <v>139.84336766336594</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B24" s="106" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="106">
+        <v>3</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="H24" s="173">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="I24" s="236">
+        <v>139.84336766336594</v>
+      </c>
+      <c r="K24" s="242">
+        <f t="shared" si="3"/>
+        <v>139.84336766336594</v>
+      </c>
+      <c r="M24" s="243"/>
+      <c r="O24" s="150">
+        <f t="shared" si="4"/>
+        <v>139.84336766336594</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B25" s="106" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="106">
+        <v>4</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="H25" s="173">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="I25" s="236">
+        <v>139.84336766336594</v>
+      </c>
+      <c r="K25" s="242">
+        <f t="shared" si="3"/>
+        <v>139.84336766336594</v>
+      </c>
+      <c r="M25" s="243"/>
+      <c r="O25" s="150">
+        <f t="shared" si="4"/>
+        <v>139.84336766336594</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B26" s="106" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="106">
+        <v>5</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="H26" s="173">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="I26" s="236">
+        <v>139.84336766336594</v>
+      </c>
+      <c r="K26" s="242">
+        <f t="shared" si="3"/>
+        <v>139.84336766336594</v>
+      </c>
+      <c r="M26" s="243"/>
+      <c r="O26" s="150">
+        <f t="shared" si="4"/>
+        <v>139.84336766336594</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B27" s="106" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="106">
+        <v>6</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="H27" s="173">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="I27" s="236">
+        <v>69.921683831682969</v>
+      </c>
+      <c r="K27" s="242">
+        <f t="shared" si="3"/>
+        <v>69.921683831682969</v>
+      </c>
+      <c r="M27" s="243"/>
+      <c r="O27" s="150">
+        <f t="shared" si="4"/>
+        <v>69.921683831682969</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B28" s="106" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="106">
+        <v>7</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="H28" s="173">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="I28" s="236">
+        <v>69.921683831682969</v>
+      </c>
+      <c r="K28" s="242">
+        <f t="shared" si="3"/>
+        <v>69.921683831682969</v>
+      </c>
+      <c r="M28" s="243"/>
+      <c r="O28" s="150">
+        <f t="shared" si="4"/>
+        <v>69.921683831682969</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B29" s="106" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="106">
+        <v>8</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="H29" s="173">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="I29" s="236">
+        <v>69.921683831682969</v>
+      </c>
+      <c r="K29" s="242">
+        <f t="shared" si="3"/>
+        <v>69.921683831682969</v>
+      </c>
+      <c r="M29" s="243"/>
+      <c r="O29" s="150">
+        <f t="shared" si="4"/>
+        <v>69.921683831682969</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="H30" s="107" t="s">
+        <v>130</v>
+      </c>
+      <c r="I30" s="236">
+        <f>SUM(I22:I29)</f>
+        <v>932.28911775577285</v>
+      </c>
+      <c r="K30" s="244">
+        <f>SUM(K22:K29)</f>
+        <v>932.28911775577285</v>
+      </c>
+      <c r="M30" s="241">
+        <f>SUM(M22:M29)</f>
+        <v>0</v>
+      </c>
+      <c r="O30" s="150">
+        <f>SUM(O22:O29)</f>
+        <v>932.28911775577285</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="O31" s="150"/>
+    </row>
+    <row r="32" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D32" s="226" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" s="227"/>
+      <c r="F32" s="177">
+        <v>228917.02000000002</v>
+      </c>
+      <c r="I32" s="245">
+        <f>F20+I20+I30</f>
+        <v>228917.02000000002</v>
+      </c>
+      <c r="K32" s="150">
+        <f>K20+K30</f>
+        <v>228917.02000000008</v>
+      </c>
+      <c r="M32" s="241">
+        <f>M20+M30</f>
+        <v>19298.384737544497</v>
+      </c>
+      <c r="O32" s="150">
+        <f>O20+O30</f>
+        <v>209618.6352624555</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="D32:E32"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A2E191-9409-46F3-B653-02D2C9674BEA}">
-  <dimension ref="B2:K39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" style="190" customWidth="1"/>
-    <col min="6" max="6" width="13" style="190" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" style="190" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" style="190" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="190" customWidth="1"/>
-    <col min="12" max="12" width="2.7109375" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B474AF3-BA14-4AC3-BE41-D99CD4C43EE8}">
+  <dimension ref="C3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2" s="106" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="106" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" s="172" t="s">
-        <v>126</v>
-      </c>
-      <c r="E2" s="172" t="s">
-        <v>127</v>
-      </c>
-      <c r="F2" s="106" t="s">
-        <v>128</v>
-      </c>
-      <c r="G2" s="106" t="s">
-        <v>129</v>
-      </c>
-      <c r="H2" s="107" t="s">
-        <v>130</v>
-      </c>
-      <c r="I2" s="106"/>
-      <c r="J2" s="173" t="s">
-        <v>131</v>
-      </c>
-      <c r="K2" s="107" t="s">
+    <row r="3" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C3" s="178" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="174">
-        <v>1</v>
-      </c>
-      <c r="C3" s="174" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" s="175">
-        <v>8687.5</v>
-      </c>
-      <c r="E3" s="175">
-        <v>8687.5</v>
-      </c>
-      <c r="F3" s="176">
-        <f>(E3-D3)</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="177">
-        <f>F3/F32</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="178">
-        <f>(F3/F32)*H32</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="179">
-        <v>0.12</v>
-      </c>
-      <c r="J3" s="151">
-        <f>H34*I3</f>
-        <v>29460.826927751194</v>
-      </c>
-      <c r="K3" s="150">
-        <f>H3+J3</f>
-        <v>29460.826927751194</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="180">
-        <v>1</v>
-      </c>
-      <c r="C4" s="180" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" s="181">
-        <v>4488.6000000000004</v>
-      </c>
-      <c r="E4" s="181">
-        <v>4865.1000000000004</v>
-      </c>
-      <c r="F4" s="182">
-        <f>(E4-D4)</f>
-        <v>376.5</v>
-      </c>
-      <c r="G4" s="183">
-        <f>F4/F32</f>
-        <v>0.67412712623097581</v>
-      </c>
-      <c r="H4" s="178">
-        <f>(F4/F32)*H32</f>
-        <v>132902.00501196174</v>
-      </c>
-      <c r="I4" s="184">
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="J4" s="151">
-        <f>H34*I4</f>
-        <v>16203.454810263158</v>
-      </c>
-      <c r="K4" s="150">
-        <f t="shared" ref="K4:K28" si="0">H4+J4</f>
-        <v>149105.45982222489</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="180">
-        <v>1</v>
-      </c>
-      <c r="C5" s="180" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" s="175">
-        <v>2366.38</v>
-      </c>
-      <c r="E5" s="175">
-        <v>2366.38</v>
-      </c>
-      <c r="F5" s="176">
-        <f t="shared" ref="F5:F17" si="1">(E5-D5)</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="177">
-        <f>F5/F32</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="178">
-        <f>(F5/F32)*H32</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="184">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="J5" s="151">
-        <f>H34*I5</f>
-        <v>13257.372117488037</v>
-      </c>
-      <c r="K5" s="150">
-        <f t="shared" si="0"/>
-        <v>13257.372117488037</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="174">
-        <v>2</v>
-      </c>
-      <c r="C6" s="174" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" s="175">
-        <v>3731.1</v>
-      </c>
-      <c r="E6" s="175">
-        <v>3731.1</v>
-      </c>
-      <c r="F6" s="176">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="177">
-        <f>F6/F32</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="178">
-        <f>(F6/F32)*H32</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="184">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="J6" s="151">
-        <f>H34*I6</f>
-        <v>13257.372117488037</v>
-      </c>
-      <c r="K6" s="150">
-        <f t="shared" si="0"/>
-        <v>13257.372117488037</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="174">
-        <v>2</v>
-      </c>
-      <c r="C7" s="174" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="175">
-        <v>3897.7</v>
-      </c>
-      <c r="E7" s="175">
-        <v>3897.7</v>
-      </c>
-      <c r="F7" s="176">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="177">
-        <f>F7/F32</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="178">
-        <f>(F7/F32)*H32</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="184">
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="J7" s="151">
-        <f>H34*I7</f>
-        <v>16203.454810263158</v>
-      </c>
-      <c r="K7" s="150">
-        <f t="shared" si="0"/>
-        <v>16203.454810263158</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="174">
-        <v>2</v>
-      </c>
-      <c r="C8" s="174" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" s="175">
-        <v>2956.2</v>
-      </c>
-      <c r="E8" s="175">
-        <v>2956.2</v>
-      </c>
-      <c r="F8" s="176">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G8" s="177">
-        <f>F8/F32</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="178">
-        <f>(F8/F32)*H32</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="184">
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="J8" s="151">
-        <f>H34*I8</f>
-        <v>16203.454810263158</v>
-      </c>
-      <c r="K8" s="150">
-        <f t="shared" si="0"/>
-        <v>16203.454810263158</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="174">
-        <v>2</v>
-      </c>
-      <c r="C9" s="174" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" s="175">
-        <v>3923.7</v>
-      </c>
-      <c r="E9" s="175">
-        <v>3923.7</v>
-      </c>
-      <c r="F9" s="176">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="177">
-        <f>F9/F32</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="185">
-        <f>(F9/F32)*H32</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="184">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="J9" s="151">
-        <f>H34*I9</f>
-        <v>13257.372117488037</v>
-      </c>
-      <c r="K9" s="150">
-        <f t="shared" si="0"/>
-        <v>13257.372117488037</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="174">
-        <v>3</v>
-      </c>
-      <c r="C10" s="174" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="175">
-        <v>2881.8</v>
-      </c>
-      <c r="E10" s="175">
-        <v>2881.8</v>
-      </c>
-      <c r="F10" s="176">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="177">
-        <f>F10/F32</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="178">
-        <f>(F10/F32)*H32</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="184">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="J10" s="151">
-        <f>H34*I10</f>
-        <v>13257.372117488037</v>
-      </c>
-      <c r="K10" s="150">
-        <f t="shared" si="0"/>
-        <v>13257.372117488037</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B11" s="180">
-        <v>3</v>
-      </c>
-      <c r="C11" s="180" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" s="181">
-        <v>4646</v>
-      </c>
-      <c r="E11" s="181">
-        <v>4828</v>
-      </c>
-      <c r="F11" s="182">
-        <f t="shared" si="1"/>
-        <v>182</v>
-      </c>
-      <c r="G11" s="183">
-        <f>F11/F32</f>
-        <v>0.32587287376902419</v>
-      </c>
-      <c r="H11" s="178">
-        <f>(F11/F32)*H32</f>
-        <v>64244.793923444988</v>
-      </c>
-      <c r="I11" s="184">
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="J11" s="151">
-        <f>H34*I11</f>
-        <v>16203.454810263158</v>
-      </c>
-      <c r="K11" s="150">
-        <f t="shared" si="0"/>
-        <v>80448.24873370814</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="174">
-        <v>3</v>
-      </c>
-      <c r="C12" s="174" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" s="175">
-        <v>4554.6000000000004</v>
-      </c>
-      <c r="E12" s="175">
-        <v>4554.6000000000004</v>
-      </c>
-      <c r="F12" s="176">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="177">
-        <f>F12/F32</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="178">
-        <f>(F12/F32)*H32</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="184">
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="J12" s="151">
-        <f>H34*I12</f>
-        <v>16203.454810263158</v>
-      </c>
-      <c r="K12" s="150">
-        <f t="shared" si="0"/>
-        <v>16203.454810263158</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="174">
-        <v>3</v>
-      </c>
-      <c r="C13" s="174" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" s="175">
-        <v>4138.6000000000004</v>
-      </c>
-      <c r="E13" s="175">
-        <v>4138.6000000000004</v>
-      </c>
-      <c r="F13" s="176">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="177">
-        <f>F13/F32</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="178">
-        <f>(F13/F32)*H32</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="184">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="J13" s="151">
-        <f>H34*I13</f>
-        <v>13257.372117488037</v>
-      </c>
-      <c r="K13" s="150">
-        <f t="shared" si="0"/>
-        <v>13257.372117488037</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="174">
-        <v>4</v>
-      </c>
-      <c r="C14" s="174" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" s="175">
-        <v>8190.4</v>
-      </c>
-      <c r="E14" s="175">
-        <v>8190.4</v>
-      </c>
-      <c r="F14" s="176">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="177">
-        <f>F14/F32</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="178">
-        <f>(F14/F32)*H32</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="184">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="J14" s="151">
-        <f>H34*I14</f>
-        <v>13257.372117488037</v>
-      </c>
-      <c r="K14" s="150">
-        <f t="shared" si="0"/>
-        <v>13257.372117488037</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="174">
-        <v>4</v>
-      </c>
-      <c r="C15" s="174" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" s="175">
-        <v>3475.3</v>
-      </c>
-      <c r="E15" s="175">
-        <v>3475.3</v>
-      </c>
-      <c r="F15" s="176">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="177">
-        <f>F15/F32</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="178">
-        <f>(F15/F32)*H32</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="184">
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="J15" s="151">
-        <f>H34*I15</f>
-        <v>16203.454810263158</v>
-      </c>
-      <c r="K15" s="150">
-        <f t="shared" si="0"/>
-        <v>16203.454810263158</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="174">
-        <v>4</v>
-      </c>
-      <c r="C16" s="174" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="175">
-        <v>4363.3</v>
-      </c>
-      <c r="E16" s="175">
-        <v>4363.3</v>
-      </c>
-      <c r="F16" s="176">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="177">
-        <f>F16/F32</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="178">
-        <f>(F16/F32)*H32</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="184">
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="J16" s="151">
-        <f>H34*I16</f>
-        <v>16203.454810263158</v>
-      </c>
-      <c r="K16" s="150">
-        <f t="shared" si="0"/>
-        <v>16203.454810263158</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="174">
-        <v>4</v>
-      </c>
-      <c r="C17" s="174" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" s="175">
-        <v>6036.6</v>
-      </c>
-      <c r="E17" s="175">
-        <v>6036.6</v>
-      </c>
-      <c r="F17" s="176">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="177">
-        <f>F17/F32</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="178">
-        <f>(F17/F32)*H32</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="184">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="J17" s="151">
-        <f>H34*I17</f>
-        <v>13257.372117488037</v>
-      </c>
-      <c r="K17" s="150">
-        <f t="shared" si="0"/>
-        <v>13257.372117488037</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="106"/>
-      <c r="C18" s="106"/>
-      <c r="D18" s="186"/>
-      <c r="E18" s="186"/>
-      <c r="F18" s="187">
-        <f>SUM(F3:F17)</f>
-        <v>558.5</v>
-      </c>
-      <c r="G18" s="107" t="s">
-        <v>133</v>
-      </c>
-      <c r="H18" s="178">
-        <f>SUM(H3:H17)</f>
-        <v>197146.79893540672</v>
-      </c>
-      <c r="I18" s="106"/>
-      <c r="J18" s="188">
-        <f>SUM(J3:J17)</f>
-        <v>235686.61542200952</v>
-      </c>
-      <c r="K18" s="150">
-        <f t="shared" si="0"/>
-        <v>432833.41435741622</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="106"/>
-      <c r="C19" s="106"/>
-      <c r="D19" s="106"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="106"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="189"/>
-      <c r="K19" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B20" s="106" t="s">
-        <v>85</v>
-      </c>
-      <c r="C20" s="106">
-        <v>1</v>
-      </c>
-      <c r="D20" s="106"/>
-      <c r="E20" s="106"/>
-      <c r="F20" s="106"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="106"/>
-      <c r="I20" s="184">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="J20" s="151">
-        <f>H34*I20</f>
-        <v>1718.548237452153</v>
-      </c>
-      <c r="K20" s="150">
-        <f t="shared" si="0"/>
-        <v>1718.548237452153</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="106" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" s="106">
-        <v>2</v>
-      </c>
-      <c r="D21" s="106"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="106"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="106"/>
-      <c r="I21" s="184">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="J21" s="151">
-        <f>H34*I21</f>
-        <v>1473.0413463875598</v>
-      </c>
-      <c r="K21" s="150">
-        <f t="shared" si="0"/>
-        <v>1473.0413463875598</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="106" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" s="106">
-        <v>3</v>
-      </c>
-      <c r="D22" s="106"/>
-      <c r="E22" s="106"/>
-      <c r="F22" s="106"/>
-      <c r="G22" s="106"/>
-      <c r="H22" s="106"/>
-      <c r="I22" s="184">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="J22" s="151">
-        <f>H34*I22</f>
-        <v>1473.0413463875598</v>
-      </c>
-      <c r="K22" s="150">
-        <f t="shared" si="0"/>
-        <v>1473.0413463875598</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="106" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" s="106">
-        <v>4</v>
-      </c>
-      <c r="D23" s="106"/>
-      <c r="E23" s="106"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="106"/>
-      <c r="I23" s="184">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="J23" s="151">
-        <f>H34*I23</f>
-        <v>1473.0413463875598</v>
-      </c>
-      <c r="K23" s="150">
-        <f t="shared" si="0"/>
-        <v>1473.0413463875598</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="106" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" s="106">
-        <v>5</v>
-      </c>
-      <c r="D24" s="106"/>
-      <c r="E24" s="106"/>
-      <c r="F24" s="106"/>
-      <c r="G24" s="106"/>
-      <c r="H24" s="106"/>
-      <c r="I24" s="184">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="J24" s="151">
-        <f>H34*I24</f>
-        <v>1473.0413463875598</v>
-      </c>
-      <c r="K24" s="150">
-        <f t="shared" si="0"/>
-        <v>1473.0413463875598</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="106" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" s="106">
-        <v>6</v>
-      </c>
-      <c r="D25" s="106"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="106"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="106"/>
-      <c r="I25" s="184">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="J25" s="151">
-        <f>H34*I25</f>
-        <v>736.52067319377988</v>
-      </c>
-      <c r="K25" s="150">
-        <f t="shared" si="0"/>
-        <v>736.52067319377988</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="106" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" s="106">
-        <v>7</v>
-      </c>
-      <c r="D26" s="106"/>
-      <c r="E26" s="106"/>
-      <c r="F26" s="106"/>
-      <c r="G26" s="106"/>
-      <c r="H26" s="106"/>
-      <c r="I26" s="184">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="J26" s="151">
-        <f>H34*I26</f>
-        <v>736.52067319377988</v>
-      </c>
-      <c r="K26" s="150">
-        <f t="shared" si="0"/>
-        <v>736.52067319377988</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="106" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" s="106">
-        <v>8</v>
-      </c>
-      <c r="D27" s="106"/>
-      <c r="E27" s="106"/>
-      <c r="F27" s="106"/>
-      <c r="G27" s="106"/>
-      <c r="H27" s="106"/>
-      <c r="I27" s="184">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="J27" s="151">
-        <f>H34*I27</f>
-        <v>736.52067319377988</v>
-      </c>
-      <c r="K27" s="150">
-        <f t="shared" si="0"/>
-        <v>736.52067319377988</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="109"/>
-      <c r="C28" s="109"/>
-      <c r="D28" s="109"/>
-      <c r="E28" s="109"/>
-      <c r="F28" s="109"/>
-      <c r="G28" s="109"/>
-      <c r="H28" s="109"/>
-      <c r="I28" s="107" t="s">
-        <v>134</v>
-      </c>
-      <c r="J28" s="151">
-        <f>SUM(J20:J27)</f>
-        <v>9820.2756425837306</v>
-      </c>
-      <c r="K28" s="150">
-        <f t="shared" si="0"/>
-        <v>9820.2756425837306</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F29" s="109"/>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D30" s="241" t="s">
-        <v>135</v>
-      </c>
-      <c r="E30" s="242"/>
-      <c r="F30" s="108">
-        <v>1254</v>
-      </c>
-      <c r="G30" s="107" t="s">
-        <v>136</v>
-      </c>
-      <c r="H30" s="191">
-        <v>442653.69</v>
-      </c>
-      <c r="K30" s="150">
-        <f>K18+K28</f>
-        <v>442653.68999999994</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D31" s="109"/>
-      <c r="E31" s="109"/>
-      <c r="F31" s="110"/>
-      <c r="H31" s="192"/>
-      <c r="K31" s="193"/>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D32" s="241" t="s">
-        <v>137</v>
-      </c>
-      <c r="E32" s="242"/>
-      <c r="F32" s="187">
-        <f>SUM(F3:F17)</f>
-        <v>558.5</v>
-      </c>
-      <c r="G32" s="107" t="s">
-        <v>133</v>
-      </c>
-      <c r="H32" s="194">
-        <f>H30-H34</f>
-        <v>197146.79893540672</v>
-      </c>
-      <c r="K32" s="193"/>
-    </row>
-    <row r="33" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D33" s="241"/>
-      <c r="E33" s="242"/>
-      <c r="F33" s="108"/>
-      <c r="G33" s="107"/>
-      <c r="H33" s="195"/>
-      <c r="K33" s="193"/>
-    </row>
-    <row r="34" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D34" s="241" t="s">
-        <v>138</v>
-      </c>
-      <c r="E34" s="242"/>
-      <c r="F34" s="187">
-        <f>F30-F32</f>
-        <v>695.5</v>
-      </c>
-      <c r="G34" s="107" t="s">
-        <v>139</v>
-      </c>
-      <c r="H34" s="194">
-        <f>(H30*F34)/F30</f>
-        <v>245506.89106459328</v>
-      </c>
-      <c r="K34" s="1"/>
-    </row>
-    <row r="36" spans="4:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="F36" s="237" t="s">
-        <v>140</v>
-      </c>
-      <c r="G36" s="238"/>
-      <c r="H36" s="196">
-        <f>H32+H33+H34</f>
-        <v>442653.69</v>
-      </c>
-    </row>
-    <row r="38" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D38" s="239" t="s">
-        <v>141</v>
-      </c>
-      <c r="E38" s="240"/>
-      <c r="F38" s="197">
-        <v>46164</v>
-      </c>
-      <c r="G38" s="197">
-        <v>46197</v>
-      </c>
-      <c r="H38" s="198" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="39" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D39" s="239" t="s">
-        <v>143</v>
-      </c>
-      <c r="E39" s="240"/>
-      <c r="F39" s="198">
-        <v>274268</v>
-      </c>
-      <c r="G39" s="198">
-        <v>275522</v>
-      </c>
-      <c r="H39" s="198">
-        <f>G39-F39</f>
-        <v>1254</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/2026/SALTA 1167/Agosto/SALTA1167-Agosto.xlsx
+++ b/2026/SALTA 1167/Agosto/SALTA1167-Agosto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\SALTA 1167\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F420E782-441A-4179-8365-1D3412C3BC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{764417E8-AABF-44EC-9B01-B67CD3A99462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$96</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1468,132 +1473,6 @@
     </xf>
     <xf numFmtId="8" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1635,6 +1514,132 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1714,9 +1719,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1754,9 +1759,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1789,9 +1794,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1824,9 +1846,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2001,21 +2040,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5546875" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.44140625" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
       <c r="B1" s="44" t="s">
         <v>73</v>
@@ -2024,7 +2063,7 @@
       <c r="D1" s="44"/>
       <c r="E1" s="45"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
       <c r="B2" s="46" t="s">
         <v>14</v>
@@ -2033,16 +2072,16 @@
       <c r="D2" s="46"/>
       <c r="E2" s="47"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13"/>
-      <c r="B3" s="196" t="s">
+      <c r="B3" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
-      <c r="E3" s="197"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="208"/>
+      <c r="D3" s="208"/>
+      <c r="E3" s="209"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>0</v>
       </c>
@@ -2053,7 +2092,7 @@
       <c r="D4" s="17"/>
       <c r="E4" s="18"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>74</v>
       </c>
@@ -2066,7 +2105,7 @@
       </c>
       <c r="E5" s="15"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>122</v>
       </c>
@@ -2077,57 +2116,57 @@
       </c>
       <c r="E6" s="18"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="199" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="211" t="s">
         <v>133</v>
       </c>
-      <c r="C8" s="199"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="199"/>
-      <c r="C9" s="199"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="199"/>
-      <c r="C10" s="199"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="198" t="s">
+      <c r="C8" s="211"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="211"/>
+      <c r="C9" s="211"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="211"/>
+      <c r="C10" s="211"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="210" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="198"/>
-      <c r="C13" s="198"/>
-      <c r="D13" s="198"/>
-      <c r="E13" s="198"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="198"/>
-      <c r="B14" s="198"/>
-      <c r="C14" s="198"/>
-      <c r="D14" s="198"/>
-      <c r="E14" s="198"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="198"/>
-      <c r="B15" s="198"/>
-      <c r="C15" s="198"/>
-      <c r="D15" s="198"/>
-      <c r="E15" s="198"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="198"/>
-      <c r="B16" s="198"/>
-      <c r="C16" s="198"/>
-      <c r="D16" s="198"/>
-      <c r="E16" s="198"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="210"/>
+      <c r="C13" s="210"/>
+      <c r="D13" s="210"/>
+      <c r="E13" s="210"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="210"/>
+      <c r="B14" s="210"/>
+      <c r="C14" s="210"/>
+      <c r="D14" s="210"/>
+      <c r="E14" s="210"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="210"/>
+      <c r="B15" s="210"/>
+      <c r="C15" s="210"/>
+      <c r="D15" s="210"/>
+      <c r="E15" s="210"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="210"/>
+      <c r="B16" s="210"/>
+      <c r="C16" s="210"/>
+      <c r="D16" s="210"/>
+      <c r="E16" s="210"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>101</v>
       </c>
@@ -2136,7 +2175,7 @@
       <c r="D20" s="6"/>
       <c r="E20" s="11"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
         <v>76</v>
       </c>
@@ -2145,11 +2184,11 @@
       <c r="D21" s="98"/>
       <c r="E21" s="93"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="192" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="206" t="s">
         <v>112</v>
       </c>
-      <c r="B22" s="193"/>
+      <c r="B22" s="207"/>
       <c r="C22" s="151"/>
       <c r="D22" s="180">
         <v>510846.85</v>
@@ -2159,15 +2198,15 @@
       </c>
       <c r="H22" s="82"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="192"/>
-      <c r="B23" s="193"/>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="206"/>
+      <c r="B23" s="207"/>
       <c r="C23" s="151"/>
       <c r="D23" s="180"/>
       <c r="E23" s="94"/>
       <c r="H23" s="82"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="152" t="s">
         <v>9</v>
       </c>
@@ -2179,7 +2218,7 @@
         <v>510846.85</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="153" t="s">
         <v>17</v>
       </c>
@@ -2188,11 +2227,11 @@
       <c r="D25" s="182"/>
       <c r="E25" s="138"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="192" t="s">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="206" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="193"/>
+      <c r="B26" s="207"/>
       <c r="C26" s="154"/>
       <c r="D26" s="183">
         <v>79873.05</v>
@@ -2201,7 +2240,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="152" t="s">
         <v>1</v>
       </c>
@@ -2213,7 +2252,7 @@
         <v>79873.05</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="153" t="s">
         <v>10</v>
       </c>
@@ -2222,7 +2261,7 @@
       <c r="D28" s="184"/>
       <c r="E28" s="139"/>
     </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="65" t="s">
         <v>66</v>
       </c>
@@ -2235,7 +2274,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="65" t="s">
         <v>66</v>
       </c>
@@ -2248,7 +2287,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="65" t="s">
         <v>65</v>
       </c>
@@ -2262,7 +2301,7 @@
         <v>Transf 04/08</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="65" t="s">
         <v>65</v>
       </c>
@@ -2275,11 +2314,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="194" t="s">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="204" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="195"/>
+      <c r="B33" s="205"/>
       <c r="C33" s="65"/>
       <c r="D33" s="95">
         <v>872785.72</v>
@@ -2288,7 +2327,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="157" t="s">
         <v>77</v>
       </c>
@@ -2301,7 +2340,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="152" t="s">
         <v>2</v>
       </c>
@@ -2313,18 +2352,18 @@
         <v>1669885.23</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="153"/>
       <c r="B36" s="152"/>
       <c r="C36" s="152"/>
       <c r="D36" s="181"/>
       <c r="E36" s="141"/>
     </row>
-    <row r="37" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="192" t="s">
+    <row r="37" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="206" t="s">
         <v>114</v>
       </c>
-      <c r="B37" s="193"/>
+      <c r="B37" s="207"/>
       <c r="C37" s="65"/>
       <c r="D37" s="95">
         <v>82000</v>
@@ -2333,7 +2372,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="159" t="s">
         <v>140</v>
       </c>
@@ -2347,18 +2386,18 @@
         <v>137</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="192" t="s">
+    <row r="39" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="206" t="s">
         <v>142</v>
       </c>
-      <c r="B39" s="193"/>
+      <c r="B39" s="207"/>
       <c r="C39" s="65"/>
       <c r="D39" s="68">
         <v>157988.29</v>
       </c>
       <c r="E39" s="96"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="152" t="s">
         <v>6</v>
       </c>
@@ -2370,7 +2409,7 @@
         <v>439518.29000000004</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="153" t="s">
         <v>11</v>
       </c>
@@ -2379,11 +2418,11 @@
       <c r="D41" s="98"/>
       <c r="E41" s="142"/>
     </row>
-    <row r="42" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="192" t="s">
+    <row r="42" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="206" t="s">
         <v>135</v>
       </c>
-      <c r="B42" s="193"/>
+      <c r="B42" s="207"/>
       <c r="C42" s="151"/>
       <c r="D42" s="186">
         <v>190000</v>
@@ -2392,7 +2431,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="152" t="s">
         <v>9</v>
       </c>
@@ -2404,7 +2443,7 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="153" t="s">
         <v>8</v>
       </c>
@@ -2413,7 +2452,7 @@
       <c r="D44" s="187"/>
       <c r="E44" s="104"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="65" t="s">
         <v>144</v>
       </c>
@@ -2424,7 +2463,7 @@
       <c r="D45" s="95"/>
       <c r="E45" s="144"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="65" t="s">
         <v>113</v>
       </c>
@@ -2436,7 +2475,7 @@
       </c>
       <c r="E46" s="145"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="162" t="s">
         <v>9</v>
       </c>
@@ -2448,23 +2487,26 @@
         <v>36608.320000000007</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="65"/>
       <c r="B48" s="65"/>
       <c r="C48" s="65"/>
       <c r="D48" s="65"/>
       <c r="E48" s="70"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="163" t="s">
         <v>97</v>
       </c>
       <c r="B49" s="163"/>
       <c r="C49" s="163"/>
       <c r="D49" s="71"/>
-      <c r="E49" s="105"/>
-    </row>
-    <row r="50" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E49" s="105">
+        <f>3000000-2926731.74</f>
+        <v>73268.259999999776</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="164"/>
       <c r="B50" s="72"/>
       <c r="C50" s="72"/>
@@ -2472,7 +2514,7 @@
       <c r="E50" s="73"/>
       <c r="F50" s="27"/>
     </row>
-    <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="165" t="s">
         <v>93</v>
       </c>
@@ -2481,19 +2523,19 @@
       <c r="D51" s="74"/>
       <c r="E51" s="75">
         <f>(SUM(E21:E49))</f>
-        <v>2926731.7399999998</v>
+        <v>2999999.9999999995</v>
       </c>
       <c r="F51" s="92"/>
       <c r="G51" s="27"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="72"/>
       <c r="B52" s="72"/>
       <c r="C52" s="72"/>
       <c r="D52" s="72"/>
       <c r="E52" s="72"/>
     </row>
-    <row r="53" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="72"/>
       <c r="B53" s="72"/>
       <c r="C53" s="72"/>
@@ -2501,7 +2543,7 @@
       <c r="E53" s="72"/>
       <c r="H53" s="99"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="167" t="s">
         <v>94</v>
       </c>
@@ -2510,35 +2552,35 @@
       <c r="D54" s="76"/>
       <c r="E54" s="77"/>
     </row>
-    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="170"/>
       <c r="B55" s="158"/>
       <c r="C55" s="65"/>
       <c r="D55" s="68"/>
       <c r="E55" s="66"/>
     </row>
-    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="191"/>
-      <c r="B56" s="191"/>
+    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="214"/>
+      <c r="B56" s="214"/>
       <c r="C56" s="65"/>
       <c r="D56" s="95"/>
       <c r="E56" s="66"/>
     </row>
-    <row r="57" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="67"/>
       <c r="B58" s="69"/>
       <c r="C58" s="4"/>
       <c r="D58" s="68"/>
       <c r="E58" s="66"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="32"/>
       <c r="B59" s="31"/>
       <c r="C59" s="31"/>
@@ -2548,9 +2590,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="20" t="s">
         <v>96</v>
       </c>
@@ -2559,8 +2601,8 @@
       <c r="D62" s="21"/>
       <c r="E62" s="135"/>
     </row>
-    <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="64" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>95</v>
       </c>
@@ -2572,17 +2614,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="63" t="s">
         <v>102</v>
       </c>
       <c r="B66" s="64">
         <f>E51</f>
-        <v>2926731.7399999998</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2999999.9999999995</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="63" t="s">
         <v>103</v>
       </c>
@@ -2591,7 +2633,7 @@
         <v>2926731.7399999998</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="63" t="s">
         <v>104</v>
       </c>
@@ -2600,7 +2642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="63" t="s">
         <v>105</v>
       </c>
@@ -2609,12 +2651,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="B71" s="26"/>
       <c r="C71" s="24"/>
     </row>
-    <row r="72" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="84" t="s">
         <v>106</v>
       </c>
@@ -2624,7 +2666,7 @@
       <c r="C72" s="24"/>
       <c r="D72" s="30"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="35" t="s">
         <v>99</v>
       </c>
@@ -2634,7 +2676,7 @@
       </c>
       <c r="E73" s="27"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="35" t="s">
         <v>25</v>
       </c>
@@ -2643,7 +2685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="35" t="s">
         <v>108</v>
       </c>
@@ -2652,7 +2694,7 @@
         <v>3248082.4500000007</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="91" t="s">
         <v>143</v>
       </c>
@@ -2660,7 +2702,7 @@
         <v>-50000</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="87" t="s">
         <v>110</v>
       </c>
@@ -2670,13 +2712,13 @@
       </c>
       <c r="D77" s="27"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="85"/>
       <c r="B78" s="85"/>
       <c r="D78" s="27"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="84" t="s">
         <v>107</v>
       </c>
@@ -2686,7 +2728,7 @@
       <c r="D79" s="26"/>
       <c r="E79" s="27"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="35" t="s">
         <v>100</v>
       </c>
@@ -2697,7 +2739,7 @@
       <c r="D80" s="27"/>
       <c r="E80" s="27"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="35" t="s">
         <v>25</v>
       </c>
@@ -2707,7 +2749,7 @@
       </c>
       <c r="D81" s="27"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="35" t="s">
         <v>109</v>
       </c>
@@ -2716,7 +2758,7 @@
       </c>
       <c r="D82" s="136"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="91" t="s">
         <v>24</v>
       </c>
@@ -2725,7 +2767,7 @@
       <c r="E83" s="27"/>
       <c r="F83" s="26"/>
     </row>
-    <row r="84" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="87" t="s">
         <v>111</v>
       </c>
@@ -2736,15 +2778,15 @@
       <c r="D84" s="27"/>
       <c r="F84" s="27"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="85"/>
       <c r="B85" s="85"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="85"/>
       <c r="B86" s="85"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="84" t="s">
         <v>124</v>
       </c>
@@ -2752,7 +2794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="35" t="s">
         <v>125</v>
       </c>
@@ -2760,7 +2802,7 @@
         <v>1025063.51</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="87" t="s">
         <v>145</v>
       </c>
@@ -2768,20 +2810,20 @@
         <v>1054849.6000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A91" s="190" t="s">
+    <row r="90" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" s="213" t="s">
         <v>18</v>
       </c>
-      <c r="B91" s="190"/>
-      <c r="C91" s="190"/>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A92" s="190"/>
-      <c r="B92" s="190"/>
-      <c r="C92" s="190"/>
-    </row>
-    <row r="93" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B91" s="213"/>
+      <c r="C91" s="213"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" s="213"/>
+      <c r="B92" s="213"/>
+      <c r="C92" s="213"/>
+    </row>
+    <row r="93" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="79"/>
       <c r="B93" s="23"/>
       <c r="C93" s="23">
@@ -2789,13 +2831,13 @@
       </c>
       <c r="E93" s="92"/>
     </row>
-    <row r="94" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="79"/>
       <c r="B94" s="81"/>
       <c r="C94" s="78"/>
       <c r="D94" s="92"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="28" t="s">
         <v>6</v>
       </c>
@@ -2805,39 +2847,45 @@
       </c>
       <c r="C95" s="29"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M96" s="5"/>
     </row>
-    <row r="97" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="189"/>
-      <c r="B97" s="189"/>
-      <c r="C97" s="189"/>
-      <c r="D97" s="189"/>
-      <c r="E97" s="189"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="189"/>
-      <c r="B98" s="189"/>
-      <c r="C98" s="189"/>
-      <c r="D98" s="189"/>
-      <c r="E98" s="189"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="189"/>
-      <c r="B99" s="189"/>
-      <c r="C99" s="189"/>
-      <c r="D99" s="189"/>
-      <c r="E99" s="189"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="189"/>
-      <c r="B100" s="189"/>
-      <c r="C100" s="189"/>
-      <c r="D100" s="189"/>
-      <c r="E100" s="189"/>
+    <row r="97" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="212"/>
+      <c r="B97" s="212"/>
+      <c r="C97" s="212"/>
+      <c r="D97" s="212"/>
+      <c r="E97" s="212"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="212"/>
+      <c r="B98" s="212"/>
+      <c r="C98" s="212"/>
+      <c r="D98" s="212"/>
+      <c r="E98" s="212"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="212"/>
+      <c r="B99" s="212"/>
+      <c r="C99" s="212"/>
+      <c r="D99" s="212"/>
+      <c r="E99" s="212"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="212"/>
+      <c r="B100" s="212"/>
+      <c r="C100" s="212"/>
+      <c r="D100" s="212"/>
+      <c r="E100" s="212"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A97:E100"/>
+    <mergeCell ref="A91:C92"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A42:B42"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
@@ -2845,12 +2893,6 @@
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A97:E100"/>
-    <mergeCell ref="A91:C92"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A42:B42"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2861,47 +2903,47 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4.44140625" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="1" max="2" width="4.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" customWidth="1"/>
     <col min="15" max="15" width="12" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="14.44140625" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="112"/>
       <c r="B1" s="113"/>
       <c r="C1" s="114"/>
       <c r="D1" s="114"/>
-      <c r="E1" s="205"/>
-      <c r="F1" s="205"/>
-      <c r="G1" s="205"/>
-      <c r="H1" s="205"/>
-      <c r="I1" s="205"/>
-      <c r="J1" s="205"/>
-      <c r="K1" s="205"/>
-      <c r="L1" s="205"/>
-      <c r="M1" s="205"/>
-      <c r="N1" s="205"/>
+      <c r="E1" s="215"/>
+      <c r="F1" s="215"/>
+      <c r="G1" s="215"/>
+      <c r="H1" s="215"/>
+      <c r="I1" s="215"/>
+      <c r="J1" s="215"/>
+      <c r="K1" s="215"/>
+      <c r="L1" s="215"/>
+      <c r="M1" s="215"/>
+      <c r="N1" s="215"/>
       <c r="O1" s="113"/>
       <c r="P1" s="115"/>
     </row>
-    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="116"/>
       <c r="B2" s="117"/>
       <c r="C2" s="118"/>
@@ -2919,7 +2961,7 @@
         <v>91</v>
       </c>
       <c r="K2" s="121">
-        <v>2700000</v>
+        <v>3000000</v>
       </c>
       <c r="L2" s="121"/>
       <c r="M2" s="121"/>
@@ -2928,7 +2970,7 @@
       <c r="P2" s="124"/>
       <c r="Q2" s="19"/>
     </row>
-    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="116"/>
       <c r="B3" s="117"/>
       <c r="C3" s="118"/>
@@ -2947,212 +2989,212 @@
       <c r="P3" s="124"/>
       <c r="Q3" s="19"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="212" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="226" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="213"/>
-      <c r="C4" s="213"/>
-      <c r="D4" s="213"/>
-      <c r="E4" s="213"/>
-      <c r="F4" s="213"/>
-      <c r="G4" s="213"/>
-      <c r="H4" s="213"/>
-      <c r="I4" s="213"/>
-      <c r="J4" s="213"/>
-      <c r="K4" s="213"/>
-      <c r="L4" s="213"/>
-      <c r="M4" s="213"/>
-      <c r="N4" s="213"/>
-      <c r="O4" s="213"/>
-      <c r="P4" s="214"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
+      <c r="D4" s="227"/>
+      <c r="E4" s="227"/>
+      <c r="F4" s="227"/>
+      <c r="G4" s="227"/>
+      <c r="H4" s="227"/>
+      <c r="I4" s="227"/>
+      <c r="J4" s="227"/>
+      <c r="K4" s="227"/>
+      <c r="L4" s="227"/>
+      <c r="M4" s="227"/>
+      <c r="N4" s="227"/>
+      <c r="O4" s="227"/>
+      <c r="P4" s="228"/>
       <c r="Q4" s="19"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="215"/>
-      <c r="B5" s="216"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="216"/>
-      <c r="E5" s="216"/>
-      <c r="F5" s="216"/>
-      <c r="G5" s="216"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="216"/>
-      <c r="J5" s="216"/>
-      <c r="K5" s="216"/>
-      <c r="L5" s="216"/>
-      <c r="M5" s="216"/>
-      <c r="N5" s="216"/>
-      <c r="O5" s="216"/>
-      <c r="P5" s="217"/>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="229"/>
+      <c r="B5" s="230"/>
+      <c r="C5" s="230"/>
+      <c r="D5" s="230"/>
+      <c r="E5" s="230"/>
+      <c r="F5" s="230"/>
+      <c r="G5" s="230"/>
+      <c r="H5" s="230"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="230"/>
+      <c r="K5" s="230"/>
+      <c r="L5" s="230"/>
+      <c r="M5" s="230"/>
+      <c r="N5" s="230"/>
+      <c r="O5" s="230"/>
+      <c r="P5" s="231"/>
       <c r="Q5" s="19"/>
     </row>
-    <row r="6" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="215"/>
-      <c r="B6" s="216"/>
-      <c r="C6" s="216"/>
-      <c r="D6" s="216"/>
-      <c r="E6" s="216"/>
-      <c r="F6" s="216"/>
-      <c r="G6" s="216"/>
-      <c r="H6" s="216"/>
-      <c r="I6" s="216"/>
-      <c r="J6" s="216"/>
-      <c r="K6" s="216"/>
-      <c r="L6" s="216"/>
-      <c r="M6" s="216"/>
-      <c r="N6" s="216"/>
-      <c r="O6" s="216"/>
-      <c r="P6" s="217"/>
+    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="229"/>
+      <c r="B6" s="230"/>
+      <c r="C6" s="230"/>
+      <c r="D6" s="230"/>
+      <c r="E6" s="230"/>
+      <c r="F6" s="230"/>
+      <c r="G6" s="230"/>
+      <c r="H6" s="230"/>
+      <c r="I6" s="230"/>
+      <c r="J6" s="230"/>
+      <c r="K6" s="230"/>
+      <c r="L6" s="230"/>
+      <c r="M6" s="230"/>
+      <c r="N6" s="230"/>
+      <c r="O6" s="230"/>
+      <c r="P6" s="231"/>
       <c r="Q6" s="19"/>
     </row>
-    <row r="7" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="215"/>
-      <c r="B7" s="216"/>
-      <c r="C7" s="216"/>
-      <c r="D7" s="216"/>
-      <c r="E7" s="216"/>
-      <c r="F7" s="216"/>
-      <c r="G7" s="216"/>
-      <c r="H7" s="216"/>
-      <c r="I7" s="216"/>
-      <c r="J7" s="216"/>
-      <c r="K7" s="216"/>
-      <c r="L7" s="216"/>
-      <c r="M7" s="216"/>
-      <c r="N7" s="216"/>
-      <c r="O7" s="216"/>
-      <c r="P7" s="217"/>
+    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="229"/>
+      <c r="B7" s="230"/>
+      <c r="C7" s="230"/>
+      <c r="D7" s="230"/>
+      <c r="E7" s="230"/>
+      <c r="F7" s="230"/>
+      <c r="G7" s="230"/>
+      <c r="H7" s="230"/>
+      <c r="I7" s="230"/>
+      <c r="J7" s="230"/>
+      <c r="K7" s="230"/>
+      <c r="L7" s="230"/>
+      <c r="M7" s="230"/>
+      <c r="N7" s="230"/>
+      <c r="O7" s="230"/>
+      <c r="P7" s="231"/>
       <c r="Q7" s="19"/>
     </row>
-    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="218"/>
-      <c r="B8" s="219"/>
-      <c r="C8" s="219"/>
-      <c r="D8" s="219"/>
-      <c r="E8" s="219"/>
-      <c r="F8" s="219"/>
-      <c r="G8" s="219"/>
-      <c r="H8" s="219"/>
-      <c r="I8" s="219"/>
-      <c r="J8" s="219"/>
-      <c r="K8" s="219"/>
-      <c r="L8" s="219"/>
-      <c r="M8" s="219"/>
-      <c r="N8" s="219"/>
-      <c r="O8" s="219"/>
-      <c r="P8" s="220"/>
-    </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="223" t="s">
+    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="232"/>
+      <c r="B8" s="233"/>
+      <c r="C8" s="233"/>
+      <c r="D8" s="233"/>
+      <c r="E8" s="233"/>
+      <c r="F8" s="233"/>
+      <c r="G8" s="233"/>
+      <c r="H8" s="233"/>
+      <c r="I8" s="233"/>
+      <c r="J8" s="233"/>
+      <c r="K8" s="233"/>
+      <c r="L8" s="233"/>
+      <c r="M8" s="233"/>
+      <c r="N8" s="233"/>
+      <c r="O8" s="233"/>
+      <c r="P8" s="234"/>
+    </row>
+    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="237" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="224"/>
-      <c r="C9" s="224"/>
-      <c r="D9" s="224"/>
-      <c r="E9" s="224"/>
-      <c r="F9" s="224"/>
-      <c r="G9" s="224"/>
-      <c r="H9" s="224"/>
-      <c r="I9" s="224"/>
-      <c r="J9" s="224"/>
-      <c r="K9" s="224"/>
-      <c r="L9" s="224"/>
-      <c r="M9" s="224"/>
-      <c r="N9" s="224"/>
-      <c r="O9" s="224"/>
-      <c r="P9" s="224"/>
-    </row>
-    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="225" t="s">
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
+      <c r="D9" s="238"/>
+      <c r="E9" s="238"/>
+      <c r="F9" s="238"/>
+      <c r="G9" s="238"/>
+      <c r="H9" s="238"/>
+      <c r="I9" s="238"/>
+      <c r="J9" s="238"/>
+      <c r="K9" s="238"/>
+      <c r="L9" s="238"/>
+      <c r="M9" s="238"/>
+      <c r="N9" s="238"/>
+      <c r="O9" s="238"/>
+      <c r="P9" s="238"/>
+    </row>
+    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="239" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="225"/>
-      <c r="C10" s="225"/>
-      <c r="D10" s="225"/>
-      <c r="E10" s="225"/>
-      <c r="F10" s="225"/>
-      <c r="G10" s="225"/>
-      <c r="H10" s="225"/>
-      <c r="I10" s="225"/>
-      <c r="J10" s="225"/>
-      <c r="K10" s="225"/>
-      <c r="L10" s="225"/>
-      <c r="M10" s="225"/>
-      <c r="N10" s="225"/>
-      <c r="O10" s="225"/>
-      <c r="P10" s="225"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="200" t="s">
+      <c r="B10" s="239"/>
+      <c r="C10" s="239"/>
+      <c r="D10" s="239"/>
+      <c r="E10" s="239"/>
+      <c r="F10" s="239"/>
+      <c r="G10" s="239"/>
+      <c r="H10" s="239"/>
+      <c r="I10" s="239"/>
+      <c r="J10" s="239"/>
+      <c r="K10" s="239"/>
+      <c r="L10" s="239"/>
+      <c r="M10" s="239"/>
+      <c r="N10" s="239"/>
+      <c r="O10" s="239"/>
+      <c r="P10" s="239"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="220" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="101"/>
-      <c r="C11" s="200" t="s">
+      <c r="C11" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="200" t="s">
+      <c r="D11" s="220" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="200" t="s">
+      <c r="E11" s="220" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="203" t="s">
+      <c r="F11" s="216" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="200" t="s">
+      <c r="G11" s="220" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="208" t="s">
+      <c r="H11" s="222" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="203" t="s">
+      <c r="I11" s="216" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="203" t="s">
+      <c r="J11" s="216" t="s">
         <v>91</v>
       </c>
-      <c r="K11" s="210" t="s">
+      <c r="K11" s="224" t="s">
         <v>92</v>
       </c>
-      <c r="L11" s="203" t="s">
+      <c r="L11" s="216" t="s">
         <v>78</v>
       </c>
-      <c r="M11" s="203" t="s">
+      <c r="M11" s="216" t="s">
         <v>123</v>
       </c>
       <c r="N11" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="206" t="s">
+      <c r="O11" s="218" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="221" t="s">
+      <c r="P11" s="235" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="202"/>
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="221"/>
       <c r="B12" s="102"/>
-      <c r="C12" s="202"/>
-      <c r="D12" s="201"/>
-      <c r="E12" s="202"/>
-      <c r="F12" s="204"/>
-      <c r="G12" s="202"/>
-      <c r="H12" s="209"/>
-      <c r="I12" s="204"/>
-      <c r="J12" s="204"/>
-      <c r="K12" s="211"/>
-      <c r="L12" s="204"/>
-      <c r="M12" s="204"/>
+      <c r="C12" s="221"/>
+      <c r="D12" s="240"/>
+      <c r="E12" s="221"/>
+      <c r="F12" s="217"/>
+      <c r="G12" s="221"/>
+      <c r="H12" s="223"/>
+      <c r="I12" s="217"/>
+      <c r="J12" s="217"/>
+      <c r="K12" s="225"/>
+      <c r="L12" s="217"/>
+      <c r="M12" s="217"/>
       <c r="N12" s="37" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="O12" s="207"/>
-      <c r="P12" s="222"/>
-    </row>
-    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O12" s="219"/>
+      <c r="P12" s="236"/>
+    </row>
+    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="40">
         <v>1</v>
       </c>
@@ -3183,7 +3225,7 @@
       </c>
       <c r="J13" s="97">
         <f t="shared" ref="J13:J35" si="1">K$2*E13/100</f>
-        <v>324000</v>
+        <v>360000</v>
       </c>
       <c r="K13" s="97">
         <f t="shared" ref="K13:K35" si="2">G$2*E13/100</f>
@@ -3196,21 +3238,21 @@
       <c r="M13" s="148"/>
       <c r="N13" s="133">
         <f>ROUND(SUM(H13:M13),0) + Q13</f>
-        <v>324000.01</v>
+        <v>360000.01</v>
       </c>
       <c r="O13" s="52">
         <f>ROUND(N13*6% + N13,0) + Q13</f>
-        <v>343440.01</v>
+        <v>381600.01</v>
       </c>
       <c r="P13" s="53">
         <f>ROUND(N13*3%,0) + N13</f>
-        <v>333720.01</v>
+        <v>370800.01</v>
       </c>
       <c r="Q13" s="27">
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="126">
         <v>2</v>
       </c>
@@ -3241,7 +3283,7 @@
       </c>
       <c r="J14" s="130">
         <f t="shared" si="1"/>
-        <v>178200</v>
+        <v>198000</v>
       </c>
       <c r="K14" s="130">
         <f t="shared" si="2"/>
@@ -3256,22 +3298,22 @@
       </c>
       <c r="N14" s="133">
         <f t="shared" ref="N14:N35" si="4">ROUND(SUM(H14:M14),0) + Q14</f>
-        <v>319873.02</v>
+        <v>339673.02</v>
       </c>
       <c r="O14" s="131">
         <f t="shared" ref="O14:O30" si="5">ROUND(N14*6% + N14,0) + Q14</f>
-        <v>339065.02</v>
+        <v>360053.02</v>
       </c>
       <c r="P14" s="132">
         <f t="shared" ref="P14:P35" si="6">ROUND(N14*3%,0) + N14</f>
-        <v>329469.02</v>
+        <v>349863.02</v>
       </c>
       <c r="Q14" s="27">
         <f>Q13+0.01</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="40">
         <v>3</v>
       </c>
@@ -3304,7 +3346,7 @@
       </c>
       <c r="J15" s="97">
         <f t="shared" si="1"/>
-        <v>145800.00000000003</v>
+        <v>162000.00000000003</v>
       </c>
       <c r="K15" s="97">
         <f t="shared" si="2"/>
@@ -3317,22 +3359,22 @@
       <c r="M15" s="147"/>
       <c r="N15" s="133">
         <f t="shared" si="4"/>
-        <v>145800.03</v>
+        <v>162000.03</v>
       </c>
       <c r="O15" s="52">
         <f t="shared" si="5"/>
-        <v>154548.03</v>
+        <v>171720.03</v>
       </c>
       <c r="P15" s="53">
         <f t="shared" si="6"/>
-        <v>150174.03</v>
+        <v>166860.03</v>
       </c>
       <c r="Q15" s="27">
         <f t="shared" ref="Q15:Q30" si="7">Q14+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="40">
         <v>4</v>
       </c>
@@ -3365,7 +3407,7 @@
       </c>
       <c r="J16" s="97">
         <f t="shared" si="1"/>
-        <v>178200</v>
+        <v>198000</v>
       </c>
       <c r="K16" s="97">
         <f t="shared" si="2"/>
@@ -3378,22 +3420,22 @@
       <c r="M16" s="148"/>
       <c r="N16" s="133">
         <f t="shared" si="4"/>
-        <v>171838.04</v>
+        <v>191638.04</v>
       </c>
       <c r="O16" s="52">
         <f t="shared" si="5"/>
-        <v>182148.04</v>
+        <v>203136.04</v>
       </c>
       <c r="P16" s="53">
         <f t="shared" si="6"/>
-        <v>176993.04</v>
+        <v>197387.04</v>
       </c>
       <c r="Q16" s="27">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="126">
         <v>5</v>
       </c>
@@ -3426,7 +3468,7 @@
       </c>
       <c r="J17" s="130">
         <f t="shared" si="1"/>
-        <v>178200</v>
+        <v>198000</v>
       </c>
       <c r="K17" s="130">
         <f t="shared" si="2"/>
@@ -3441,15 +3483,15 @@
       </c>
       <c r="N17" s="133">
         <f t="shared" si="4"/>
-        <v>178200.05</v>
+        <v>198000.05</v>
       </c>
       <c r="O17" s="131">
         <f t="shared" si="5"/>
-        <v>188892.05</v>
+        <v>209880.05</v>
       </c>
       <c r="P17" s="132">
         <f t="shared" si="6"/>
-        <v>183546.05</v>
+        <v>203940.05</v>
       </c>
       <c r="Q17" s="27">
         <f t="shared" si="7"/>
@@ -3459,7 +3501,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <v>6</v>
       </c>
@@ -3492,7 +3534,7 @@
       </c>
       <c r="J18" s="97">
         <f t="shared" si="1"/>
-        <v>145800.00000000003</v>
+        <v>162000.00000000003</v>
       </c>
       <c r="K18" s="97">
         <f t="shared" si="2"/>
@@ -3505,22 +3547,22 @@
       <c r="M18" s="148"/>
       <c r="N18" s="133">
         <f t="shared" si="4"/>
-        <v>145800.06</v>
+        <v>162000.06</v>
       </c>
       <c r="O18" s="52">
         <f t="shared" si="5"/>
-        <v>154548.06</v>
+        <v>171720.06</v>
       </c>
       <c r="P18" s="53">
         <f t="shared" si="6"/>
-        <v>150174.06</v>
+        <v>166860.06</v>
       </c>
       <c r="Q18" s="27">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="126">
         <v>7</v>
       </c>
@@ -3553,7 +3595,7 @@
       </c>
       <c r="J19" s="130">
         <f t="shared" si="1"/>
-        <v>145800.00000000003</v>
+        <v>162000.00000000003</v>
       </c>
       <c r="K19" s="130">
         <f t="shared" si="2"/>
@@ -3566,22 +3608,22 @@
       <c r="M19" s="148"/>
       <c r="N19" s="133">
         <f t="shared" si="4"/>
-        <v>145800.07</v>
+        <v>162000.07</v>
       </c>
       <c r="O19" s="131">
         <f t="shared" si="5"/>
-        <v>154548.07</v>
+        <v>171720.07</v>
       </c>
       <c r="P19" s="132">
         <f t="shared" si="6"/>
-        <v>150174.07</v>
+        <v>166860.07</v>
       </c>
       <c r="Q19" s="27">
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="126">
         <v>8</v>
       </c>
@@ -3614,7 +3656,7 @@
       </c>
       <c r="J20" s="130">
         <f t="shared" si="1"/>
-        <v>178200</v>
+        <v>198000</v>
       </c>
       <c r="K20" s="130">
         <f t="shared" si="2"/>
@@ -3627,22 +3669,22 @@
       <c r="M20" s="148"/>
       <c r="N20" s="133">
         <f t="shared" si="4"/>
-        <v>255213.08</v>
+        <v>275013.08</v>
       </c>
       <c r="O20" s="131">
         <f t="shared" si="5"/>
-        <v>270526.08000000002</v>
+        <v>291514.08</v>
       </c>
       <c r="P20" s="132">
         <f t="shared" si="6"/>
-        <v>262869.07999999996</v>
+        <v>283263.08</v>
       </c>
       <c r="Q20" s="27">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="126">
         <v>9</v>
       </c>
@@ -3676,7 +3718,7 @@
       </c>
       <c r="J21" s="97">
         <f t="shared" si="1"/>
-        <v>178200</v>
+        <v>198000</v>
       </c>
       <c r="K21" s="97">
         <f t="shared" si="2"/>
@@ -3691,22 +3733,22 @@
       </c>
       <c r="N21" s="133">
         <f t="shared" si="4"/>
-        <v>178200.09</v>
+        <v>198000.09</v>
       </c>
       <c r="O21" s="52">
         <f t="shared" si="5"/>
-        <v>188892.09</v>
+        <v>209880.09</v>
       </c>
       <c r="P21" s="53">
         <f t="shared" si="6"/>
-        <v>183546.09</v>
+        <v>203940.09</v>
       </c>
       <c r="Q21" s="27">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="126">
         <v>10</v>
       </c>
@@ -3739,7 +3781,7 @@
       </c>
       <c r="J22" s="97">
         <f t="shared" si="1"/>
-        <v>145800.00000000003</v>
+        <v>162000.00000000003</v>
       </c>
       <c r="K22" s="97">
         <f t="shared" si="2"/>
@@ -3752,22 +3794,22 @@
       <c r="M22" s="148"/>
       <c r="N22" s="133">
         <f t="shared" si="4"/>
-        <v>-12187.9</v>
+        <v>4012.1</v>
       </c>
       <c r="O22" s="52">
         <f t="shared" si="5"/>
-        <v>-12918.9</v>
+        <v>4253.1000000000004</v>
       </c>
       <c r="P22" s="53">
         <f t="shared" si="6"/>
-        <v>-12553.9</v>
+        <v>4132.1000000000004</v>
       </c>
       <c r="Q22" s="27">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="40">
         <v>11</v>
       </c>
@@ -3798,7 +3840,7 @@
       </c>
       <c r="J23" s="97">
         <f t="shared" si="1"/>
-        <v>145800.00000000003</v>
+        <v>162000.00000000003</v>
       </c>
       <c r="K23" s="97">
         <f t="shared" si="2"/>
@@ -3811,15 +3853,15 @@
       <c r="M23" s="148"/>
       <c r="N23" s="133">
         <f t="shared" si="4"/>
-        <v>145800.10999999999</v>
+        <v>162000.10999999999</v>
       </c>
       <c r="O23" s="52">
         <f t="shared" si="5"/>
-        <v>154548.10999999999</v>
+        <v>171720.11</v>
       </c>
       <c r="P23" s="53">
         <f t="shared" si="6"/>
-        <v>150174.10999999999</v>
+        <v>166860.10999999999</v>
       </c>
       <c r="Q23" s="27">
         <f t="shared" si="7"/>
@@ -3829,7 +3871,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>12</v>
       </c>
@@ -3862,7 +3904,7 @@
       </c>
       <c r="J24" s="97">
         <f t="shared" si="1"/>
-        <v>178200</v>
+        <v>198000</v>
       </c>
       <c r="K24" s="97">
         <f t="shared" si="2"/>
@@ -3875,22 +3917,22 @@
       <c r="M24" s="148"/>
       <c r="N24" s="133">
         <f t="shared" si="4"/>
-        <v>178200.12</v>
+        <v>198000.12</v>
       </c>
       <c r="O24" s="52">
         <f t="shared" si="5"/>
-        <v>188892.12</v>
+        <v>209880.12</v>
       </c>
       <c r="P24" s="53">
         <f t="shared" si="6"/>
-        <v>183546.12</v>
+        <v>203940.12</v>
       </c>
       <c r="Q24" s="27">
         <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="40">
         <v>13</v>
       </c>
@@ -3922,7 +3964,7 @@
       </c>
       <c r="J25" s="97">
         <f t="shared" si="1"/>
-        <v>178200</v>
+        <v>198000</v>
       </c>
       <c r="K25" s="97">
         <f t="shared" si="2"/>
@@ -3935,22 +3977,22 @@
       <c r="M25" s="148"/>
       <c r="N25" s="133">
         <f t="shared" si="4"/>
-        <v>172368.13</v>
+        <v>192168.13</v>
       </c>
       <c r="O25" s="52">
         <f t="shared" si="5"/>
-        <v>182710.13</v>
+        <v>203698.13</v>
       </c>
       <c r="P25" s="53">
         <f t="shared" si="6"/>
-        <v>177539.13</v>
+        <v>197933.13</v>
       </c>
       <c r="Q25" s="27">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="126">
         <v>14</v>
       </c>
@@ -3981,7 +4023,7 @@
       </c>
       <c r="J26" s="130">
         <f t="shared" si="1"/>
-        <v>145800.00000000003</v>
+        <v>162000.00000000003</v>
       </c>
       <c r="K26" s="130">
         <f t="shared" si="2"/>
@@ -3994,22 +4036,22 @@
       <c r="M26" s="149"/>
       <c r="N26" s="133">
         <f t="shared" si="4"/>
-        <v>145800.14000000001</v>
+        <v>162000.14000000001</v>
       </c>
       <c r="O26" s="131">
         <f t="shared" si="5"/>
-        <v>154548.14000000001</v>
+        <v>171720.14</v>
       </c>
       <c r="P26" s="132">
         <f t="shared" si="6"/>
-        <v>150174.14000000001</v>
+        <v>166860.14000000001</v>
       </c>
       <c r="Q26" s="27">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="40">
         <v>15</v>
       </c>
@@ -4040,7 +4082,7 @@
       </c>
       <c r="J27" s="97">
         <f t="shared" si="1"/>
-        <v>145800.00000000003</v>
+        <v>162000.00000000003</v>
       </c>
       <c r="K27" s="97">
         <f t="shared" si="2"/>
@@ -4053,22 +4095,22 @@
       <c r="M27" s="148"/>
       <c r="N27" s="133">
         <f t="shared" si="4"/>
-        <v>145800.15</v>
+        <v>162000.15</v>
       </c>
       <c r="O27" s="52">
         <f t="shared" si="5"/>
-        <v>154548.15</v>
+        <v>171720.15</v>
       </c>
       <c r="P27" s="53">
         <f t="shared" si="6"/>
-        <v>150174.15</v>
+        <v>166860.15</v>
       </c>
       <c r="Q27" s="27">
         <f t="shared" si="7"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="126">
         <v>16</v>
       </c>
@@ -4101,7 +4143,7 @@
       </c>
       <c r="J28" s="97">
         <f t="shared" si="1"/>
-        <v>18899.999999999996</v>
+        <v>21000</v>
       </c>
       <c r="K28" s="97">
         <f t="shared" si="2"/>
@@ -4114,22 +4156,22 @@
       <c r="M28" s="148"/>
       <c r="N28" s="133">
         <f t="shared" si="4"/>
-        <v>19063.16</v>
+        <v>21163.16</v>
       </c>
       <c r="O28" s="52">
         <f t="shared" si="5"/>
-        <v>20207.16</v>
+        <v>22433.16</v>
       </c>
       <c r="P28" s="53">
         <f t="shared" si="6"/>
-        <v>19635.16</v>
+        <v>21798.16</v>
       </c>
       <c r="Q28" s="27">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="126">
         <v>17</v>
       </c>
@@ -4160,7 +4202,7 @@
       </c>
       <c r="J29" s="97">
         <f t="shared" si="1"/>
-        <v>16200</v>
+        <v>18000</v>
       </c>
       <c r="K29" s="97">
         <f t="shared" si="2"/>
@@ -4173,22 +4215,22 @@
       <c r="M29" s="148"/>
       <c r="N29" s="133">
         <f t="shared" si="4"/>
-        <v>16340.17</v>
+        <v>18140.169999999998</v>
       </c>
       <c r="O29" s="52">
         <f t="shared" si="5"/>
-        <v>17321.169999999998</v>
+        <v>19229.169999999998</v>
       </c>
       <c r="P29" s="53">
         <f t="shared" si="6"/>
-        <v>16830.169999999998</v>
+        <v>18684.169999999998</v>
       </c>
       <c r="Q29" s="27">
         <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>18</v>
       </c>
@@ -4219,7 +4261,7 @@
       </c>
       <c r="J30" s="97">
         <f t="shared" si="1"/>
-        <v>16200</v>
+        <v>18000</v>
       </c>
       <c r="K30" s="97">
         <f t="shared" si="2"/>
@@ -4232,22 +4274,22 @@
       <c r="M30" s="148"/>
       <c r="N30" s="133">
         <f t="shared" si="4"/>
-        <v>16340.18</v>
+        <v>18140.18</v>
       </c>
       <c r="O30" s="52">
         <f t="shared" si="5"/>
-        <v>17321.18</v>
+        <v>19229.18</v>
       </c>
       <c r="P30" s="53">
         <f t="shared" si="6"/>
-        <v>16830.18</v>
+        <v>18684.18</v>
       </c>
       <c r="Q30" s="27">
         <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="126">
         <v>19</v>
       </c>
@@ -4278,7 +4320,7 @@
       </c>
       <c r="J31" s="130">
         <f t="shared" si="1"/>
-        <v>16200</v>
+        <v>18000</v>
       </c>
       <c r="K31" s="130">
         <f t="shared" si="2"/>
@@ -4291,19 +4333,19 @@
       <c r="M31" s="149"/>
       <c r="N31" s="133">
         <f t="shared" si="4"/>
-        <v>16340.19</v>
+        <v>18140.189999999999</v>
       </c>
       <c r="O31" s="131"/>
       <c r="P31" s="132">
         <f t="shared" si="6"/>
-        <v>16830.190000000002</v>
+        <v>18684.189999999999</v>
       </c>
       <c r="Q31" s="27">
         <f>Q30+0.01</f>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="21.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A32" s="54">
         <v>20</v>
       </c>
@@ -4336,7 +4378,7 @@
       </c>
       <c r="J32" s="97">
         <f t="shared" si="1"/>
-        <v>16200</v>
+        <v>18000</v>
       </c>
       <c r="K32" s="97">
         <f t="shared" si="2"/>
@@ -4349,19 +4391,19 @@
       <c r="M32" s="148"/>
       <c r="N32" s="133">
         <f t="shared" si="4"/>
-        <v>16340.2</v>
+        <v>18140.2</v>
       </c>
       <c r="O32" s="52"/>
       <c r="P32" s="53">
         <f t="shared" si="6"/>
-        <v>16830.2</v>
+        <v>18684.2</v>
       </c>
       <c r="Q32" s="27">
         <f t="shared" ref="Q32:Q35" si="9">Q31+0.01</f>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="54">
         <v>21</v>
       </c>
@@ -4394,7 +4436,7 @@
       </c>
       <c r="J33" s="97">
         <f t="shared" si="1"/>
-        <v>8100</v>
+        <v>9000</v>
       </c>
       <c r="K33" s="97">
         <f t="shared" si="2"/>
@@ -4407,19 +4449,19 @@
       <c r="M33" s="148"/>
       <c r="N33" s="133">
         <f t="shared" si="4"/>
-        <v>8170.21</v>
+        <v>9070.2099999999991</v>
       </c>
       <c r="O33" s="52"/>
       <c r="P33" s="53">
         <f t="shared" si="6"/>
-        <v>8415.2099999999991</v>
+        <v>9342.2099999999991</v>
       </c>
       <c r="Q33" s="27">
         <f t="shared" si="9"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="55">
         <v>22</v>
       </c>
@@ -4450,7 +4492,7 @@
       </c>
       <c r="J34" s="97">
         <f t="shared" si="1"/>
-        <v>8100</v>
+        <v>9000</v>
       </c>
       <c r="K34" s="97">
         <f t="shared" si="2"/>
@@ -4463,19 +4505,19 @@
       <c r="M34" s="148"/>
       <c r="N34" s="133">
         <f t="shared" si="4"/>
-        <v>8170.22</v>
+        <v>9070.2199999999993</v>
       </c>
       <c r="O34" s="52"/>
       <c r="P34" s="53">
         <f t="shared" si="6"/>
-        <v>8415.2200000000012</v>
+        <v>9342.2199999999993</v>
       </c>
       <c r="Q34" s="27">
         <f t="shared" si="9"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="40">
         <v>23</v>
       </c>
@@ -4508,7 +4550,7 @@
       </c>
       <c r="J35" s="97">
         <f t="shared" si="1"/>
-        <v>8100</v>
+        <v>9000</v>
       </c>
       <c r="K35" s="97">
         <f t="shared" si="2"/>
@@ -4521,19 +4563,19 @@
       <c r="M35" s="148"/>
       <c r="N35" s="133">
         <f t="shared" si="4"/>
-        <v>8170.23</v>
+        <v>9070.23</v>
       </c>
       <c r="O35" s="58"/>
       <c r="P35" s="53">
         <f t="shared" si="6"/>
-        <v>8415.23</v>
+        <v>9342.23</v>
       </c>
       <c r="Q35" s="27">
         <f t="shared" si="9"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="59"/>
       <c r="B36" s="59"/>
       <c r="C36" s="60"/>
@@ -4560,7 +4602,7 @@
       </c>
       <c r="J36" s="86">
         <f t="shared" si="11"/>
-        <v>2700000</v>
+        <v>3000000</v>
       </c>
       <c r="K36" s="38">
         <f t="shared" si="11"/>
@@ -4573,111 +4615,117 @@
       <c r="M36" s="61"/>
       <c r="N36" s="61">
         <f>SUM(N13:N35)</f>
-        <v>2749439.7600000012</v>
+        <v>3049439.7600000012</v>
       </c>
       <c r="O36" s="61">
         <f t="shared" si="11"/>
-        <v>2853784.7100000009</v>
+        <v>3165106.7100000004</v>
       </c>
       <c r="P36" s="61">
         <f>SUM(P13:P35)</f>
-        <v>2831920.7600000012</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>3140920.7600000007</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="33"/>
       <c r="D37" s="33"/>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="189" t="str">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="212" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="189"/>
-      <c r="E39" s="189"/>
-      <c r="F39" s="189"/>
-      <c r="G39" s="189"/>
-      <c r="H39" s="189"/>
-      <c r="I39" s="189"/>
-      <c r="J39" s="189"/>
-      <c r="K39" s="189"/>
-      <c r="L39" s="189"/>
-      <c r="M39" s="189"/>
-      <c r="N39" s="189"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="189"/>
-      <c r="D40" s="189"/>
-      <c r="E40" s="189"/>
-      <c r="F40" s="189"/>
-      <c r="G40" s="189"/>
-      <c r="H40" s="189"/>
-      <c r="I40" s="189"/>
-      <c r="J40" s="189"/>
-      <c r="K40" s="189"/>
-      <c r="L40" s="189"/>
-      <c r="M40" s="189"/>
-      <c r="N40" s="189"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="189"/>
-      <c r="D41" s="189"/>
-      <c r="E41" s="189"/>
-      <c r="F41" s="189"/>
-      <c r="G41" s="189"/>
-      <c r="H41" s="189"/>
-      <c r="I41" s="189"/>
-      <c r="J41" s="189"/>
-      <c r="K41" s="189"/>
-      <c r="L41" s="189"/>
-      <c r="M41" s="189"/>
-      <c r="N41" s="189"/>
-    </row>
-    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="189"/>
-      <c r="D42" s="189"/>
-      <c r="E42" s="189"/>
-      <c r="F42" s="189"/>
-      <c r="G42" s="189"/>
-      <c r="H42" s="189"/>
-      <c r="I42" s="189"/>
-      <c r="J42" s="189"/>
-      <c r="K42" s="189"/>
-      <c r="L42" s="189"/>
-      <c r="M42" s="189"/>
-      <c r="N42" s="189"/>
-    </row>
-    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="189"/>
-      <c r="D43" s="189"/>
-      <c r="E43" s="189"/>
-      <c r="F43" s="189"/>
-      <c r="G43" s="189"/>
-      <c r="H43" s="189"/>
-      <c r="I43" s="189"/>
-      <c r="J43" s="189"/>
-      <c r="K43" s="189"/>
-      <c r="L43" s="189"/>
-      <c r="M43" s="189"/>
-      <c r="N43" s="189"/>
-    </row>
-    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="189"/>
-      <c r="D44" s="189"/>
-      <c r="E44" s="189"/>
-      <c r="F44" s="189"/>
-      <c r="G44" s="189"/>
-      <c r="H44" s="189"/>
-      <c r="I44" s="189"/>
-      <c r="J44" s="189"/>
-      <c r="K44" s="189"/>
-      <c r="L44" s="189"/>
-      <c r="M44" s="189"/>
-      <c r="N44" s="189"/>
+      <c r="D39" s="212"/>
+      <c r="E39" s="212"/>
+      <c r="F39" s="212"/>
+      <c r="G39" s="212"/>
+      <c r="H39" s="212"/>
+      <c r="I39" s="212"/>
+      <c r="J39" s="212"/>
+      <c r="K39" s="212"/>
+      <c r="L39" s="212"/>
+      <c r="M39" s="212"/>
+      <c r="N39" s="212"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="212"/>
+      <c r="D40" s="212"/>
+      <c r="E40" s="212"/>
+      <c r="F40" s="212"/>
+      <c r="G40" s="212"/>
+      <c r="H40" s="212"/>
+      <c r="I40" s="212"/>
+      <c r="J40" s="212"/>
+      <c r="K40" s="212"/>
+      <c r="L40" s="212"/>
+      <c r="M40" s="212"/>
+      <c r="N40" s="212"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="212"/>
+      <c r="D41" s="212"/>
+      <c r="E41" s="212"/>
+      <c r="F41" s="212"/>
+      <c r="G41" s="212"/>
+      <c r="H41" s="212"/>
+      <c r="I41" s="212"/>
+      <c r="J41" s="212"/>
+      <c r="K41" s="212"/>
+      <c r="L41" s="212"/>
+      <c r="M41" s="212"/>
+      <c r="N41" s="212"/>
+    </row>
+    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="212"/>
+      <c r="D42" s="212"/>
+      <c r="E42" s="212"/>
+      <c r="F42" s="212"/>
+      <c r="G42" s="212"/>
+      <c r="H42" s="212"/>
+      <c r="I42" s="212"/>
+      <c r="J42" s="212"/>
+      <c r="K42" s="212"/>
+      <c r="L42" s="212"/>
+      <c r="M42" s="212"/>
+      <c r="N42" s="212"/>
+    </row>
+    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="212"/>
+      <c r="D43" s="212"/>
+      <c r="E43" s="212"/>
+      <c r="F43" s="212"/>
+      <c r="G43" s="212"/>
+      <c r="H43" s="212"/>
+      <c r="I43" s="212"/>
+      <c r="J43" s="212"/>
+      <c r="K43" s="212"/>
+      <c r="L43" s="212"/>
+      <c r="M43" s="212"/>
+      <c r="N43" s="212"/>
+    </row>
+    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="212"/>
+      <c r="D44" s="212"/>
+      <c r="E44" s="212"/>
+      <c r="F44" s="212"/>
+      <c r="G44" s="212"/>
+      <c r="H44" s="212"/>
+      <c r="I44" s="212"/>
+      <c r="J44" s="212"/>
+      <c r="K44" s="212"/>
+      <c r="L44" s="212"/>
+      <c r="M44" s="212"/>
+      <c r="N44" s="212"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C39:N44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="M11:M12"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4691,12 +4739,6 @@
     <mergeCell ref="A9:P9"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="L11:L12"/>
-    <mergeCell ref="C39:N44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="M11:M12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4706,48 +4748,48 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFC03CC8-EEB1-4121-A90D-748455B927ED}">
   <dimension ref="B2:O32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" customWidth="1"/>
-    <col min="7" max="7" width="1.77734375" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" customWidth="1"/>
-    <col min="9" max="9" width="14.21875" customWidth="1"/>
-    <col min="10" max="10" width="1.77734375" customWidth="1"/>
-    <col min="11" max="11" width="19.5546875" style="109" customWidth="1"/>
-    <col min="12" max="12" width="2.109375" customWidth="1"/>
-    <col min="13" max="13" width="19.77734375" style="110" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+    <col min="7" max="7" width="1.7109375" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" customWidth="1"/>
+    <col min="10" max="10" width="1.7109375" customWidth="1"/>
+    <col min="11" max="11" width="19.5703125" style="109" customWidth="1"/>
+    <col min="12" max="12" width="2.140625" customWidth="1"/>
+    <col min="13" max="13" width="19.7109375" style="110" customWidth="1"/>
     <col min="14" max="14" width="2" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" style="176" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" style="176" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="D2" s="228" t="s">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="D2" s="241" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="228"/>
-      <c r="F2" s="228"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="229" t="s">
+      <c r="H2" s="242" t="s">
         <v>148</v>
       </c>
-      <c r="I2" s="230"/>
+      <c r="I2" s="243"/>
       <c r="J2" s="1"/>
       <c r="K2" s="107" t="s">
         <v>149</v>
       </c>
-      <c r="M2" s="231" t="s">
+      <c r="M2" s="189" t="s">
         <v>150</v>
       </c>
       <c r="O2" s="107" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="106" t="s">
         <v>79</v>
       </c>
@@ -4773,33 +4815,33 @@
       <c r="M3" s="108"/>
       <c r="O3" s="107"/>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="232">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B4" s="190">
         <v>1</v>
       </c>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="190" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="233">
-        <v>0</v>
-      </c>
-      <c r="E4" s="234">
-        <v>0</v>
-      </c>
-      <c r="F4" s="235">
+      <c r="D4" s="191">
+        <v>0</v>
+      </c>
+      <c r="E4" s="192">
+        <v>0</v>
+      </c>
+      <c r="F4" s="193">
         <v>0</v>
       </c>
       <c r="H4" s="172">
         <v>0.12</v>
       </c>
-      <c r="I4" s="236">
+      <c r="I4" s="194">
         <v>2796.8673532673188</v>
       </c>
       <c r="K4" s="150">
         <f>I4+F4</f>
         <v>2796.8673532673188</v>
       </c>
-      <c r="M4" s="237">
+      <c r="M4" s="195">
         <f>K4</f>
         <v>2796.8673532673188</v>
       </c>
@@ -4808,7 +4850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="106">
         <v>1</v>
       </c>
@@ -4818,23 +4860,23 @@
       <c r="D5" s="174">
         <v>344.5</v>
       </c>
-      <c r="E5" s="234">
+      <c r="E5" s="192">
         <v>0.63292302039316528</v>
       </c>
-      <c r="F5" s="235">
+      <c r="F5" s="193">
         <v>130135.17061056105</v>
       </c>
       <c r="H5" s="173">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I5" s="236">
+      <c r="I5" s="194">
         <v>1538.2770442970254</v>
       </c>
       <c r="K5" s="150">
         <f t="shared" ref="K5:K18" si="0">I5+F5</f>
         <v>131673.44765485809</v>
       </c>
-      <c r="M5" s="237">
+      <c r="M5" s="195">
         <v>0</v>
       </c>
       <c r="O5" s="150">
@@ -4842,33 +4884,33 @@
         <v>131673.44765485809</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B6" s="232">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B6" s="190">
         <v>1</v>
       </c>
-      <c r="C6" s="232" t="s">
+      <c r="C6" s="190" t="s">
         <v>83</v>
       </c>
-      <c r="D6" s="233">
-        <v>0</v>
-      </c>
-      <c r="E6" s="234">
-        <v>0</v>
-      </c>
-      <c r="F6" s="235">
+      <c r="D6" s="191">
+        <v>0</v>
+      </c>
+      <c r="E6" s="192">
+        <v>0</v>
+      </c>
+      <c r="F6" s="193">
         <v>0</v>
       </c>
       <c r="H6" s="173">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I6" s="236">
+      <c r="I6" s="194">
         <v>1258.5903089702933</v>
       </c>
       <c r="K6" s="150">
         <f t="shared" si="0"/>
         <v>1258.5903089702933</v>
       </c>
-      <c r="M6" s="237">
+      <c r="M6" s="195">
         <f t="shared" ref="M6:M18" si="2">K6</f>
         <v>1258.5903089702933</v>
       </c>
@@ -4877,33 +4919,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B7" s="232">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B7" s="190">
         <v>2</v>
       </c>
-      <c r="C7" s="232" t="s">
+      <c r="C7" s="190" t="s">
         <v>81</v>
       </c>
-      <c r="D7" s="233">
-        <v>0</v>
-      </c>
-      <c r="E7" s="234">
-        <v>0</v>
-      </c>
-      <c r="F7" s="235">
+      <c r="D7" s="191">
+        <v>0</v>
+      </c>
+      <c r="E7" s="192">
+        <v>0</v>
+      </c>
+      <c r="F7" s="193">
         <v>0</v>
       </c>
       <c r="H7" s="173">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I7" s="236">
+      <c r="I7" s="194">
         <v>1258.5903089702933</v>
       </c>
       <c r="K7" s="150">
         <f t="shared" si="0"/>
         <v>1258.5903089702933</v>
       </c>
-      <c r="M7" s="237">
+      <c r="M7" s="195">
         <f t="shared" si="2"/>
         <v>1258.5903089702933</v>
       </c>
@@ -4912,33 +4954,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B8" s="232">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B8" s="190">
         <v>2</v>
       </c>
-      <c r="C8" s="232" t="s">
+      <c r="C8" s="190" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="233">
-        <v>0</v>
-      </c>
-      <c r="E8" s="234">
-        <v>0</v>
-      </c>
-      <c r="F8" s="235">
+      <c r="D8" s="191">
+        <v>0</v>
+      </c>
+      <c r="E8" s="192">
+        <v>0</v>
+      </c>
+      <c r="F8" s="193">
         <v>0</v>
       </c>
       <c r="H8" s="173">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I8" s="236">
+      <c r="I8" s="194">
         <v>1538.2770442970254</v>
       </c>
       <c r="K8" s="150">
         <f t="shared" si="0"/>
         <v>1538.2770442970254</v>
       </c>
-      <c r="M8" s="237">
+      <c r="M8" s="195">
         <f t="shared" si="2"/>
         <v>1538.2770442970254</v>
       </c>
@@ -4947,33 +4989,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B9" s="232">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B9" s="190">
         <v>2</v>
       </c>
-      <c r="C9" s="232" t="s">
+      <c r="C9" s="190" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="233">
-        <v>0</v>
-      </c>
-      <c r="E9" s="234">
-        <v>0</v>
-      </c>
-      <c r="F9" s="235">
+      <c r="D9" s="191">
+        <v>0</v>
+      </c>
+      <c r="E9" s="192">
+        <v>0</v>
+      </c>
+      <c r="F9" s="193">
         <v>0</v>
       </c>
       <c r="H9" s="173">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I9" s="236">
+      <c r="I9" s="194">
         <v>1538.2770442970254</v>
       </c>
       <c r="K9" s="150">
         <f t="shared" si="0"/>
         <v>1538.2770442970254</v>
       </c>
-      <c r="M9" s="237">
+      <c r="M9" s="195">
         <f t="shared" si="2"/>
         <v>1538.2770442970254</v>
       </c>
@@ -4982,33 +5024,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B10" s="232">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B10" s="190">
         <v>2</v>
       </c>
-      <c r="C10" s="232" t="s">
+      <c r="C10" s="190" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="233">
-        <v>0</v>
-      </c>
-      <c r="E10" s="234">
-        <v>0</v>
-      </c>
-      <c r="F10" s="238">
+      <c r="D10" s="191">
+        <v>0</v>
+      </c>
+      <c r="E10" s="192">
+        <v>0</v>
+      </c>
+      <c r="F10" s="196">
         <v>0</v>
       </c>
       <c r="H10" s="173">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I10" s="236">
+      <c r="I10" s="194">
         <v>1258.5903089702933</v>
       </c>
       <c r="K10" s="150">
         <f t="shared" si="0"/>
         <v>1258.5903089702933</v>
       </c>
-      <c r="M10" s="237">
+      <c r="M10" s="195">
         <f t="shared" si="2"/>
         <v>1258.5903089702933</v>
       </c>
@@ -5017,33 +5059,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B11" s="232">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B11" s="190">
         <v>3</v>
       </c>
-      <c r="C11" s="232" t="s">
+      <c r="C11" s="190" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="233">
-        <v>0</v>
-      </c>
-      <c r="E11" s="234">
-        <v>0</v>
-      </c>
-      <c r="F11" s="235">
+      <c r="D11" s="191">
+        <v>0</v>
+      </c>
+      <c r="E11" s="192">
+        <v>0</v>
+      </c>
+      <c r="F11" s="193">
         <v>0</v>
       </c>
       <c r="H11" s="173">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I11" s="236">
+      <c r="I11" s="194">
         <v>1258.5903089702933</v>
       </c>
       <c r="K11" s="150">
         <f t="shared" si="0"/>
         <v>1258.5903089702933</v>
       </c>
-      <c r="M11" s="237">
+      <c r="M11" s="195">
         <f t="shared" si="2"/>
         <v>1258.5903089702933</v>
       </c>
@@ -5052,7 +5094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="106">
         <v>3</v>
       </c>
@@ -5062,23 +5104,23 @@
       <c r="D12" s="174">
         <v>199.80000000000018</v>
       </c>
-      <c r="E12" s="234">
+      <c r="E12" s="192">
         <v>0.36707697960683466</v>
       </c>
-      <c r="F12" s="235">
+      <c r="F12" s="193">
         <v>75474.621445544617</v>
       </c>
       <c r="H12" s="173">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I12" s="236">
+      <c r="I12" s="194">
         <v>1538.2770442970254</v>
       </c>
       <c r="K12" s="150">
         <f t="shared" si="0"/>
         <v>77012.898489841638</v>
       </c>
-      <c r="M12" s="237">
+      <c r="M12" s="195">
         <v>0</v>
       </c>
       <c r="O12" s="150">
@@ -5086,33 +5128,33 @@
         <v>77012.898489841638</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="232">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B13" s="190">
         <v>3</v>
       </c>
-      <c r="C13" s="232" t="s">
+      <c r="C13" s="190" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="233">
-        <v>0</v>
-      </c>
-      <c r="E13" s="234">
-        <v>0</v>
-      </c>
-      <c r="F13" s="235">
+      <c r="D13" s="191">
+        <v>0</v>
+      </c>
+      <c r="E13" s="192">
+        <v>0</v>
+      </c>
+      <c r="F13" s="193">
         <v>0</v>
       </c>
       <c r="H13" s="173">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I13" s="236">
+      <c r="I13" s="194">
         <v>1538.2770442970254</v>
       </c>
       <c r="K13" s="150">
         <f t="shared" si="0"/>
         <v>1538.2770442970254</v>
       </c>
-      <c r="M13" s="237">
+      <c r="M13" s="195">
         <f t="shared" si="2"/>
         <v>1538.2770442970254</v>
       </c>
@@ -5121,33 +5163,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B14" s="232">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B14" s="190">
         <v>3</v>
       </c>
-      <c r="C14" s="232" t="s">
+      <c r="C14" s="190" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="233">
-        <v>0</v>
-      </c>
-      <c r="E14" s="234">
-        <v>0</v>
-      </c>
-      <c r="F14" s="235">
+      <c r="D14" s="191">
+        <v>0</v>
+      </c>
+      <c r="E14" s="192">
+        <v>0</v>
+      </c>
+      <c r="F14" s="193">
         <v>0</v>
       </c>
       <c r="H14" s="173">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I14" s="236">
+      <c r="I14" s="194">
         <v>1258.5903089702933</v>
       </c>
       <c r="K14" s="150">
         <f t="shared" si="0"/>
         <v>1258.5903089702933</v>
       </c>
-      <c r="M14" s="237">
+      <c r="M14" s="195">
         <f t="shared" si="2"/>
         <v>1258.5903089702933</v>
       </c>
@@ -5156,33 +5198,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="232">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B15" s="190">
         <v>4</v>
       </c>
-      <c r="C15" s="232" t="s">
+      <c r="C15" s="190" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="233">
-        <v>0</v>
-      </c>
-      <c r="E15" s="234">
-        <v>0</v>
-      </c>
-      <c r="F15" s="235">
+      <c r="D15" s="191">
+        <v>0</v>
+      </c>
+      <c r="E15" s="192">
+        <v>0</v>
+      </c>
+      <c r="F15" s="193">
         <v>0</v>
       </c>
       <c r="H15" s="173">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I15" s="236">
+      <c r="I15" s="194">
         <v>1258.5903089702933</v>
       </c>
       <c r="K15" s="150">
         <f t="shared" si="0"/>
         <v>1258.5903089702933</v>
       </c>
-      <c r="M15" s="237">
+      <c r="M15" s="195">
         <f t="shared" si="2"/>
         <v>1258.5903089702933</v>
       </c>
@@ -5191,33 +5233,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B16" s="232">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B16" s="190">
         <v>4</v>
       </c>
-      <c r="C16" s="232" t="s">
+      <c r="C16" s="190" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="233">
-        <v>0</v>
-      </c>
-      <c r="E16" s="234">
-        <v>0</v>
-      </c>
-      <c r="F16" s="235">
+      <c r="D16" s="191">
+        <v>0</v>
+      </c>
+      <c r="E16" s="192">
+        <v>0</v>
+      </c>
+      <c r="F16" s="193">
         <v>0</v>
       </c>
       <c r="H16" s="173">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I16" s="236">
+      <c r="I16" s="194">
         <v>1538.2770442970254</v>
       </c>
       <c r="K16" s="150">
         <f t="shared" si="0"/>
         <v>1538.2770442970254</v>
       </c>
-      <c r="M16" s="237">
+      <c r="M16" s="195">
         <f t="shared" si="2"/>
         <v>1538.2770442970254</v>
       </c>
@@ -5226,33 +5268,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B17" s="232">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B17" s="190">
         <v>4</v>
       </c>
-      <c r="C17" s="232" t="s">
+      <c r="C17" s="190" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="233">
-        <v>0</v>
-      </c>
-      <c r="E17" s="234">
-        <v>0</v>
-      </c>
-      <c r="F17" s="235">
+      <c r="D17" s="191">
+        <v>0</v>
+      </c>
+      <c r="E17" s="192">
+        <v>0</v>
+      </c>
+      <c r="F17" s="193">
         <v>0</v>
       </c>
       <c r="H17" s="173">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I17" s="236">
+      <c r="I17" s="194">
         <v>1538.2770442970254</v>
       </c>
       <c r="K17" s="150">
         <f t="shared" si="0"/>
         <v>1538.2770442970254</v>
       </c>
-      <c r="M17" s="237">
+      <c r="M17" s="195">
         <f t="shared" si="2"/>
         <v>1538.2770442970254</v>
       </c>
@@ -5261,33 +5303,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B18" s="232">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B18" s="190">
         <v>4</v>
       </c>
-      <c r="C18" s="232" t="s">
+      <c r="C18" s="190" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="233">
-        <v>0</v>
-      </c>
-      <c r="E18" s="234">
-        <v>0</v>
-      </c>
-      <c r="F18" s="235">
+      <c r="D18" s="191">
+        <v>0</v>
+      </c>
+      <c r="E18" s="192">
+        <v>0</v>
+      </c>
+      <c r="F18" s="193">
         <v>0</v>
       </c>
       <c r="H18" s="173">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I18" s="236">
+      <c r="I18" s="194">
         <v>1258.5903089702933</v>
       </c>
       <c r="K18" s="150">
         <f t="shared" si="0"/>
         <v>1258.5903089702933</v>
       </c>
-      <c r="M18" s="237">
+      <c r="M18" s="195">
         <f t="shared" si="2"/>
         <v>1258.5903089702933</v>
       </c>
@@ -5296,19 +5338,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B19" s="232"/>
-      <c r="C19" s="232"/>
-      <c r="D19" s="233"/>
-      <c r="E19" s="234"/>
-      <c r="F19" s="239"/>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B19" s="190"/>
+      <c r="C19" s="190"/>
+      <c r="D19" s="191"/>
+      <c r="E19" s="192"/>
+      <c r="F19" s="197"/>
       <c r="H19" s="106"/>
       <c r="I19" s="175"/>
       <c r="K19" s="106"/>
       <c r="M19" s="108"/>
       <c r="O19" s="107"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" s="106"/>
       <c r="C20" s="106" t="s">
         <v>153</v>
@@ -5318,11 +5360,11 @@
         <v>544.30000000000018</v>
       </c>
       <c r="E20" s="107"/>
-      <c r="F20" s="239">
+      <c r="F20" s="197">
         <f>SUM(F4:F19)</f>
         <v>205609.79205610568</v>
       </c>
-      <c r="H20" s="240"/>
+      <c r="H20" s="198"/>
       <c r="I20" s="175">
         <f>SUM(I4:I19)</f>
         <v>22374.938826138547</v>
@@ -5331,7 +5373,7 @@
         <f>SUM(K4:K19)</f>
         <v>227984.7308822443</v>
       </c>
-      <c r="M20" s="241">
+      <c r="M20" s="199">
         <f>SUM(M4:M19)</f>
         <v>19298.384737544497</v>
       </c>
@@ -5340,7 +5382,7 @@
         <v>208686.34614469972</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21" s="106"/>
       <c r="C21" s="106"/>
       <c r="D21" s="4"/>
@@ -5349,7 +5391,7 @@
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B22" s="106" t="s">
         <v>85</v>
       </c>
@@ -5362,20 +5404,20 @@
       <c r="H22" s="173">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="I22" s="236">
+      <c r="I22" s="194">
         <v>163.15059560726027</v>
       </c>
-      <c r="K22" s="242">
+      <c r="K22" s="200">
         <f>I22</f>
         <v>163.15059560726027</v>
       </c>
-      <c r="M22" s="243"/>
+      <c r="M22" s="201"/>
       <c r="O22" s="150">
         <f>K22-M22</f>
         <v>163.15059560726027</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B23" s="106" t="s">
         <v>85</v>
       </c>
@@ -5388,20 +5430,20 @@
       <c r="H23" s="173">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I23" s="236">
+      <c r="I23" s="194">
         <v>139.84336766336594</v>
       </c>
-      <c r="K23" s="242">
+      <c r="K23" s="200">
         <f t="shared" ref="K23:K29" si="3">I23</f>
         <v>139.84336766336594</v>
       </c>
-      <c r="M23" s="243"/>
+      <c r="M23" s="201"/>
       <c r="O23" s="150">
         <f t="shared" ref="O23:O29" si="4">K23-M23</f>
         <v>139.84336766336594</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B24" s="106" t="s">
         <v>85</v>
       </c>
@@ -5414,20 +5456,20 @@
       <c r="H24" s="173">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I24" s="236">
+      <c r="I24" s="194">
         <v>139.84336766336594</v>
       </c>
-      <c r="K24" s="242">
+      <c r="K24" s="200">
         <f t="shared" si="3"/>
         <v>139.84336766336594</v>
       </c>
-      <c r="M24" s="243"/>
+      <c r="M24" s="201"/>
       <c r="O24" s="150">
         <f t="shared" si="4"/>
         <v>139.84336766336594</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" s="106" t="s">
         <v>85</v>
       </c>
@@ -5440,20 +5482,20 @@
       <c r="H25" s="173">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I25" s="236">
+      <c r="I25" s="194">
         <v>139.84336766336594</v>
       </c>
-      <c r="K25" s="242">
+      <c r="K25" s="200">
         <f t="shared" si="3"/>
         <v>139.84336766336594</v>
       </c>
-      <c r="M25" s="243"/>
+      <c r="M25" s="201"/>
       <c r="O25" s="150">
         <f t="shared" si="4"/>
         <v>139.84336766336594</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B26" s="106" t="s">
         <v>85</v>
       </c>
@@ -5466,20 +5508,20 @@
       <c r="H26" s="173">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I26" s="236">
+      <c r="I26" s="194">
         <v>139.84336766336594</v>
       </c>
-      <c r="K26" s="242">
+      <c r="K26" s="200">
         <f t="shared" si="3"/>
         <v>139.84336766336594</v>
       </c>
-      <c r="M26" s="243"/>
+      <c r="M26" s="201"/>
       <c r="O26" s="150">
         <f t="shared" si="4"/>
         <v>139.84336766336594</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B27" s="106" t="s">
         <v>85</v>
       </c>
@@ -5492,20 +5534,20 @@
       <c r="H27" s="173">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I27" s="236">
+      <c r="I27" s="194">
         <v>69.921683831682969</v>
       </c>
-      <c r="K27" s="242">
+      <c r="K27" s="200">
         <f t="shared" si="3"/>
         <v>69.921683831682969</v>
       </c>
-      <c r="M27" s="243"/>
+      <c r="M27" s="201"/>
       <c r="O27" s="150">
         <f t="shared" si="4"/>
         <v>69.921683831682969</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B28" s="106" t="s">
         <v>85</v>
       </c>
@@ -5518,20 +5560,20 @@
       <c r="H28" s="173">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I28" s="236">
+      <c r="I28" s="194">
         <v>69.921683831682969</v>
       </c>
-      <c r="K28" s="242">
+      <c r="K28" s="200">
         <f t="shared" si="3"/>
         <v>69.921683831682969</v>
       </c>
-      <c r="M28" s="243"/>
+      <c r="M28" s="201"/>
       <c r="O28" s="150">
         <f t="shared" si="4"/>
         <v>69.921683831682969</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B29" s="106" t="s">
         <v>85</v>
       </c>
@@ -5544,32 +5586,32 @@
       <c r="H29" s="173">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I29" s="236">
+      <c r="I29" s="194">
         <v>69.921683831682969</v>
       </c>
-      <c r="K29" s="242">
+      <c r="K29" s="200">
         <f t="shared" si="3"/>
         <v>69.921683831682969</v>
       </c>
-      <c r="M29" s="243"/>
+      <c r="M29" s="201"/>
       <c r="O29" s="150">
         <f t="shared" si="4"/>
         <v>69.921683831682969</v>
       </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="H30" s="107" t="s">
         <v>130</v>
       </c>
-      <c r="I30" s="236">
+      <c r="I30" s="194">
         <f>SUM(I22:I29)</f>
         <v>932.28911775577285</v>
       </c>
-      <c r="K30" s="244">
+      <c r="K30" s="202">
         <f>SUM(K22:K29)</f>
         <v>932.28911775577285</v>
       </c>
-      <c r="M30" s="241">
+      <c r="M30" s="199">
         <f>SUM(M22:M29)</f>
         <v>0</v>
       </c>
@@ -5578,18 +5620,18 @@
         <v>932.28911775577285</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O31" s="150"/>
     </row>
-    <row r="32" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D32" s="226" t="s">
+    <row r="32" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D32" s="244" t="s">
         <v>131</v>
       </c>
-      <c r="E32" s="227"/>
+      <c r="E32" s="245"/>
       <c r="F32" s="177">
         <v>228917.02000000002</v>
       </c>
-      <c r="I32" s="245">
+      <c r="I32" s="203">
         <f>F20+I20+I30</f>
         <v>228917.02000000002</v>
       </c>
@@ -5597,7 +5639,7 @@
         <f>K20+K30</f>
         <v>228917.02000000008</v>
       </c>
-      <c r="M32" s="241">
+      <c r="M32" s="199">
         <f>M20+M30</f>
         <v>19298.384737544497</v>
       </c>
@@ -5612,16 +5654,17 @@
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="D32:E32"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B474AF3-BA14-4AC3-BE41-D99CD4C43EE8}">
   <dimension ref="C3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3" s="178" t="s">
         <v>132</v>
       </c>
